--- a/target/classes/com/ratioTable.xlsx
+++ b/target/classes/com/ratioTable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IT\Documents\GitHub\Balatro\src\main\resources\com\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFBD2F77-1312-4030-80F4-3F7BCD96150F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D521942-BA47-4134-9A2E-F3BA3120DFF6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7890" xr2:uid="{706E2108-D16A-4E70-A675-C3702A172F02}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="44">
   <si>
     <t>Play Button</t>
   </si>
@@ -38,9 +38,6 @@
   </si>
   <si>
     <t>Sort</t>
-  </si>
-  <si>
-    <t>Deck</t>
   </si>
   <si>
     <t>Reward</t>
@@ -155,6 +152,12 @@
   </si>
   <si>
     <t>Game Screen Layout</t>
+  </si>
+  <si>
+    <t>Cards</t>
+  </si>
+  <si>
+    <t>Cards OverView</t>
   </si>
 </sst>
 </file>
@@ -568,7 +571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AE52DC3-6553-4C6D-A135-8A8C4D8FA77D}">
-  <dimension ref="A1:O115"/>
+  <dimension ref="A1:O111"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="11.42578125" style="4"/>
@@ -585,28 +588,28 @@
   <sheetData>
     <row r="1" spans="1:15">
       <c r="C1" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="10" t="s">
-        <v>32</v>
-      </c>
       <c r="G1" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="H1" s="10" t="s">
-        <v>32</v>
-      </c>
       <c r="J1" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="K1" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="K1" s="10" t="s">
-        <v>32</v>
-      </c>
       <c r="M1" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N1" s="10" t="s">
         <v>31</v>
-      </c>
-      <c r="N1" s="10" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:15">
@@ -637,7 +640,7 @@
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B3" s="11"/>
       <c r="C3" s="12"/>
@@ -660,7 +663,7 @@
     </row>
     <row r="5" spans="1:15">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C5" s="4">
         <v>1444</v>
@@ -707,7 +710,7 @@
     </row>
     <row r="7" spans="1:15">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C7" s="4">
         <v>1214</v>
@@ -754,7 +757,7 @@
     </row>
     <row r="9" spans="1:15">
       <c r="A9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C9" s="4">
         <v>1262</v>
@@ -801,7 +804,7 @@
     </row>
     <row r="11" spans="1:15">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C11" s="4">
         <v>1652</v>
@@ -848,7 +851,7 @@
     </row>
     <row r="13" spans="1:15">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C13" s="4">
         <v>1294</v>
@@ -895,7 +898,7 @@
     </row>
     <row r="15" spans="1:15">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C15" s="4">
         <v>2148</v>
@@ -942,7 +945,7 @@
     </row>
     <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C17" s="4">
         <v>1444</v>
@@ -989,7 +992,7 @@
     </row>
     <row r="19" spans="1:14">
       <c r="A19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C19" s="4">
         <v>824</v>
@@ -1036,7 +1039,7 @@
     </row>
     <row r="21" spans="1:14">
       <c r="A21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C21" s="4">
         <v>1914</v>
@@ -1083,7 +1086,7 @@
     </row>
     <row r="23" spans="1:14">
       <c r="A23" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C23" s="4">
         <v>2038</v>
@@ -1168,7 +1171,7 @@
     </row>
     <row r="27" spans="1:14" s="11" customFormat="1">
       <c r="A27" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C27" s="12"/>
       <c r="E27" s="13"/>
@@ -1184,7 +1187,7 @@
     </row>
     <row r="29" spans="1:14">
       <c r="A29" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C29" s="4">
         <v>572</v>
@@ -1230,37 +1233,46 @@
       <c r="H30" s="6"/>
     </row>
     <row r="31" spans="1:14">
+      <c r="A31" t="s">
+        <v>42</v>
+      </c>
+      <c r="C31" s="4">
+        <v>220</v>
+      </c>
+      <c r="D31" s="6">
+        <v>292</v>
+      </c>
       <c r="E31" s="1">
         <f t="shared" ref="E31" si="80" xml:space="preserve"> C31/C$2</f>
-        <v>0</v>
+        <v>8.59375E-2</v>
       </c>
       <c r="F31" s="1">
         <f t="shared" ref="F31" si="81" xml:space="preserve"> D31/D$2</f>
-        <v>0</v>
+        <v>0.20277777777777778</v>
       </c>
       <c r="G31" s="4">
         <f t="shared" ref="G31" si="82">IF(ISBLANK(C31),0,(C31*G$2/C$2))</f>
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="H31" s="6">
         <f t="shared" ref="H31" si="83">IF(ISBLANK(D31),0,(D31*H$2/D$2))</f>
-        <v>0</v>
+        <v>438</v>
       </c>
       <c r="J31" s="4">
         <f t="shared" ref="J31" si="84">IF(ISBLANK(C31),0,(C31*J$2/C$2))</f>
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="K31" s="6">
         <f t="shared" ref="K31" si="85">IF(ISBLANK(D31),0,(D31*K$2/D$2))</f>
-        <v>0</v>
+        <v>219</v>
       </c>
       <c r="M31" s="4">
         <f t="shared" ref="M31" si="86">IF(ISBLANK(C31),0,(C31*M$2/C$2))</f>
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="N31" s="6">
         <f t="shared" ref="N31" si="87">IF(ISBLANK(D31),0,(D31*N$2/D$2))</f>
-        <v>0</v>
+        <v>146</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1268,37 +1280,46 @@
       <c r="H32" s="6"/>
     </row>
     <row r="33" spans="1:14">
+      <c r="A33" t="s">
+        <v>43</v>
+      </c>
+      <c r="C33" s="4">
+        <v>140</v>
+      </c>
+      <c r="D33" s="6">
+        <v>200</v>
+      </c>
       <c r="E33" s="1">
         <f t="shared" ref="E33" si="88" xml:space="preserve"> C33/C$2</f>
-        <v>0</v>
+        <v>5.46875E-2</v>
       </c>
       <c r="F33" s="1">
         <f t="shared" ref="F33" si="89" xml:space="preserve"> D33/D$2</f>
-        <v>0</v>
+        <v>0.1388888888888889</v>
       </c>
       <c r="G33" s="4">
         <f t="shared" ref="G33" si="90">IF(ISBLANK(C33),0,(C33*G$2/C$2))</f>
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="H33" s="6">
         <f t="shared" ref="H33" si="91">IF(ISBLANK(D33),0,(D33*H$2/D$2))</f>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="J33" s="4">
         <f t="shared" ref="J33" si="92">IF(ISBLANK(C33),0,(C33*J$2/C$2))</f>
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="K33" s="6">
         <f t="shared" ref="K33" si="93">IF(ISBLANK(D33),0,(D33*K$2/D$2))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M33" s="4">
         <f t="shared" ref="M33" si="94">IF(ISBLANK(C33),0,(C33*M$2/C$2))</f>
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="N33" s="6">
         <f t="shared" ref="N33" si="95">IF(ISBLANK(D33),0,(D33*N$2/D$2))</f>
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="34" spans="1:14">
@@ -1444,7 +1465,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C43" s="4">
         <v>572</v>
@@ -1794,80 +1815,50 @@
       </c>
     </row>
     <row r="52" spans="1:14">
-      <c r="E52" s="1">
-        <f xml:space="preserve"> C52/C$2</f>
-        <v>0</v>
-      </c>
-      <c r="F52" s="1">
-        <f xml:space="preserve"> D52/D$2</f>
-        <v>0</v>
-      </c>
-      <c r="G52" s="4">
-        <f>IF(ISBLANK(C52),0,(C52*G$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="H52" s="6">
-        <f>IF(ISBLANK(D52),0,(D52*H$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="J52" s="4">
-        <f>IF(ISBLANK(C52),0,(C52*J$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="K52" s="6">
-        <f>IF(ISBLANK(D52),0,(D52*K$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="M52" s="4">
-        <f>IF(ISBLANK(C52),0,(C52*M$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="N52" s="6">
-        <f>IF(ISBLANK(D52),0,(D52*N$2/D$2))</f>
-        <v>0</v>
-      </c>
+      <c r="G52" s="4"/>
+      <c r="H52" s="6"/>
     </row>
     <row r="53" spans="1:14">
       <c r="A53" t="s">
         <v>4</v>
       </c>
       <c r="C53" s="4">
-        <v>212</v>
+        <v>1200</v>
       </c>
       <c r="D53" s="6">
-        <v>284</v>
+        <v>944</v>
       </c>
       <c r="E53" s="1">
         <f xml:space="preserve"> C53/C$2</f>
-        <v>8.2812499999999997E-2</v>
+        <v>0.46875</v>
       </c>
       <c r="F53" s="1">
         <f xml:space="preserve"> D53/D$2</f>
-        <v>0.19722222222222222</v>
+        <v>0.65555555555555556</v>
       </c>
       <c r="G53" s="4">
         <f>IF(ISBLANK(C53),0,(C53*G$2/C$2))</f>
-        <v>318</v>
+        <v>1800</v>
       </c>
       <c r="H53" s="6">
         <f>IF(ISBLANK(D53),0,(D53*H$2/D$2))</f>
-        <v>426</v>
+        <v>1416</v>
       </c>
       <c r="J53" s="4">
         <f>IF(ISBLANK(C53),0,(C53*J$2/C$2))</f>
-        <v>159</v>
+        <v>900</v>
       </c>
       <c r="K53" s="6">
         <f>IF(ISBLANK(D53),0,(D53*K$2/D$2))</f>
-        <v>213</v>
+        <v>708</v>
       </c>
       <c r="M53" s="4">
         <f>IF(ISBLANK(C53),0,(C53*M$2/C$2))</f>
-        <v>106</v>
+        <v>600</v>
       </c>
       <c r="N53" s="6">
         <f>IF(ISBLANK(D53),0,(D53*N$2/D$2))</f>
-        <v>142</v>
+        <v>472</v>
       </c>
     </row>
     <row r="54" spans="1:14">
@@ -1906,45 +1897,45 @@
     </row>
     <row r="55" spans="1:14">
       <c r="A55" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C55" s="4">
-        <v>1200</v>
+        <v>420</v>
       </c>
       <c r="D55" s="6">
-        <v>944</v>
+        <v>1032</v>
       </c>
       <c r="E55" s="1">
         <f xml:space="preserve"> C55/C$2</f>
-        <v>0.46875</v>
+        <v>0.1640625</v>
       </c>
       <c r="F55" s="1">
         <f xml:space="preserve"> D55/D$2</f>
-        <v>0.65555555555555556</v>
+        <v>0.71666666666666667</v>
       </c>
       <c r="G55" s="4">
         <f>IF(ISBLANK(C55),0,(C55*G$2/C$2))</f>
-        <v>1800</v>
+        <v>630</v>
       </c>
       <c r="H55" s="6">
         <f>IF(ISBLANK(D55),0,(D55*H$2/D$2))</f>
-        <v>1416</v>
+        <v>1548</v>
       </c>
       <c r="J55" s="4">
         <f>IF(ISBLANK(C55),0,(C55*J$2/C$2))</f>
-        <v>900</v>
+        <v>315</v>
       </c>
       <c r="K55" s="6">
         <f>IF(ISBLANK(D55),0,(D55*K$2/D$2))</f>
-        <v>708</v>
+        <v>774</v>
       </c>
       <c r="M55" s="4">
         <f>IF(ISBLANK(C55),0,(C55*M$2/C$2))</f>
-        <v>600</v>
+        <v>210</v>
       </c>
       <c r="N55" s="6">
         <f>IF(ISBLANK(D55),0,(D55*N$2/D$2))</f>
-        <v>472</v>
+        <v>516</v>
       </c>
     </row>
     <row r="56" spans="1:14">
@@ -1986,42 +1977,42 @@
         <v>7</v>
       </c>
       <c r="C57" s="4">
-        <v>420</v>
+        <v>1360</v>
       </c>
       <c r="D57" s="6">
-        <v>1032</v>
+        <v>952</v>
       </c>
       <c r="E57" s="1">
         <f xml:space="preserve"> C57/C$2</f>
-        <v>0.1640625</v>
+        <v>0.53125</v>
       </c>
       <c r="F57" s="1">
         <f xml:space="preserve"> D57/D$2</f>
-        <v>0.71666666666666667</v>
+        <v>0.66111111111111109</v>
       </c>
       <c r="G57" s="4">
         <f>IF(ISBLANK(C57),0,(C57*G$2/C$2))</f>
-        <v>630</v>
+        <v>2040</v>
       </c>
       <c r="H57" s="6">
         <f>IF(ISBLANK(D57),0,(D57*H$2/D$2))</f>
-        <v>1548</v>
+        <v>1428</v>
       </c>
       <c r="J57" s="4">
         <f>IF(ISBLANK(C57),0,(C57*J$2/C$2))</f>
-        <v>315</v>
+        <v>1020</v>
       </c>
       <c r="K57" s="6">
         <f>IF(ISBLANK(D57),0,(D57*K$2/D$2))</f>
-        <v>774</v>
+        <v>714</v>
       </c>
       <c r="M57" s="4">
         <f>IF(ISBLANK(C57),0,(C57*M$2/C$2))</f>
-        <v>210</v>
+        <v>680</v>
       </c>
       <c r="N57" s="6">
         <f>IF(ISBLANK(D57),0,(D57*N$2/D$2))</f>
-        <v>516</v>
+        <v>476</v>
       </c>
     </row>
     <row r="58" spans="1:14">
@@ -2063,42 +2054,42 @@
         <v>8</v>
       </c>
       <c r="C59" s="4">
-        <v>1360</v>
+        <v>712</v>
       </c>
       <c r="D59" s="6">
-        <v>952</v>
+        <v>488</v>
       </c>
       <c r="E59" s="1">
         <f xml:space="preserve"> C59/C$2</f>
-        <v>0.53125</v>
+        <v>0.27812500000000001</v>
       </c>
       <c r="F59" s="1">
         <f xml:space="preserve"> D59/D$2</f>
-        <v>0.66111111111111109</v>
+        <v>0.33888888888888891</v>
       </c>
       <c r="G59" s="4">
         <f>IF(ISBLANK(C59),0,(C59*G$2/C$2))</f>
-        <v>2040</v>
+        <v>1068</v>
       </c>
       <c r="H59" s="6">
         <f>IF(ISBLANK(D59),0,(D59*H$2/D$2))</f>
-        <v>1428</v>
+        <v>732</v>
       </c>
       <c r="J59" s="4">
         <f>IF(ISBLANK(C59),0,(C59*J$2/C$2))</f>
-        <v>1020</v>
+        <v>534</v>
       </c>
       <c r="K59" s="6">
         <f>IF(ISBLANK(D59),0,(D59*K$2/D$2))</f>
-        <v>714</v>
+        <v>366</v>
       </c>
       <c r="M59" s="4">
         <f>IF(ISBLANK(C59),0,(C59*M$2/C$2))</f>
-        <v>680</v>
+        <v>356</v>
       </c>
       <c r="N59" s="6">
         <f>IF(ISBLANK(D59),0,(D59*N$2/D$2))</f>
-        <v>476</v>
+        <v>244</v>
       </c>
     </row>
     <row r="60" spans="1:14">
@@ -2137,45 +2128,42 @@
     </row>
     <row r="61" spans="1:14">
       <c r="A61" t="s">
-        <v>9</v>
-      </c>
-      <c r="C61" s="4">
-        <v>712</v>
+        <v>10</v>
       </c>
       <c r="D61" s="6">
-        <v>488</v>
+        <v>412</v>
       </c>
       <c r="E61" s="1">
         <f xml:space="preserve"> C61/C$2</f>
-        <v>0.27812500000000001</v>
+        <v>0</v>
       </c>
       <c r="F61" s="1">
         <f xml:space="preserve"> D61/D$2</f>
-        <v>0.33888888888888891</v>
+        <v>0.28611111111111109</v>
       </c>
       <c r="G61" s="4">
         <f>IF(ISBLANK(C61),0,(C61*G$2/C$2))</f>
-        <v>1068</v>
+        <v>0</v>
       </c>
       <c r="H61" s="6">
         <f>IF(ISBLANK(D61),0,(D61*H$2/D$2))</f>
-        <v>732</v>
+        <v>618</v>
       </c>
       <c r="J61" s="4">
         <f>IF(ISBLANK(C61),0,(C61*J$2/C$2))</f>
-        <v>534</v>
+        <v>0</v>
       </c>
       <c r="K61" s="6">
         <f>IF(ISBLANK(D61),0,(D61*K$2/D$2))</f>
-        <v>366</v>
+        <v>309</v>
       </c>
       <c r="M61" s="4">
         <f>IF(ISBLANK(C61),0,(C61*M$2/C$2))</f>
-        <v>356</v>
+        <v>0</v>
       </c>
       <c r="N61" s="6">
         <f>IF(ISBLANK(D61),0,(D61*N$2/D$2))</f>
-        <v>244</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62" spans="1:14">
@@ -2214,42 +2202,45 @@
     </row>
     <row r="63" spans="1:14">
       <c r="A63" t="s">
-        <v>11</v>
+        <v>17</v>
+      </c>
+      <c r="C63" s="4">
+        <v>228</v>
       </c>
       <c r="D63" s="6">
-        <v>412</v>
+        <v>372</v>
       </c>
       <c r="E63" s="1">
         <f xml:space="preserve"> C63/C$2</f>
-        <v>0</v>
+        <v>8.9062500000000003E-2</v>
       </c>
       <c r="F63" s="1">
         <f xml:space="preserve"> D63/D$2</f>
-        <v>0.28611111111111109</v>
+        <v>0.25833333333333336</v>
       </c>
       <c r="G63" s="4">
         <f>IF(ISBLANK(C63),0,(C63*G$2/C$2))</f>
-        <v>0</v>
+        <v>342</v>
       </c>
       <c r="H63" s="6">
         <f>IF(ISBLANK(D63),0,(D63*H$2/D$2))</f>
-        <v>618</v>
+        <v>558</v>
       </c>
       <c r="J63" s="4">
         <f>IF(ISBLANK(C63),0,(C63*J$2/C$2))</f>
-        <v>0</v>
+        <v>171</v>
       </c>
       <c r="K63" s="6">
         <f>IF(ISBLANK(D63),0,(D63*K$2/D$2))</f>
-        <v>309</v>
+        <v>279</v>
       </c>
       <c r="M63" s="4">
         <f>IF(ISBLANK(C63),0,(C63*M$2/C$2))</f>
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="N63" s="6">
         <f>IF(ISBLANK(D63),0,(D63*N$2/D$2))</f>
-        <v>206</v>
+        <v>186</v>
       </c>
     </row>
     <row r="64" spans="1:14">
@@ -2288,45 +2279,45 @@
     </row>
     <row r="65" spans="1:14">
       <c r="A65" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C65" s="4">
-        <v>220</v>
+        <v>1320</v>
       </c>
       <c r="D65" s="6">
-        <v>292</v>
+        <v>960</v>
       </c>
       <c r="E65" s="1">
         <f xml:space="preserve"> C65/C$2</f>
-        <v>8.59375E-2</v>
+        <v>0.515625</v>
       </c>
       <c r="F65" s="1">
         <f xml:space="preserve"> D65/D$2</f>
-        <v>0.20277777777777778</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="G65" s="4">
         <f>IF(ISBLANK(C65),0,(C65*G$2/C$2))</f>
-        <v>330</v>
+        <v>1980</v>
       </c>
       <c r="H65" s="6">
         <f>IF(ISBLANK(D65),0,(D65*H$2/D$2))</f>
-        <v>438</v>
+        <v>1440</v>
       </c>
       <c r="J65" s="4">
         <f>IF(ISBLANK(C65),0,(C65*J$2/C$2))</f>
-        <v>165</v>
+        <v>990</v>
       </c>
       <c r="K65" s="6">
         <f>IF(ISBLANK(D65),0,(D65*K$2/D$2))</f>
-        <v>219</v>
+        <v>720</v>
       </c>
       <c r="M65" s="4">
         <f>IF(ISBLANK(C65),0,(C65*M$2/C$2))</f>
-        <v>110</v>
+        <v>660</v>
       </c>
       <c r="N65" s="6">
         <f>IF(ISBLANK(D65),0,(D65*N$2/D$2))</f>
-        <v>146</v>
+        <v>480</v>
       </c>
     </row>
     <row r="66" spans="1:14">
@@ -2367,43 +2358,40 @@
       <c r="A67" t="s">
         <v>18</v>
       </c>
-      <c r="C67" s="4">
-        <v>228</v>
-      </c>
       <c r="D67" s="6">
-        <v>372</v>
+        <v>82</v>
       </c>
       <c r="E67" s="1">
         <f xml:space="preserve"> C67/C$2</f>
-        <v>8.9062500000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="F67" s="1">
         <f xml:space="preserve"> D67/D$2</f>
-        <v>0.25833333333333336</v>
+        <v>5.6944444444444443E-2</v>
       </c>
       <c r="G67" s="4">
         <f>IF(ISBLANK(C67),0,(C67*G$2/C$2))</f>
-        <v>342</v>
+        <v>0</v>
       </c>
       <c r="H67" s="6">
         <f>IF(ISBLANK(D67),0,(D67*H$2/D$2))</f>
-        <v>558</v>
+        <v>123</v>
       </c>
       <c r="J67" s="4">
         <f>IF(ISBLANK(C67),0,(C67*J$2/C$2))</f>
-        <v>171</v>
+        <v>0</v>
       </c>
       <c r="K67" s="6">
         <f>IF(ISBLANK(D67),0,(D67*K$2/D$2))</f>
-        <v>279</v>
+        <v>61.5</v>
       </c>
       <c r="M67" s="4">
         <f>IF(ISBLANK(C67),0,(C67*M$2/C$2))</f>
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="N67" s="6">
         <f>IF(ISBLANK(D67),0,(D67*N$2/D$2))</f>
-        <v>186</v>
+        <v>41</v>
       </c>
     </row>
     <row r="68" spans="1:14">
@@ -2442,45 +2430,45 @@
     </row>
     <row r="69" spans="1:14">
       <c r="A69" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C69" s="4">
-        <v>1320</v>
+        <v>124</v>
       </c>
       <c r="D69" s="6">
-        <v>960</v>
+        <v>80</v>
       </c>
       <c r="E69" s="1">
         <f xml:space="preserve"> C69/C$2</f>
-        <v>0.515625</v>
+        <v>4.8437500000000001E-2</v>
       </c>
       <c r="F69" s="1">
         <f xml:space="preserve"> D69/D$2</f>
-        <v>0.66666666666666663</v>
+        <v>5.5555555555555552E-2</v>
       </c>
       <c r="G69" s="4">
         <f>IF(ISBLANK(C69),0,(C69*G$2/C$2))</f>
-        <v>1980</v>
+        <v>186</v>
       </c>
       <c r="H69" s="6">
         <f>IF(ISBLANK(D69),0,(D69*H$2/D$2))</f>
-        <v>1440</v>
+        <v>120</v>
       </c>
       <c r="J69" s="4">
         <f>IF(ISBLANK(C69),0,(C69*J$2/C$2))</f>
-        <v>990</v>
+        <v>93</v>
       </c>
       <c r="K69" s="6">
         <f>IF(ISBLANK(D69),0,(D69*K$2/D$2))</f>
-        <v>720</v>
+        <v>60</v>
       </c>
       <c r="M69" s="4">
         <f>IF(ISBLANK(C69),0,(C69*M$2/C$2))</f>
-        <v>660</v>
+        <v>62</v>
       </c>
       <c r="N69" s="6">
         <f>IF(ISBLANK(D69),0,(D69*N$2/D$2))</f>
-        <v>480</v>
+        <v>40</v>
       </c>
     </row>
     <row r="70" spans="1:14">
@@ -2519,42 +2507,45 @@
     </row>
     <row r="71" spans="1:14">
       <c r="A71" t="s">
-        <v>19</v>
+        <v>23</v>
+      </c>
+      <c r="C71" s="4">
+        <v>124</v>
       </c>
       <c r="D71" s="6">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="E71" s="1">
         <f xml:space="preserve"> C71/C$2</f>
-        <v>0</v>
+        <v>4.8437500000000001E-2</v>
       </c>
       <c r="F71" s="1">
         <f xml:space="preserve"> D71/D$2</f>
-        <v>5.6944444444444443E-2</v>
+        <v>6.9444444444444448E-2</v>
       </c>
       <c r="G71" s="4">
         <f>IF(ISBLANK(C71),0,(C71*G$2/C$2))</f>
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="H71" s="6">
         <f>IF(ISBLANK(D71),0,(D71*H$2/D$2))</f>
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="J71" s="4">
         <f>IF(ISBLANK(C71),0,(C71*J$2/C$2))</f>
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="K71" s="6">
         <f>IF(ISBLANK(D71),0,(D71*K$2/D$2))</f>
-        <v>61.5</v>
+        <v>75</v>
       </c>
       <c r="M71" s="4">
         <f>IF(ISBLANK(C71),0,(C71*M$2/C$2))</f>
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="N71" s="6">
         <f>IF(ISBLANK(D71),0,(D71*N$2/D$2))</f>
-        <v>41</v>
+        <v>50</v>
       </c>
     </row>
     <row r="72" spans="1:14">
@@ -2593,45 +2584,45 @@
     </row>
     <row r="73" spans="1:14">
       <c r="A73" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C73" s="4">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="D73" s="6">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="E73" s="1">
         <f xml:space="preserve"> C73/C$2</f>
-        <v>4.8437500000000001E-2</v>
+        <v>4.5312499999999999E-2</v>
       </c>
       <c r="F73" s="1">
         <f xml:space="preserve"> D73/D$2</f>
-        <v>5.5555555555555552E-2</v>
+        <v>7.7777777777777779E-2</v>
       </c>
       <c r="G73" s="4">
         <f>IF(ISBLANK(C73),0,(C73*G$2/C$2))</f>
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="H73" s="6">
         <f>IF(ISBLANK(D73),0,(D73*H$2/D$2))</f>
-        <v>120</v>
+        <v>168</v>
       </c>
       <c r="J73" s="4">
         <f>IF(ISBLANK(C73),0,(C73*J$2/C$2))</f>
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="K73" s="6">
         <f>IF(ISBLANK(D73),0,(D73*K$2/D$2))</f>
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="M73" s="4">
         <f>IF(ISBLANK(C73),0,(C73*M$2/C$2))</f>
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="N73" s="6">
         <f>IF(ISBLANK(D73),0,(D73*N$2/D$2))</f>
-        <v>40</v>
+        <v>56</v>
       </c>
     </row>
     <row r="74" spans="1:14">
@@ -2669,237 +2660,237 @@
       </c>
     </row>
     <row r="75" spans="1:14">
-      <c r="A75" t="s">
-        <v>24</v>
-      </c>
-      <c r="C75" s="4">
-        <v>124</v>
-      </c>
-      <c r="D75" s="6">
-        <v>100</v>
-      </c>
       <c r="E75" s="1">
         <f xml:space="preserve"> C75/C$2</f>
-        <v>4.8437500000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="F75" s="1">
         <f xml:space="preserve"> D75/D$2</f>
-        <v>6.9444444444444448E-2</v>
+        <v>0</v>
       </c>
       <c r="G75" s="4">
         <f>IF(ISBLANK(C75),0,(C75*G$2/C$2))</f>
-        <v>186</v>
+        <v>0</v>
       </c>
       <c r="H75" s="6">
         <f>IF(ISBLANK(D75),0,(D75*H$2/D$2))</f>
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="J75" s="4">
         <f>IF(ISBLANK(C75),0,(C75*J$2/C$2))</f>
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="K75" s="6">
         <f>IF(ISBLANK(D75),0,(D75*K$2/D$2))</f>
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="M75" s="4">
         <f>IF(ISBLANK(C75),0,(C75*M$2/C$2))</f>
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="N75" s="6">
         <f>IF(ISBLANK(D75),0,(D75*N$2/D$2))</f>
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:14">
+      <c r="A76" t="s">
+        <v>26</v>
+      </c>
+      <c r="C76" s="4">
+        <v>280</v>
+      </c>
+      <c r="D76" s="6">
+        <v>84</v>
+      </c>
       <c r="E76" s="1">
         <f xml:space="preserve"> C76/C$2</f>
-        <v>0</v>
+        <v>0.109375</v>
       </c>
       <c r="F76" s="1">
         <f xml:space="preserve"> D76/D$2</f>
-        <v>0</v>
+        <v>5.8333333333333334E-2</v>
       </c>
       <c r="G76" s="4">
         <f>IF(ISBLANK(C76),0,(C76*G$2/C$2))</f>
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="H76" s="6">
         <f>IF(ISBLANK(D76),0,(D76*H$2/D$2))</f>
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="J76" s="4">
         <f>IF(ISBLANK(C76),0,(C76*J$2/C$2))</f>
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="K76" s="6">
         <f>IF(ISBLANK(D76),0,(D76*K$2/D$2))</f>
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="M76" s="4">
         <f>IF(ISBLANK(C76),0,(C76*M$2/C$2))</f>
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="N76" s="6">
         <f>IF(ISBLANK(D76),0,(D76*N$2/D$2))</f>
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="77" spans="1:14">
-      <c r="A77" t="s">
-        <v>25</v>
-      </c>
-      <c r="C77" s="4">
-        <v>116</v>
-      </c>
-      <c r="D77" s="6">
-        <v>112</v>
-      </c>
       <c r="E77" s="1">
         <f xml:space="preserve"> C77/C$2</f>
-        <v>4.5312499999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="F77" s="1">
         <f xml:space="preserve"> D77/D$2</f>
-        <v>7.7777777777777779E-2</v>
+        <v>0</v>
       </c>
       <c r="G77" s="4">
         <f>IF(ISBLANK(C77),0,(C77*G$2/C$2))</f>
-        <v>174</v>
+        <v>0</v>
       </c>
       <c r="H77" s="6">
         <f>IF(ISBLANK(D77),0,(D77*H$2/D$2))</f>
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="J77" s="4">
         <f>IF(ISBLANK(C77),0,(C77*J$2/C$2))</f>
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="K77" s="6">
         <f>IF(ISBLANK(D77),0,(D77*K$2/D$2))</f>
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="M77" s="4">
         <f>IF(ISBLANK(C77),0,(C77*M$2/C$2))</f>
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="N77" s="6">
         <f>IF(ISBLANK(D77),0,(D77*N$2/D$2))</f>
-        <v>56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:14">
+      <c r="A78" t="s">
+        <v>27</v>
+      </c>
+      <c r="C78" s="4">
+        <v>660</v>
+      </c>
+      <c r="D78" s="6">
+        <v>140</v>
+      </c>
       <c r="E78" s="1">
         <f xml:space="preserve"> C78/C$2</f>
-        <v>0</v>
+        <v>0.2578125</v>
       </c>
       <c r="F78" s="1">
         <f xml:space="preserve"> D78/D$2</f>
-        <v>0</v>
+        <v>9.7222222222222224E-2</v>
       </c>
       <c r="G78" s="4">
         <f>IF(ISBLANK(C78),0,(C78*G$2/C$2))</f>
-        <v>0</v>
+        <v>990</v>
       </c>
       <c r="H78" s="6">
         <f>IF(ISBLANK(D78),0,(D78*H$2/D$2))</f>
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="J78" s="4">
         <f>IF(ISBLANK(C78),0,(C78*J$2/C$2))</f>
-        <v>0</v>
+        <v>495</v>
       </c>
       <c r="K78" s="6">
         <f>IF(ISBLANK(D78),0,(D78*K$2/D$2))</f>
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="M78" s="4">
         <f>IF(ISBLANK(C78),0,(C78*M$2/C$2))</f>
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="N78" s="6">
         <f>IF(ISBLANK(D78),0,(D78*N$2/D$2))</f>
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="79" spans="1:14">
+      <c r="A79" t="s">
+        <v>28</v>
+      </c>
+      <c r="C79" s="4">
+        <v>560</v>
+      </c>
+      <c r="D79" s="6">
+        <v>46</v>
+      </c>
       <c r="E79" s="1">
         <f xml:space="preserve"> C79/C$2</f>
-        <v>0</v>
+        <v>0.21875</v>
       </c>
       <c r="F79" s="1">
         <f xml:space="preserve"> D79/D$2</f>
-        <v>0</v>
+        <v>3.1944444444444442E-2</v>
       </c>
       <c r="G79" s="4">
         <f>IF(ISBLANK(C79),0,(C79*G$2/C$2))</f>
-        <v>0</v>
+        <v>840</v>
       </c>
       <c r="H79" s="6">
         <f>IF(ISBLANK(D79),0,(D79*H$2/D$2))</f>
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="J79" s="4">
         <f>IF(ISBLANK(C79),0,(C79*J$2/C$2))</f>
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="K79" s="6">
         <f>IF(ISBLANK(D79),0,(D79*K$2/D$2))</f>
-        <v>0</v>
+        <v>34.5</v>
       </c>
       <c r="M79" s="4">
         <f>IF(ISBLANK(C79),0,(C79*M$2/C$2))</f>
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="N79" s="6">
         <f>IF(ISBLANK(D79),0,(D79*N$2/D$2))</f>
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="80" spans="1:14">
-      <c r="A80" t="s">
-        <v>27</v>
-      </c>
-      <c r="C80" s="4">
-        <v>280</v>
-      </c>
-      <c r="D80" s="6">
-        <v>84</v>
-      </c>
       <c r="E80" s="1">
         <f xml:space="preserve"> C80/C$2</f>
-        <v>0.109375</v>
+        <v>0</v>
       </c>
       <c r="F80" s="1">
         <f xml:space="preserve"> D80/D$2</f>
-        <v>5.8333333333333334E-2</v>
+        <v>0</v>
       </c>
       <c r="G80" s="4">
         <f>IF(ISBLANK(C80),0,(C80*G$2/C$2))</f>
-        <v>420</v>
+        <v>0</v>
       </c>
       <c r="H80" s="6">
         <f>IF(ISBLANK(D80),0,(D80*H$2/D$2))</f>
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="J80" s="4">
         <f>IF(ISBLANK(C80),0,(C80*J$2/C$2))</f>
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="K80" s="6">
         <f>IF(ISBLANK(D80),0,(D80*K$2/D$2))</f>
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="M80" s="4">
         <f>IF(ISBLANK(C80),0,(C80*M$2/C$2))</f>
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="N80" s="6">
         <f>IF(ISBLANK(D80),0,(D80*N$2/D$2))</f>
-        <v>42</v>
-      </c>
-    </row>
-    <row r="81" spans="1:14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="5:14">
       <c r="E81" s="1">
         <f xml:space="preserve"> C81/C$2</f>
         <v>0</v>
@@ -2933,93 +2924,75 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:14">
-      <c r="A82" t="s">
-        <v>28</v>
-      </c>
-      <c r="C82" s="4">
-        <v>660</v>
-      </c>
-      <c r="D82" s="6">
-        <v>140</v>
-      </c>
+    <row r="82" spans="5:14">
       <c r="E82" s="1">
         <f xml:space="preserve"> C82/C$2</f>
-        <v>0.2578125</v>
+        <v>0</v>
       </c>
       <c r="F82" s="1">
         <f xml:space="preserve"> D82/D$2</f>
-        <v>9.7222222222222224E-2</v>
+        <v>0</v>
       </c>
       <c r="G82" s="4">
         <f>IF(ISBLANK(C82),0,(C82*G$2/C$2))</f>
-        <v>990</v>
+        <v>0</v>
       </c>
       <c r="H82" s="6">
         <f>IF(ISBLANK(D82),0,(D82*H$2/D$2))</f>
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="J82" s="4">
         <f>IF(ISBLANK(C82),0,(C82*J$2/C$2))</f>
-        <v>495</v>
+        <v>0</v>
       </c>
       <c r="K82" s="6">
         <f>IF(ISBLANK(D82),0,(D82*K$2/D$2))</f>
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="M82" s="4">
         <f>IF(ISBLANK(C82),0,(C82*M$2/C$2))</f>
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="N82" s="6">
         <f>IF(ISBLANK(D82),0,(D82*N$2/D$2))</f>
-        <v>70</v>
-      </c>
-    </row>
-    <row r="83" spans="1:14">
-      <c r="A83" t="s">
-        <v>29</v>
-      </c>
-      <c r="C83" s="4">
-        <v>560</v>
-      </c>
-      <c r="D83" s="6">
-        <v>46</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="5:14">
       <c r="E83" s="1">
         <f xml:space="preserve"> C83/C$2</f>
-        <v>0.21875</v>
+        <v>0</v>
       </c>
       <c r="F83" s="1">
         <f xml:space="preserve"> D83/D$2</f>
-        <v>3.1944444444444442E-2</v>
+        <v>0</v>
       </c>
       <c r="G83" s="4">
         <f>IF(ISBLANK(C83),0,(C83*G$2/C$2))</f>
-        <v>840</v>
+        <v>0</v>
       </c>
       <c r="H83" s="6">
         <f>IF(ISBLANK(D83),0,(D83*H$2/D$2))</f>
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="J83" s="4">
         <f>IF(ISBLANK(C83),0,(C83*J$2/C$2))</f>
-        <v>420</v>
+        <v>0</v>
       </c>
       <c r="K83" s="6">
         <f>IF(ISBLANK(D83),0,(D83*K$2/D$2))</f>
-        <v>34.5</v>
+        <v>0</v>
       </c>
       <c r="M83" s="4">
         <f>IF(ISBLANK(C83),0,(C83*M$2/C$2))</f>
-        <v>280</v>
+        <v>0</v>
       </c>
       <c r="N83" s="6">
         <f>IF(ISBLANK(D83),0,(D83*N$2/D$2))</f>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="84" spans="1:14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="5:14">
       <c r="E84" s="1">
         <f xml:space="preserve"> C84/C$2</f>
         <v>0</v>
@@ -3053,7 +3026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:14">
+    <row r="85" spans="5:14">
       <c r="E85" s="1">
         <f xml:space="preserve"> C85/C$2</f>
         <v>0</v>
@@ -3087,7 +3060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:14">
+    <row r="86" spans="5:14">
       <c r="E86" s="1">
         <f xml:space="preserve"> C86/C$2</f>
         <v>0</v>
@@ -3121,7 +3094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:14">
+    <row r="87" spans="5:14">
       <c r="E87" s="1">
         <f xml:space="preserve"> C87/C$2</f>
         <v>0</v>
@@ -3155,7 +3128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:14">
+    <row r="88" spans="5:14">
       <c r="E88" s="1">
         <f xml:space="preserve"> C88/C$2</f>
         <v>0</v>
@@ -3189,7 +3162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:14">
+    <row r="89" spans="5:14">
       <c r="E89" s="1">
         <f xml:space="preserve"> C89/C$2</f>
         <v>0</v>
@@ -3223,7 +3196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:14">
+    <row r="90" spans="5:14">
       <c r="E90" s="1">
         <f xml:space="preserve"> C90/C$2</f>
         <v>0</v>
@@ -3257,7 +3230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:14">
+    <row r="91" spans="5:14">
       <c r="E91" s="1">
         <f xml:space="preserve"> C91/C$2</f>
         <v>0</v>
@@ -3291,7 +3264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:14">
+    <row r="92" spans="5:14">
       <c r="E92" s="1">
         <f xml:space="preserve"> C92/C$2</f>
         <v>0</v>
@@ -3325,7 +3298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:14">
+    <row r="93" spans="5:14">
       <c r="E93" s="1">
         <f xml:space="preserve"> C93/C$2</f>
         <v>0</v>
@@ -3359,7 +3332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:14">
+    <row r="94" spans="5:14">
       <c r="E94" s="1">
         <f xml:space="preserve"> C94/C$2</f>
         <v>0</v>
@@ -3393,7 +3366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:14">
+    <row r="95" spans="5:14">
       <c r="E95" s="1">
         <f xml:space="preserve"> C95/C$2</f>
         <v>0</v>
@@ -3427,7 +3400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:14">
+    <row r="96" spans="5:14">
       <c r="E96" s="1">
         <f xml:space="preserve"> C96/C$2</f>
         <v>0</v>
@@ -3599,171 +3572,171 @@
     </row>
     <row r="101" spans="5:14">
       <c r="E101" s="1">
-        <f xml:space="preserve"> C101/C$2</f>
+        <f t="shared" ref="E101:E111" si="112" xml:space="preserve"> C101/C$2</f>
         <v>0</v>
       </c>
       <c r="F101" s="1">
-        <f xml:space="preserve"> D101/D$2</f>
+        <f t="shared" ref="F101:F111" si="113" xml:space="preserve"> D101/D$2</f>
         <v>0</v>
       </c>
       <c r="G101" s="4">
-        <f>IF(ISBLANK(C101),0,(C101*G$2/C$2))</f>
+        <f t="shared" ref="G101:G111" si="114">IF(ISBLANK(C101),0,(C101*G$2/C$2))</f>
         <v>0</v>
       </c>
       <c r="H101" s="6">
-        <f>IF(ISBLANK(D101),0,(D101*H$2/D$2))</f>
+        <f t="shared" ref="H101:H111" si="115">IF(ISBLANK(D101),0,(D101*H$2/D$2))</f>
         <v>0</v>
       </c>
       <c r="J101" s="4">
-        <f>IF(ISBLANK(C101),0,(C101*J$2/C$2))</f>
+        <f t="shared" ref="J101:J111" si="116">IF(ISBLANK(C101),0,(C101*J$2/C$2))</f>
         <v>0</v>
       </c>
       <c r="K101" s="6">
-        <f>IF(ISBLANK(D101),0,(D101*K$2/D$2))</f>
+        <f t="shared" ref="K101:K111" si="117">IF(ISBLANK(D101),0,(D101*K$2/D$2))</f>
         <v>0</v>
       </c>
       <c r="M101" s="4">
-        <f>IF(ISBLANK(C101),0,(C101*M$2/C$2))</f>
+        <f t="shared" ref="M101:M111" si="118">IF(ISBLANK(C101),0,(C101*M$2/C$2))</f>
         <v>0</v>
       </c>
       <c r="N101" s="6">
-        <f>IF(ISBLANK(D101),0,(D101*N$2/D$2))</f>
+        <f t="shared" ref="N101:N111" si="119">IF(ISBLANK(D101),0,(D101*N$2/D$2))</f>
         <v>0</v>
       </c>
     </row>
     <row r="102" spans="5:14">
       <c r="E102" s="1">
-        <f xml:space="preserve"> C102/C$2</f>
+        <f t="shared" si="112"/>
         <v>0</v>
       </c>
       <c r="F102" s="1">
-        <f xml:space="preserve"> D102/D$2</f>
+        <f t="shared" si="113"/>
         <v>0</v>
       </c>
       <c r="G102" s="4">
-        <f>IF(ISBLANK(C102),0,(C102*G$2/C$2))</f>
+        <f t="shared" si="114"/>
         <v>0</v>
       </c>
       <c r="H102" s="6">
-        <f>IF(ISBLANK(D102),0,(D102*H$2/D$2))</f>
+        <f t="shared" si="115"/>
         <v>0</v>
       </c>
       <c r="J102" s="4">
-        <f>IF(ISBLANK(C102),0,(C102*J$2/C$2))</f>
+        <f t="shared" si="116"/>
         <v>0</v>
       </c>
       <c r="K102" s="6">
-        <f>IF(ISBLANK(D102),0,(D102*K$2/D$2))</f>
+        <f t="shared" si="117"/>
         <v>0</v>
       </c>
       <c r="M102" s="4">
-        <f>IF(ISBLANK(C102),0,(C102*M$2/C$2))</f>
+        <f t="shared" si="118"/>
         <v>0</v>
       </c>
       <c r="N102" s="6">
-        <f>IF(ISBLANK(D102),0,(D102*N$2/D$2))</f>
+        <f t="shared" si="119"/>
         <v>0</v>
       </c>
     </row>
     <row r="103" spans="5:14">
       <c r="E103" s="1">
-        <f xml:space="preserve"> C103/C$2</f>
+        <f t="shared" si="112"/>
         <v>0</v>
       </c>
       <c r="F103" s="1">
-        <f xml:space="preserve"> D103/D$2</f>
+        <f t="shared" si="113"/>
         <v>0</v>
       </c>
       <c r="G103" s="4">
-        <f>IF(ISBLANK(C103),0,(C103*G$2/C$2))</f>
+        <f t="shared" si="114"/>
         <v>0</v>
       </c>
       <c r="H103" s="6">
-        <f>IF(ISBLANK(D103),0,(D103*H$2/D$2))</f>
+        <f t="shared" si="115"/>
         <v>0</v>
       </c>
       <c r="J103" s="4">
-        <f>IF(ISBLANK(C103),0,(C103*J$2/C$2))</f>
+        <f t="shared" si="116"/>
         <v>0</v>
       </c>
       <c r="K103" s="6">
-        <f>IF(ISBLANK(D103),0,(D103*K$2/D$2))</f>
+        <f t="shared" si="117"/>
         <v>0</v>
       </c>
       <c r="M103" s="4">
-        <f>IF(ISBLANK(C103),0,(C103*M$2/C$2))</f>
+        <f t="shared" si="118"/>
         <v>0</v>
       </c>
       <c r="N103" s="6">
-        <f>IF(ISBLANK(D103),0,(D103*N$2/D$2))</f>
+        <f t="shared" si="119"/>
         <v>0</v>
       </c>
     </row>
     <row r="104" spans="5:14">
       <c r="E104" s="1">
-        <f xml:space="preserve"> C104/C$2</f>
+        <f t="shared" si="112"/>
         <v>0</v>
       </c>
       <c r="F104" s="1">
-        <f xml:space="preserve"> D104/D$2</f>
+        <f t="shared" si="113"/>
         <v>0</v>
       </c>
       <c r="G104" s="4">
-        <f>IF(ISBLANK(C104),0,(C104*G$2/C$2))</f>
+        <f t="shared" si="114"/>
         <v>0</v>
       </c>
       <c r="H104" s="6">
-        <f>IF(ISBLANK(D104),0,(D104*H$2/D$2))</f>
+        <f t="shared" si="115"/>
         <v>0</v>
       </c>
       <c r="J104" s="4">
-        <f>IF(ISBLANK(C104),0,(C104*J$2/C$2))</f>
+        <f t="shared" si="116"/>
         <v>0</v>
       </c>
       <c r="K104" s="6">
-        <f>IF(ISBLANK(D104),0,(D104*K$2/D$2))</f>
+        <f t="shared" si="117"/>
         <v>0</v>
       </c>
       <c r="M104" s="4">
-        <f>IF(ISBLANK(C104),0,(C104*M$2/C$2))</f>
+        <f t="shared" si="118"/>
         <v>0</v>
       </c>
       <c r="N104" s="6">
-        <f>IF(ISBLANK(D104),0,(D104*N$2/D$2))</f>
+        <f t="shared" si="119"/>
         <v>0</v>
       </c>
     </row>
     <row r="105" spans="5:14">
       <c r="E105" s="1">
-        <f t="shared" ref="E105:E115" si="112" xml:space="preserve"> C105/C$2</f>
+        <f t="shared" si="112"/>
         <v>0</v>
       </c>
       <c r="F105" s="1">
-        <f t="shared" ref="F105:F115" si="113" xml:space="preserve"> D105/D$2</f>
+        <f t="shared" si="113"/>
         <v>0</v>
       </c>
       <c r="G105" s="4">
-        <f t="shared" ref="G105:G115" si="114">IF(ISBLANK(C105),0,(C105*G$2/C$2))</f>
+        <f t="shared" si="114"/>
         <v>0</v>
       </c>
       <c r="H105" s="6">
-        <f t="shared" ref="H105:H115" si="115">IF(ISBLANK(D105),0,(D105*H$2/D$2))</f>
+        <f t="shared" si="115"/>
         <v>0</v>
       </c>
       <c r="J105" s="4">
-        <f t="shared" ref="J105:J115" si="116">IF(ISBLANK(C105),0,(C105*J$2/C$2))</f>
+        <f t="shared" si="116"/>
         <v>0</v>
       </c>
       <c r="K105" s="6">
-        <f t="shared" ref="K105:K115" si="117">IF(ISBLANK(D105),0,(D105*K$2/D$2))</f>
+        <f t="shared" si="117"/>
         <v>0</v>
       </c>
       <c r="M105" s="4">
-        <f t="shared" ref="M105:M115" si="118">IF(ISBLANK(C105),0,(C105*M$2/C$2))</f>
+        <f t="shared" si="118"/>
         <v>0</v>
       </c>
       <c r="N105" s="6">
-        <f t="shared" ref="N105:N115" si="119">IF(ISBLANK(D105),0,(D105*N$2/D$2))</f>
+        <f t="shared" si="119"/>
         <v>0</v>
       </c>
     </row>
@@ -3967,142 +3940,6 @@
         <v>0</v>
       </c>
       <c r="N111" s="6">
-        <f t="shared" si="119"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="5:14">
-      <c r="E112" s="1">
-        <f t="shared" si="112"/>
-        <v>0</v>
-      </c>
-      <c r="F112" s="1">
-        <f t="shared" si="113"/>
-        <v>0</v>
-      </c>
-      <c r="G112" s="4">
-        <f t="shared" si="114"/>
-        <v>0</v>
-      </c>
-      <c r="H112" s="6">
-        <f t="shared" si="115"/>
-        <v>0</v>
-      </c>
-      <c r="J112" s="4">
-        <f t="shared" si="116"/>
-        <v>0</v>
-      </c>
-      <c r="K112" s="6">
-        <f t="shared" si="117"/>
-        <v>0</v>
-      </c>
-      <c r="M112" s="4">
-        <f t="shared" si="118"/>
-        <v>0</v>
-      </c>
-      <c r="N112" s="6">
-        <f t="shared" si="119"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="5:14">
-      <c r="E113" s="1">
-        <f t="shared" si="112"/>
-        <v>0</v>
-      </c>
-      <c r="F113" s="1">
-        <f t="shared" si="113"/>
-        <v>0</v>
-      </c>
-      <c r="G113" s="4">
-        <f t="shared" si="114"/>
-        <v>0</v>
-      </c>
-      <c r="H113" s="6">
-        <f t="shared" si="115"/>
-        <v>0</v>
-      </c>
-      <c r="J113" s="4">
-        <f t="shared" si="116"/>
-        <v>0</v>
-      </c>
-      <c r="K113" s="6">
-        <f t="shared" si="117"/>
-        <v>0</v>
-      </c>
-      <c r="M113" s="4">
-        <f t="shared" si="118"/>
-        <v>0</v>
-      </c>
-      <c r="N113" s="6">
-        <f t="shared" si="119"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="5:14">
-      <c r="E114" s="1">
-        <f t="shared" si="112"/>
-        <v>0</v>
-      </c>
-      <c r="F114" s="1">
-        <f t="shared" si="113"/>
-        <v>0</v>
-      </c>
-      <c r="G114" s="4">
-        <f t="shared" si="114"/>
-        <v>0</v>
-      </c>
-      <c r="H114" s="6">
-        <f t="shared" si="115"/>
-        <v>0</v>
-      </c>
-      <c r="J114" s="4">
-        <f t="shared" si="116"/>
-        <v>0</v>
-      </c>
-      <c r="K114" s="6">
-        <f t="shared" si="117"/>
-        <v>0</v>
-      </c>
-      <c r="M114" s="4">
-        <f t="shared" si="118"/>
-        <v>0</v>
-      </c>
-      <c r="N114" s="6">
-        <f t="shared" si="119"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="5:14">
-      <c r="E115" s="1">
-        <f t="shared" si="112"/>
-        <v>0</v>
-      </c>
-      <c r="F115" s="1">
-        <f t="shared" si="113"/>
-        <v>0</v>
-      </c>
-      <c r="G115" s="4">
-        <f t="shared" si="114"/>
-        <v>0</v>
-      </c>
-      <c r="H115" s="6">
-        <f t="shared" si="115"/>
-        <v>0</v>
-      </c>
-      <c r="J115" s="4">
-        <f t="shared" si="116"/>
-        <v>0</v>
-      </c>
-      <c r="K115" s="6">
-        <f t="shared" si="117"/>
-        <v>0</v>
-      </c>
-      <c r="M115" s="4">
-        <f t="shared" si="118"/>
-        <v>0</v>
-      </c>
-      <c r="N115" s="6">
         <f t="shared" si="119"/>
         <v>0</v>
       </c>
@@ -4120,27 +3957,27 @@
   <sheetData>
     <row r="1" spans="1:23">
       <c r="A1" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
       <c r="D1" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
       <c r="G1" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
       <c r="M1" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N1" s="3"/>
       <c r="O1" s="3"/>
@@ -4326,19 +4163,19 @@
     </row>
     <row r="8" spans="1:23">
       <c r="E8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" t="s">
         <v>21</v>
       </c>
-      <c r="G8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H8" t="s">
-        <v>22</v>
-      </c>
       <c r="I8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:23">

--- a/target/classes/com/ratioTable.xlsx
+++ b/target/classes/com/ratioTable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IT\Documents\GitHub\Balatro\src\main\resources\com\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D521942-BA47-4134-9A2E-F3BA3120DFF6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1523D162-3FB6-489F-845C-565FFD912ECB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7890" xr2:uid="{706E2108-D16A-4E70-A675-C3702A172F02}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="48">
   <si>
     <t>Play Button</t>
   </si>
@@ -159,6 +159,18 @@
   <si>
     <t>Cards OverView</t>
   </si>
+  <si>
+    <t>Card Stats</t>
+  </si>
+  <si>
+    <t>Top Buttons</t>
+  </si>
+  <si>
+    <t>Stat Block</t>
+  </si>
+  <si>
+    <t>Stat Column</t>
+  </si>
 </sst>
 </file>
 
@@ -240,9 +252,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="3" applyBorder="1"/>
     <xf numFmtId="9" fontId="1" fillId="3" borderId="0" xfId="3" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="4"/>
@@ -253,6 +262,9 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="2" applyBorder="1"/>
     <xf numFmtId="9" fontId="3" fillId="2" borderId="0" xfId="2" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="20 % - Akzent1" xfId="3" builtinId="30"/>
@@ -571,3376 +583,3502 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AE52DC3-6553-4C6D-A135-8A8C4D8FA77D}">
-  <dimension ref="A1:O111"/>
+  <dimension ref="A1:AE124"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="11.42578125" style="4"/>
-    <col min="4" max="4" width="11.42578125" style="6"/>
+    <col min="3" max="3" width="11.42578125" style="3"/>
+    <col min="4" max="4" width="11.42578125" style="5"/>
     <col min="5" max="6" width="11.42578125" style="1"/>
-    <col min="7" max="7" width="11.42578125" style="5"/>
-    <col min="8" max="8" width="11.42578125" style="8"/>
+    <col min="7" max="7" width="11.42578125" style="4"/>
+    <col min="8" max="8" width="11.42578125" style="7"/>
     <col min="9" max="9" width="11.42578125" style="1"/>
-    <col min="10" max="10" width="11.42578125" style="4"/>
-    <col min="11" max="11" width="11.42578125" style="6"/>
-    <col min="13" max="13" width="11.42578125" style="4"/>
-    <col min="14" max="14" width="11.42578125" style="6"/>
+    <col min="10" max="10" width="11.42578125" style="3"/>
+    <col min="11" max="11" width="11.42578125" style="5"/>
+    <col min="13" max="13" width="11.42578125" style="3"/>
+    <col min="14" max="14" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
-      <c r="C1" s="9" t="s">
+    <row r="1" spans="1:14">
+      <c r="C1" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K1" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M1" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="N1" s="9" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
-      <c r="C2" s="4">
+    <row r="2" spans="1:14">
+      <c r="C2" s="3">
         <v>2560</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="5">
         <v>1440</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G2" s="3">
         <v>3840</v>
       </c>
-      <c r="H2" s="7">
+      <c r="H2" s="6">
         <v>2160</v>
       </c>
-      <c r="J2" s="4">
+      <c r="J2" s="3">
         <v>1920</v>
       </c>
-      <c r="K2" s="6">
+      <c r="K2" s="5">
         <v>1080</v>
       </c>
-      <c r="M2" s="4">
+      <c r="M2" s="3">
         <v>1280</v>
       </c>
-      <c r="N2" s="6">
+      <c r="N2" s="5">
         <v>720</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
-      <c r="A3" s="11" t="s">
+    <row r="3" spans="1:14">
+      <c r="A3" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="11"/>
-      <c r="L3" s="11"/>
-      <c r="M3" s="12"/>
-      <c r="N3" s="11"/>
-      <c r="O3" s="11"/>
-    </row>
-    <row r="4" spans="1:15">
-      <c r="G4" s="4"/>
-      <c r="H4" s="6"/>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="B3" s="10"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="11"/>
+      <c r="N3" s="10"/>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="G4" s="3"/>
+      <c r="H4" s="5"/>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="4">
-        <v>1444</v>
-      </c>
-      <c r="D5" s="6">
-        <v>1090</v>
+        <v>45</v>
+      </c>
+      <c r="C5" s="3">
+        <v>278</v>
+      </c>
+      <c r="D5" s="5">
+        <v>90</v>
       </c>
       <c r="E5" s="1">
         <f xml:space="preserve"> C5/C$2</f>
-        <v>0.56406250000000002</v>
+        <v>0.10859375</v>
       </c>
       <c r="F5" s="1">
         <f xml:space="preserve"> D5/D$2</f>
+        <v>6.25E-2</v>
+      </c>
+      <c r="G5" s="3">
+        <f>IF(ISBLANK(C5),0,(C5*G$2/C$2))</f>
+        <v>417</v>
+      </c>
+      <c r="H5" s="5">
+        <f>IF(ISBLANK(D5),0,(D5*H$2/D$2))</f>
+        <v>135</v>
+      </c>
+      <c r="J5" s="3">
+        <f>IF(ISBLANK(C5),0,(C5*J$2/C$2))</f>
+        <v>208.5</v>
+      </c>
+      <c r="K5" s="5">
+        <f>IF(ISBLANK(D5),0,(D5*K$2/D$2))</f>
+        <v>67.5</v>
+      </c>
+      <c r="M5" s="3">
+        <f>IF(ISBLANK(C5),0,(C5*M$2/C$2))</f>
+        <v>139</v>
+      </c>
+      <c r="N5" s="5">
+        <f>IF(ISBLANK(D5),0,(D5*N$2/D$2))</f>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="G6" s="3"/>
+      <c r="H6" s="5"/>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="3">
+        <v>1444</v>
+      </c>
+      <c r="D7" s="5">
+        <v>1090</v>
+      </c>
+      <c r="E7" s="1">
+        <f xml:space="preserve"> C7/C$2</f>
+        <v>0.56406250000000002</v>
+      </c>
+      <c r="F7" s="1">
+        <f xml:space="preserve"> D7/D$2</f>
         <v>0.75694444444444442</v>
       </c>
-      <c r="G5" s="4">
-        <f>IF(ISBLANK(C5),0,(C5*G$2/C$2))</f>
+      <c r="G7" s="3">
+        <f>IF(ISBLANK(C7),0,(C7*G$2/C$2))</f>
         <v>2166</v>
       </c>
-      <c r="H5" s="6">
-        <f>IF(ISBLANK(D5),0,(D5*H$2/D$2))</f>
+      <c r="H7" s="5">
+        <f>IF(ISBLANK(D7),0,(D7*H$2/D$2))</f>
         <v>1635</v>
       </c>
-      <c r="J5" s="4">
-        <f>IF(ISBLANK(C5),0,(C5*J$2/C$2))</f>
+      <c r="J7" s="3">
+        <f>IF(ISBLANK(C7),0,(C7*J$2/C$2))</f>
         <v>1083</v>
       </c>
-      <c r="K5" s="6">
-        <f>IF(ISBLANK(D5),0,(D5*K$2/D$2))</f>
+      <c r="K7" s="5">
+        <f>IF(ISBLANK(D7),0,(D7*K$2/D$2))</f>
         <v>817.5</v>
       </c>
-      <c r="M5" s="4">
-        <f>IF(ISBLANK(C5),0,(C5*M$2/C$2))</f>
+      <c r="M7" s="3">
+        <f>IF(ISBLANK(C7),0,(C7*M$2/C$2))</f>
         <v>722</v>
       </c>
-      <c r="N5" s="6">
-        <f>IF(ISBLANK(D5),0,(D5*N$2/D$2))</f>
+      <c r="N7" s="5">
+        <f>IF(ISBLANK(D7),0,(D7*N$2/D$2))</f>
         <v>545</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
-      <c r="G6" s="4"/>
-      <c r="H6" s="6"/>
-    </row>
-    <row r="7" spans="1:15">
-      <c r="A7" t="s">
+    <row r="8" spans="1:14">
+      <c r="G8" s="3"/>
+      <c r="H8" s="5"/>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C9" s="3">
         <v>1214</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D9" s="5">
         <v>1216</v>
       </c>
-      <c r="E7" s="1">
-        <f t="shared" ref="E7:E43" si="0" xml:space="preserve"> C7/C$2</f>
+      <c r="E9" s="1">
+        <f t="shared" ref="E9:E13" si="0" xml:space="preserve"> C9/C$2</f>
         <v>0.47421875000000002</v>
       </c>
-      <c r="F7" s="1">
-        <f t="shared" ref="F7:F43" si="1" xml:space="preserve"> D7/D$2</f>
+      <c r="F9" s="1">
+        <f t="shared" ref="F9:F13" si="1" xml:space="preserve"> D9/D$2</f>
         <v>0.84444444444444444</v>
       </c>
-      <c r="G7" s="4">
-        <f t="shared" ref="G7:G43" si="2">IF(ISBLANK(C7),0,(C7*G$2/C$2))</f>
+      <c r="G9" s="3">
+        <f t="shared" ref="G9:G13" si="2">IF(ISBLANK(C9),0,(C9*G$2/C$2))</f>
         <v>1821</v>
       </c>
-      <c r="H7" s="6">
-        <f t="shared" ref="H7:H43" si="3">IF(ISBLANK(D7),0,(D7*H$2/D$2))</f>
+      <c r="H9" s="5">
+        <f t="shared" ref="H9:H13" si="3">IF(ISBLANK(D9),0,(D9*H$2/D$2))</f>
         <v>1824</v>
       </c>
-      <c r="J7" s="4">
-        <f t="shared" ref="J7:J43" si="4">IF(ISBLANK(C7),0,(C7*J$2/C$2))</f>
+      <c r="J9" s="3">
+        <f t="shared" ref="J9:J13" si="4">IF(ISBLANK(C9),0,(C9*J$2/C$2))</f>
         <v>910.5</v>
       </c>
-      <c r="K7" s="6">
-        <f t="shared" ref="K7:K43" si="5">IF(ISBLANK(D7),0,(D7*K$2/D$2))</f>
+      <c r="K9" s="5">
+        <f t="shared" ref="K9:K13" si="5">IF(ISBLANK(D9),0,(D9*K$2/D$2))</f>
         <v>912</v>
       </c>
-      <c r="M7" s="4">
-        <f t="shared" ref="M7:M43" si="6">IF(ISBLANK(C7),0,(C7*M$2/C$2))</f>
+      <c r="M9" s="3">
+        <f t="shared" ref="M9:M13" si="6">IF(ISBLANK(C9),0,(C9*M$2/C$2))</f>
         <v>607</v>
       </c>
-      <c r="N7" s="6">
-        <f t="shared" ref="N7:N43" si="7">IF(ISBLANK(D7),0,(D7*N$2/D$2))</f>
+      <c r="N9" s="5">
+        <f t="shared" ref="N9:N13" si="7">IF(ISBLANK(D9),0,(D9*N$2/D$2))</f>
         <v>608</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
-      <c r="G8" s="4"/>
-      <c r="H8" s="6"/>
-    </row>
-    <row r="9" spans="1:15">
-      <c r="A9" t="s">
+    <row r="10" spans="1:14">
+      <c r="G10" s="3"/>
+      <c r="H10" s="5"/>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C11" s="3">
         <v>1262</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D11" s="5">
         <v>876</v>
       </c>
-      <c r="E9" s="1">
-        <f t="shared" ref="E9" si="8" xml:space="preserve"> C9/C$2</f>
+      <c r="E11" s="1">
+        <f t="shared" ref="E11" si="8" xml:space="preserve"> C11/C$2</f>
         <v>0.49296875000000001</v>
       </c>
-      <c r="F9" s="1">
-        <f t="shared" ref="F9" si="9" xml:space="preserve"> D9/D$2</f>
+      <c r="F11" s="1">
+        <f t="shared" ref="F11" si="9" xml:space="preserve"> D11/D$2</f>
         <v>0.60833333333333328</v>
       </c>
-      <c r="G9" s="4">
-        <f t="shared" ref="G9" si="10">IF(ISBLANK(C9),0,(C9*G$2/C$2))</f>
+      <c r="G11" s="3">
+        <f t="shared" ref="G11" si="10">IF(ISBLANK(C11),0,(C11*G$2/C$2))</f>
         <v>1893</v>
       </c>
-      <c r="H9" s="6">
-        <f t="shared" ref="H9" si="11">IF(ISBLANK(D9),0,(D9*H$2/D$2))</f>
+      <c r="H11" s="5">
+        <f t="shared" ref="H11" si="11">IF(ISBLANK(D11),0,(D11*H$2/D$2))</f>
         <v>1314</v>
       </c>
-      <c r="J9" s="4">
-        <f t="shared" ref="J9" si="12">IF(ISBLANK(C9),0,(C9*J$2/C$2))</f>
+      <c r="J11" s="3">
+        <f t="shared" ref="J11" si="12">IF(ISBLANK(C11),0,(C11*J$2/C$2))</f>
         <v>946.5</v>
       </c>
-      <c r="K9" s="6">
-        <f t="shared" ref="K9" si="13">IF(ISBLANK(D9),0,(D9*K$2/D$2))</f>
+      <c r="K11" s="5">
+        <f t="shared" ref="K11" si="13">IF(ISBLANK(D11),0,(D11*K$2/D$2))</f>
         <v>657</v>
       </c>
-      <c r="M9" s="4">
-        <f t="shared" ref="M9" si="14">IF(ISBLANK(C9),0,(C9*M$2/C$2))</f>
+      <c r="M11" s="3">
+        <f t="shared" ref="M11" si="14">IF(ISBLANK(C11),0,(C11*M$2/C$2))</f>
         <v>631</v>
       </c>
-      <c r="N9" s="6">
-        <f t="shared" ref="N9" si="15">IF(ISBLANK(D9),0,(D9*N$2/D$2))</f>
+      <c r="N11" s="5">
+        <f t="shared" ref="N11" si="15">IF(ISBLANK(D11),0,(D11*N$2/D$2))</f>
         <v>438</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
-      <c r="G10" s="4"/>
-      <c r="H10" s="6"/>
-    </row>
-    <row r="11" spans="1:15">
-      <c r="A11" t="s">
+    <row r="12" spans="1:14">
+      <c r="G12" s="3"/>
+      <c r="H12" s="5"/>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C13" s="3">
         <v>1652</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D13" s="5">
         <v>840</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E13" s="1">
         <f t="shared" si="0"/>
         <v>0.64531249999999996</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F13" s="1">
         <f t="shared" si="1"/>
         <v>0.58333333333333337</v>
       </c>
-      <c r="G11" s="4">
+      <c r="G13" s="3">
         <f t="shared" si="2"/>
         <v>2478</v>
       </c>
-      <c r="H11" s="6">
+      <c r="H13" s="5">
         <f t="shared" si="3"/>
         <v>1260</v>
       </c>
-      <c r="J11" s="4">
+      <c r="J13" s="3">
         <f t="shared" si="4"/>
         <v>1239</v>
       </c>
-      <c r="K11" s="6">
+      <c r="K13" s="5">
         <f t="shared" si="5"/>
         <v>630</v>
       </c>
-      <c r="M11" s="4">
+      <c r="M13" s="3">
         <f t="shared" si="6"/>
         <v>826</v>
       </c>
-      <c r="N11" s="6">
+      <c r="N13" s="5">
         <f t="shared" si="7"/>
         <v>420</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
-      <c r="G12" s="4"/>
-      <c r="H12" s="6"/>
-    </row>
-    <row r="13" spans="1:15">
-      <c r="A13" t="s">
+    <row r="14" spans="1:14">
+      <c r="G14" s="3"/>
+      <c r="H14" s="5"/>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C15" s="3">
         <v>1294</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D15" s="5">
         <v>964</v>
       </c>
-      <c r="E13" s="1">
-        <f t="shared" ref="E13" si="16" xml:space="preserve"> C13/C$2</f>
+      <c r="E15" s="1">
+        <f t="shared" ref="E15" si="16" xml:space="preserve"> C15/C$2</f>
         <v>0.50546875000000002</v>
       </c>
-      <c r="F13" s="1">
-        <f t="shared" ref="F13" si="17" xml:space="preserve"> D13/D$2</f>
+      <c r="F15" s="1">
+        <f t="shared" ref="F15" si="17" xml:space="preserve"> D15/D$2</f>
         <v>0.6694444444444444</v>
       </c>
-      <c r="G13" s="4">
-        <f t="shared" ref="G13" si="18">IF(ISBLANK(C13),0,(C13*G$2/C$2))</f>
+      <c r="G15" s="3">
+        <f t="shared" ref="G15" si="18">IF(ISBLANK(C15),0,(C15*G$2/C$2))</f>
         <v>1941</v>
       </c>
-      <c r="H13" s="6">
-        <f t="shared" ref="H13" si="19">IF(ISBLANK(D13),0,(D13*H$2/D$2))</f>
+      <c r="H15" s="5">
+        <f t="shared" ref="H15" si="19">IF(ISBLANK(D15),0,(D15*H$2/D$2))</f>
         <v>1446</v>
       </c>
-      <c r="J13" s="4">
-        <f t="shared" ref="J13" si="20">IF(ISBLANK(C13),0,(C13*J$2/C$2))</f>
+      <c r="J15" s="3">
+        <f t="shared" ref="J15" si="20">IF(ISBLANK(C15),0,(C15*J$2/C$2))</f>
         <v>970.5</v>
       </c>
-      <c r="K13" s="6">
-        <f t="shared" ref="K13" si="21">IF(ISBLANK(D13),0,(D13*K$2/D$2))</f>
+      <c r="K15" s="5">
+        <f t="shared" ref="K15" si="21">IF(ISBLANK(D15),0,(D15*K$2/D$2))</f>
         <v>723</v>
       </c>
-      <c r="M13" s="4">
-        <f t="shared" ref="M13" si="22">IF(ISBLANK(C13),0,(C13*M$2/C$2))</f>
+      <c r="M15" s="3">
+        <f t="shared" ref="M15" si="22">IF(ISBLANK(C15),0,(C15*M$2/C$2))</f>
         <v>647</v>
       </c>
-      <c r="N13" s="6">
-        <f t="shared" ref="N13" si="23">IF(ISBLANK(D13),0,(D13*N$2/D$2))</f>
+      <c r="N15" s="5">
+        <f t="shared" ref="N15" si="23">IF(ISBLANK(D15),0,(D15*N$2/D$2))</f>
         <v>482</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
-      <c r="G14" s="4"/>
-      <c r="H14" s="6"/>
-    </row>
-    <row r="15" spans="1:15">
-      <c r="A15" t="s">
+    <row r="16" spans="1:14">
+      <c r="G16" s="3"/>
+      <c r="H16" s="5"/>
+    </row>
+    <row r="17" spans="1:31">
+      <c r="A17" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C17" s="3">
         <v>2148</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D17" s="5">
         <v>1248</v>
       </c>
-      <c r="E15" s="1">
-        <f t="shared" ref="E15" si="24" xml:space="preserve"> C15/C$2</f>
+      <c r="E17" s="1">
+        <f t="shared" ref="E17" si="24" xml:space="preserve"> C17/C$2</f>
         <v>0.83906250000000004</v>
       </c>
-      <c r="F15" s="1">
-        <f t="shared" ref="F15" si="25" xml:space="preserve"> D15/D$2</f>
+      <c r="F17" s="1">
+        <f t="shared" ref="F17" si="25" xml:space="preserve"> D17/D$2</f>
         <v>0.8666666666666667</v>
       </c>
-      <c r="G15" s="4">
-        <f t="shared" ref="G15" si="26">IF(ISBLANK(C15),0,(C15*G$2/C$2))</f>
+      <c r="G17" s="3">
+        <f t="shared" ref="G17" si="26">IF(ISBLANK(C17),0,(C17*G$2/C$2))</f>
         <v>3222</v>
       </c>
-      <c r="H15" s="6">
-        <f t="shared" ref="H15" si="27">IF(ISBLANK(D15),0,(D15*H$2/D$2))</f>
+      <c r="H17" s="5">
+        <f t="shared" ref="H17" si="27">IF(ISBLANK(D17),0,(D17*H$2/D$2))</f>
         <v>1872</v>
       </c>
-      <c r="J15" s="4">
-        <f t="shared" ref="J15" si="28">IF(ISBLANK(C15),0,(C15*J$2/C$2))</f>
+      <c r="J17" s="3">
+        <f t="shared" ref="J17" si="28">IF(ISBLANK(C17),0,(C17*J$2/C$2))</f>
         <v>1611</v>
       </c>
-      <c r="K15" s="6">
-        <f t="shared" ref="K15" si="29">IF(ISBLANK(D15),0,(D15*K$2/D$2))</f>
+      <c r="K17" s="5">
+        <f t="shared" ref="K17" si="29">IF(ISBLANK(D17),0,(D17*K$2/D$2))</f>
         <v>936</v>
       </c>
-      <c r="M15" s="4">
-        <f t="shared" ref="M15" si="30">IF(ISBLANK(C15),0,(C15*M$2/C$2))</f>
+      <c r="M17" s="3">
+        <f t="shared" ref="M17" si="30">IF(ISBLANK(C17),0,(C17*M$2/C$2))</f>
         <v>1074</v>
       </c>
-      <c r="N15" s="6">
-        <f t="shared" ref="N15" si="31">IF(ISBLANK(D15),0,(D15*N$2/D$2))</f>
+      <c r="N17" s="5">
+        <f t="shared" ref="N17" si="31">IF(ISBLANK(D17),0,(D17*N$2/D$2))</f>
         <v>624</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
-      <c r="G16" s="4"/>
-      <c r="H16" s="6"/>
-    </row>
-    <row r="17" spans="1:14">
-      <c r="A17" t="s">
+    <row r="18" spans="1:31">
+      <c r="G18" s="3"/>
+      <c r="H18" s="5"/>
+    </row>
+    <row r="19" spans="1:31">
+      <c r="A19" t="s">
         <v>37</v>
       </c>
-      <c r="C17" s="4">
+      <c r="C19" s="3">
         <v>1444</v>
       </c>
-      <c r="D17" s="6">
+      <c r="D19" s="5">
         <v>1192</v>
       </c>
-      <c r="E17" s="1">
-        <f t="shared" ref="E17" si="32" xml:space="preserve"> C17/C$2</f>
+      <c r="E19" s="1">
+        <f t="shared" ref="E19" si="32" xml:space="preserve"> C19/C$2</f>
         <v>0.56406250000000002</v>
       </c>
-      <c r="F17" s="1">
-        <f t="shared" ref="F17" si="33" xml:space="preserve"> D17/D$2</f>
+      <c r="F19" s="1">
+        <f t="shared" ref="F19" si="33" xml:space="preserve"> D19/D$2</f>
         <v>0.82777777777777772</v>
       </c>
-      <c r="G17" s="4">
-        <f t="shared" ref="G17" si="34">IF(ISBLANK(C17),0,(C17*G$2/C$2))</f>
+      <c r="G19" s="3">
+        <f t="shared" ref="G19" si="34">IF(ISBLANK(C19),0,(C19*G$2/C$2))</f>
         <v>2166</v>
       </c>
-      <c r="H17" s="6">
-        <f t="shared" ref="H17" si="35">IF(ISBLANK(D17),0,(D17*H$2/D$2))</f>
+      <c r="H19" s="5">
+        <f t="shared" ref="H19" si="35">IF(ISBLANK(D19),0,(D19*H$2/D$2))</f>
         <v>1788</v>
       </c>
-      <c r="J17" s="4">
-        <f t="shared" ref="J17" si="36">IF(ISBLANK(C17),0,(C17*J$2/C$2))</f>
+      <c r="J19" s="3">
+        <f t="shared" ref="J19" si="36">IF(ISBLANK(C19),0,(C19*J$2/C$2))</f>
         <v>1083</v>
       </c>
-      <c r="K17" s="6">
-        <f t="shared" ref="K17" si="37">IF(ISBLANK(D17),0,(D17*K$2/D$2))</f>
+      <c r="K19" s="5">
+        <f t="shared" ref="K19" si="37">IF(ISBLANK(D19),0,(D19*K$2/D$2))</f>
         <v>894</v>
       </c>
-      <c r="M17" s="4">
-        <f t="shared" ref="M17" si="38">IF(ISBLANK(C17),0,(C17*M$2/C$2))</f>
+      <c r="M19" s="3">
+        <f t="shared" ref="M19" si="38">IF(ISBLANK(C19),0,(C19*M$2/C$2))</f>
         <v>722</v>
       </c>
-      <c r="N17" s="6">
-        <f t="shared" ref="N17" si="39">IF(ISBLANK(D17),0,(D17*N$2/D$2))</f>
+      <c r="N19" s="5">
+        <f t="shared" ref="N19" si="39">IF(ISBLANK(D19),0,(D19*N$2/D$2))</f>
         <v>596</v>
       </c>
     </row>
-    <row r="18" spans="1:14">
-      <c r="G18" s="4"/>
-      <c r="H18" s="6"/>
-    </row>
-    <row r="19" spans="1:14">
-      <c r="A19" t="s">
+    <row r="20" spans="1:31">
+      <c r="G20" s="3"/>
+      <c r="H20" s="5"/>
+    </row>
+    <row r="21" spans="1:31">
+      <c r="A21" t="s">
         <v>38</v>
       </c>
-      <c r="C19" s="4">
+      <c r="C21" s="3">
         <v>824</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D21" s="5">
         <v>892</v>
       </c>
-      <c r="E19" s="1">
-        <f t="shared" ref="E19" si="40" xml:space="preserve"> C19/C$2</f>
+      <c r="E21" s="1">
+        <f t="shared" ref="E21" si="40" xml:space="preserve"> C21/C$2</f>
         <v>0.32187500000000002</v>
       </c>
-      <c r="F19" s="1">
-        <f t="shared" ref="F19" si="41" xml:space="preserve"> D19/D$2</f>
+      <c r="F21" s="1">
+        <f t="shared" ref="F21" si="41" xml:space="preserve"> D21/D$2</f>
         <v>0.61944444444444446</v>
       </c>
-      <c r="G19" s="4">
-        <f t="shared" ref="G19" si="42">IF(ISBLANK(C19),0,(C19*G$2/C$2))</f>
+      <c r="G21" s="3">
+        <f t="shared" ref="G21" si="42">IF(ISBLANK(C21),0,(C21*G$2/C$2))</f>
         <v>1236</v>
       </c>
-      <c r="H19" s="6">
-        <f t="shared" ref="H19" si="43">IF(ISBLANK(D19),0,(D19*H$2/D$2))</f>
+      <c r="H21" s="5">
+        <f t="shared" ref="H21" si="43">IF(ISBLANK(D21),0,(D21*H$2/D$2))</f>
         <v>1338</v>
       </c>
-      <c r="J19" s="4">
-        <f t="shared" ref="J19" si="44">IF(ISBLANK(C19),0,(C19*J$2/C$2))</f>
+      <c r="J21" s="3">
+        <f t="shared" ref="J21" si="44">IF(ISBLANK(C21),0,(C21*J$2/C$2))</f>
         <v>618</v>
       </c>
-      <c r="K19" s="6">
-        <f t="shared" ref="K19" si="45">IF(ISBLANK(D19),0,(D19*K$2/D$2))</f>
+      <c r="K21" s="5">
+        <f t="shared" ref="K21" si="45">IF(ISBLANK(D21),0,(D21*K$2/D$2))</f>
         <v>669</v>
       </c>
-      <c r="M19" s="4">
-        <f t="shared" ref="M19" si="46">IF(ISBLANK(C19),0,(C19*M$2/C$2))</f>
+      <c r="M21" s="3">
+        <f t="shared" ref="M21" si="46">IF(ISBLANK(C21),0,(C21*M$2/C$2))</f>
         <v>412</v>
       </c>
-      <c r="N19" s="6">
-        <f t="shared" ref="N19" si="47">IF(ISBLANK(D19),0,(D19*N$2/D$2))</f>
+      <c r="N21" s="5">
+        <f t="shared" ref="N21" si="47">IF(ISBLANK(D21),0,(D21*N$2/D$2))</f>
         <v>446</v>
       </c>
     </row>
-    <row r="20" spans="1:14">
-      <c r="G20" s="4"/>
-      <c r="H20" s="6"/>
-    </row>
-    <row r="21" spans="1:14">
-      <c r="A21" t="s">
+    <row r="22" spans="1:31">
+      <c r="G22" s="3"/>
+      <c r="H22" s="5"/>
+    </row>
+    <row r="23" spans="1:31">
+      <c r="A23" t="s">
         <v>39</v>
       </c>
-      <c r="C21" s="4">
+      <c r="C23" s="3">
         <v>1914</v>
       </c>
-      <c r="D21" s="6">
+      <c r="D23" s="5">
         <v>974</v>
       </c>
-      <c r="E21" s="1">
-        <f t="shared" ref="E21" si="48" xml:space="preserve"> C21/C$2</f>
+      <c r="E23" s="1">
+        <f t="shared" ref="E23" si="48" xml:space="preserve"> C23/C$2</f>
         <v>0.74765625000000002</v>
       </c>
-      <c r="F21" s="1">
-        <f t="shared" ref="F21" si="49" xml:space="preserve"> D21/D$2</f>
+      <c r="F23" s="1">
+        <f t="shared" ref="F23" si="49" xml:space="preserve"> D23/D$2</f>
         <v>0.67638888888888893</v>
       </c>
-      <c r="G21" s="4">
-        <f t="shared" ref="G21" si="50">IF(ISBLANK(C21),0,(C21*G$2/C$2))</f>
+      <c r="G23" s="3">
+        <f t="shared" ref="G23" si="50">IF(ISBLANK(C23),0,(C23*G$2/C$2))</f>
         <v>2871</v>
       </c>
-      <c r="H21" s="6">
-        <f t="shared" ref="H21" si="51">IF(ISBLANK(D21),0,(D21*H$2/D$2))</f>
+      <c r="H23" s="5">
+        <f t="shared" ref="H23" si="51">IF(ISBLANK(D23),0,(D23*H$2/D$2))</f>
         <v>1461</v>
       </c>
-      <c r="J21" s="4">
-        <f t="shared" ref="J21" si="52">IF(ISBLANK(C21),0,(C21*J$2/C$2))</f>
+      <c r="J23" s="3">
+        <f t="shared" ref="J23" si="52">IF(ISBLANK(C23),0,(C23*J$2/C$2))</f>
         <v>1435.5</v>
       </c>
-      <c r="K21" s="6">
-        <f t="shared" ref="K21" si="53">IF(ISBLANK(D21),0,(D21*K$2/D$2))</f>
+      <c r="K23" s="5">
+        <f t="shared" ref="K23" si="53">IF(ISBLANK(D23),0,(D23*K$2/D$2))</f>
         <v>730.5</v>
       </c>
-      <c r="M21" s="4">
-        <f t="shared" ref="M21" si="54">IF(ISBLANK(C21),0,(C21*M$2/C$2))</f>
+      <c r="M23" s="3">
+        <f t="shared" ref="M23" si="54">IF(ISBLANK(C23),0,(C23*M$2/C$2))</f>
         <v>957</v>
       </c>
-      <c r="N21" s="6">
-        <f t="shared" ref="N21" si="55">IF(ISBLANK(D21),0,(D21*N$2/D$2))</f>
+      <c r="N23" s="5">
+        <f t="shared" ref="N23" si="55">IF(ISBLANK(D23),0,(D23*N$2/D$2))</f>
         <v>487</v>
       </c>
     </row>
-    <row r="22" spans="1:14">
-      <c r="G22" s="4"/>
-      <c r="H22" s="6"/>
-    </row>
-    <row r="23" spans="1:14">
-      <c r="A23" t="s">
+    <row r="24" spans="1:31">
+      <c r="G24" s="3"/>
+      <c r="H24" s="5"/>
+    </row>
+    <row r="25" spans="1:31">
+      <c r="A25" t="s">
         <v>40</v>
       </c>
-      <c r="C23" s="4">
+      <c r="C25" s="3">
         <v>2038</v>
       </c>
-      <c r="D23" s="6">
+      <c r="D25" s="5">
         <v>1194</v>
       </c>
-      <c r="E23" s="1">
-        <f t="shared" ref="E23" si="56" xml:space="preserve"> C23/C$2</f>
+      <c r="E25" s="1">
+        <f t="shared" ref="E25" si="56" xml:space="preserve"> C25/C$2</f>
         <v>0.79609375000000004</v>
       </c>
-      <c r="F23" s="1">
-        <f t="shared" ref="F23" si="57" xml:space="preserve"> D23/D$2</f>
+      <c r="F25" s="1">
+        <f t="shared" ref="F25" si="57" xml:space="preserve"> D25/D$2</f>
         <v>0.82916666666666672</v>
       </c>
-      <c r="G23" s="4">
-        <f t="shared" ref="G23" si="58">IF(ISBLANK(C23),0,(C23*G$2/C$2))</f>
+      <c r="G25" s="3">
+        <f t="shared" ref="G25" si="58">IF(ISBLANK(C25),0,(C25*G$2/C$2))</f>
         <v>3057</v>
       </c>
-      <c r="H23" s="6">
-        <f t="shared" ref="H23" si="59">IF(ISBLANK(D23),0,(D23*H$2/D$2))</f>
+      <c r="H25" s="5">
+        <f t="shared" ref="H25" si="59">IF(ISBLANK(D25),0,(D25*H$2/D$2))</f>
         <v>1791</v>
       </c>
-      <c r="J23" s="4">
-        <f t="shared" ref="J23" si="60">IF(ISBLANK(C23),0,(C23*J$2/C$2))</f>
+      <c r="J25" s="3">
+        <f t="shared" ref="J25" si="60">IF(ISBLANK(C25),0,(C25*J$2/C$2))</f>
         <v>1528.5</v>
       </c>
-      <c r="K23" s="6">
-        <f t="shared" ref="K23" si="61">IF(ISBLANK(D23),0,(D23*K$2/D$2))</f>
+      <c r="K25" s="5">
+        <f t="shared" ref="K25" si="61">IF(ISBLANK(D25),0,(D25*K$2/D$2))</f>
         <v>895.5</v>
       </c>
-      <c r="M23" s="4">
-        <f t="shared" ref="M23" si="62">IF(ISBLANK(C23),0,(C23*M$2/C$2))</f>
+      <c r="M25" s="3">
+        <f t="shared" ref="M25" si="62">IF(ISBLANK(C25),0,(C25*M$2/C$2))</f>
         <v>1019</v>
       </c>
-      <c r="N23" s="6">
-        <f t="shared" ref="N23" si="63">IF(ISBLANK(D23),0,(D23*N$2/D$2))</f>
+      <c r="N25" s="5">
+        <f t="shared" ref="N25" si="63">IF(ISBLANK(D25),0,(D25*N$2/D$2))</f>
         <v>597</v>
       </c>
     </row>
-    <row r="24" spans="1:14">
-      <c r="G24" s="4"/>
-      <c r="H24" s="6"/>
-    </row>
-    <row r="25" spans="1:14">
-      <c r="E25" s="1">
-        <f t="shared" ref="E25" si="64" xml:space="preserve"> C25/C$2</f>
-        <v>0</v>
-      </c>
-      <c r="F25" s="1">
-        <f t="shared" ref="F25" si="65" xml:space="preserve"> D25/D$2</f>
-        <v>0</v>
-      </c>
-      <c r="G25" s="4">
-        <f t="shared" ref="G25" si="66">IF(ISBLANK(C25),0,(C25*G$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="6">
-        <f t="shared" ref="H25" si="67">IF(ISBLANK(D25),0,(D25*H$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="J25" s="4">
-        <f t="shared" ref="J25" si="68">IF(ISBLANK(C25),0,(C25*J$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="K25" s="6">
-        <f t="shared" ref="K25" si="69">IF(ISBLANK(D25),0,(D25*K$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="M25" s="4">
-        <f t="shared" ref="M25" si="70">IF(ISBLANK(C25),0,(C25*M$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="N25" s="6">
-        <f t="shared" ref="N25" si="71">IF(ISBLANK(D25),0,(D25*N$2/D$2))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14">
-      <c r="G26" s="4"/>
-      <c r="H26" s="6"/>
-    </row>
-    <row r="27" spans="1:14" s="11" customFormat="1">
-      <c r="A27" s="11" t="s">
+    <row r="26" spans="1:31">
+      <c r="G26" s="3"/>
+      <c r="H26" s="5"/>
+    </row>
+    <row r="27" spans="1:31" s="10" customFormat="1">
+      <c r="A27"/>
+      <c r="B27"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="1">
+        <f t="shared" ref="E27" si="64" xml:space="preserve"> C27/C$2</f>
+        <v>0</v>
+      </c>
+      <c r="F27" s="1">
+        <f t="shared" ref="F27" si="65" xml:space="preserve"> D27/D$2</f>
+        <v>0</v>
+      </c>
+      <c r="G27" s="3">
+        <f t="shared" ref="G27" si="66">IF(ISBLANK(C27),0,(C27*G$2/C$2))</f>
+        <v>0</v>
+      </c>
+      <c r="H27" s="5">
+        <f t="shared" ref="H27" si="67">IF(ISBLANK(D27),0,(D27*H$2/D$2))</f>
+        <v>0</v>
+      </c>
+      <c r="I27" s="1"/>
+      <c r="J27" s="3">
+        <f t="shared" ref="J27" si="68">IF(ISBLANK(C27),0,(C27*J$2/C$2))</f>
+        <v>0</v>
+      </c>
+      <c r="K27" s="5">
+        <f t="shared" ref="K27" si="69">IF(ISBLANK(D27),0,(D27*K$2/D$2))</f>
+        <v>0</v>
+      </c>
+      <c r="L27"/>
+      <c r="M27" s="3">
+        <f t="shared" ref="M27" si="70">IF(ISBLANK(C27),0,(C27*M$2/C$2))</f>
+        <v>0</v>
+      </c>
+      <c r="N27" s="5">
+        <f t="shared" ref="N27" si="71">IF(ISBLANK(D27),0,(D27*N$2/D$2))</f>
+        <v>0</v>
+      </c>
+      <c r="O27"/>
+      <c r="P27"/>
+      <c r="Q27"/>
+      <c r="R27"/>
+      <c r="S27"/>
+      <c r="T27"/>
+      <c r="U27"/>
+      <c r="V27"/>
+      <c r="W27"/>
+      <c r="X27"/>
+      <c r="Y27"/>
+      <c r="Z27"/>
+      <c r="AA27"/>
+      <c r="AB27"/>
+      <c r="AC27"/>
+      <c r="AD27"/>
+      <c r="AE27"/>
+    </row>
+    <row r="28" spans="1:31">
+      <c r="G28" s="3"/>
+      <c r="H28" s="5"/>
+    </row>
+    <row r="29" spans="1:31">
+      <c r="A29" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="C27" s="12"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="12"/>
-      <c r="I27" s="13"/>
-      <c r="J27" s="12"/>
-      <c r="M27" s="12"/>
-    </row>
-    <row r="28" spans="1:14">
-      <c r="G28" s="4"/>
-      <c r="H28" s="6"/>
-    </row>
-    <row r="29" spans="1:14">
-      <c r="A29" t="s">
+      <c r="B29" s="10"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="10"/>
+      <c r="I29" s="12"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="10"/>
+      <c r="L29" s="10"/>
+      <c r="M29" s="11"/>
+      <c r="N29" s="10"/>
+    </row>
+    <row r="30" spans="1:31">
+      <c r="G30" s="3"/>
+      <c r="H30" s="5"/>
+    </row>
+    <row r="31" spans="1:31">
+      <c r="A31" t="s">
         <v>9</v>
       </c>
-      <c r="C29" s="4">
+      <c r="C31" s="3">
         <v>572</v>
       </c>
-      <c r="D29" s="6">
+      <c r="D31" s="5">
         <v>1440</v>
       </c>
-      <c r="E29" s="1">
-        <f t="shared" ref="E29" si="72" xml:space="preserve"> C29/C$2</f>
+      <c r="E31" s="1">
+        <f t="shared" ref="E31" si="72" xml:space="preserve"> C31/C$2</f>
         <v>0.22343750000000001</v>
       </c>
-      <c r="F29" s="1">
-        <f t="shared" ref="F29" si="73" xml:space="preserve"> D29/D$2</f>
+      <c r="F31" s="1">
+        <f t="shared" ref="F31" si="73" xml:space="preserve"> D31/D$2</f>
         <v>1</v>
       </c>
-      <c r="G29" s="4">
-        <f t="shared" ref="G29" si="74">IF(ISBLANK(C29),0,(C29*G$2/C$2))</f>
+      <c r="G31" s="3">
+        <f t="shared" ref="G31" si="74">IF(ISBLANK(C31),0,(C31*G$2/C$2))</f>
         <v>858</v>
       </c>
-      <c r="H29" s="6">
-        <f t="shared" ref="H29" si="75">IF(ISBLANK(D29),0,(D29*H$2/D$2))</f>
+      <c r="H31" s="5">
+        <f t="shared" ref="H31" si="75">IF(ISBLANK(D31),0,(D31*H$2/D$2))</f>
         <v>2160</v>
       </c>
-      <c r="J29" s="4">
-        <f t="shared" ref="J29" si="76">IF(ISBLANK(C29),0,(C29*J$2/C$2))</f>
+      <c r="J31" s="3">
+        <f t="shared" ref="J31" si="76">IF(ISBLANK(C31),0,(C31*J$2/C$2))</f>
         <v>429</v>
       </c>
-      <c r="K29" s="6">
-        <f t="shared" ref="K29" si="77">IF(ISBLANK(D29),0,(D29*K$2/D$2))</f>
+      <c r="K31" s="5">
+        <f t="shared" ref="K31" si="77">IF(ISBLANK(D31),0,(D31*K$2/D$2))</f>
         <v>1080</v>
       </c>
-      <c r="M29" s="4">
-        <f t="shared" ref="M29" si="78">IF(ISBLANK(C29),0,(C29*M$2/C$2))</f>
+      <c r="M31" s="3">
+        <f t="shared" ref="M31" si="78">IF(ISBLANK(C31),0,(C31*M$2/C$2))</f>
         <v>286</v>
       </c>
-      <c r="N29" s="6">
-        <f t="shared" ref="N29" si="79">IF(ISBLANK(D29),0,(D29*N$2/D$2))</f>
+      <c r="N31" s="5">
+        <f t="shared" ref="N31" si="79">IF(ISBLANK(D31),0,(D31*N$2/D$2))</f>
         <v>720</v>
       </c>
     </row>
-    <row r="30" spans="1:14">
-      <c r="G30" s="4"/>
-      <c r="H30" s="6"/>
-    </row>
-    <row r="31" spans="1:14">
-      <c r="A31" t="s">
+    <row r="32" spans="1:31">
+      <c r="G32" s="3"/>
+      <c r="H32" s="5"/>
+    </row>
+    <row r="33" spans="1:31">
+      <c r="A33" t="s">
         <v>42</v>
       </c>
-      <c r="C31" s="4">
+      <c r="C33" s="3">
         <v>220</v>
       </c>
-      <c r="D31" s="6">
+      <c r="D33" s="5">
         <v>292</v>
       </c>
-      <c r="E31" s="1">
-        <f t="shared" ref="E31" si="80" xml:space="preserve"> C31/C$2</f>
+      <c r="E33" s="1">
+        <f t="shared" ref="E33" si="80" xml:space="preserve"> C33/C$2</f>
         <v>8.59375E-2</v>
       </c>
-      <c r="F31" s="1">
-        <f t="shared" ref="F31" si="81" xml:space="preserve"> D31/D$2</f>
+      <c r="F33" s="1">
+        <f t="shared" ref="F33" si="81" xml:space="preserve"> D33/D$2</f>
         <v>0.20277777777777778</v>
       </c>
-      <c r="G31" s="4">
-        <f t="shared" ref="G31" si="82">IF(ISBLANK(C31),0,(C31*G$2/C$2))</f>
+      <c r="G33" s="3">
+        <f t="shared" ref="G33" si="82">IF(ISBLANK(C33),0,(C33*G$2/C$2))</f>
         <v>330</v>
       </c>
-      <c r="H31" s="6">
-        <f t="shared" ref="H31" si="83">IF(ISBLANK(D31),0,(D31*H$2/D$2))</f>
+      <c r="H33" s="5">
+        <f t="shared" ref="H33" si="83">IF(ISBLANK(D33),0,(D33*H$2/D$2))</f>
         <v>438</v>
       </c>
-      <c r="J31" s="4">
-        <f t="shared" ref="J31" si="84">IF(ISBLANK(C31),0,(C31*J$2/C$2))</f>
+      <c r="J33" s="3">
+        <f t="shared" ref="J33" si="84">IF(ISBLANK(C33),0,(C33*J$2/C$2))</f>
         <v>165</v>
       </c>
-      <c r="K31" s="6">
-        <f t="shared" ref="K31" si="85">IF(ISBLANK(D31),0,(D31*K$2/D$2))</f>
+      <c r="K33" s="5">
+        <f t="shared" ref="K33" si="85">IF(ISBLANK(D33),0,(D33*K$2/D$2))</f>
         <v>219</v>
       </c>
-      <c r="M31" s="4">
-        <f t="shared" ref="M31" si="86">IF(ISBLANK(C31),0,(C31*M$2/C$2))</f>
+      <c r="M33" s="3">
+        <f t="shared" ref="M33" si="86">IF(ISBLANK(C33),0,(C33*M$2/C$2))</f>
         <v>110</v>
       </c>
-      <c r="N31" s="6">
-        <f t="shared" ref="N31" si="87">IF(ISBLANK(D31),0,(D31*N$2/D$2))</f>
+      <c r="N33" s="5">
+        <f t="shared" ref="N33" si="87">IF(ISBLANK(D33),0,(D33*N$2/D$2))</f>
         <v>146</v>
       </c>
     </row>
-    <row r="32" spans="1:14">
-      <c r="G32" s="4"/>
-      <c r="H32" s="6"/>
-    </row>
-    <row r="33" spans="1:14">
-      <c r="A33" t="s">
+    <row r="34" spans="1:31">
+      <c r="G34" s="3"/>
+      <c r="H34" s="5"/>
+    </row>
+    <row r="35" spans="1:31">
+      <c r="A35" t="s">
         <v>43</v>
       </c>
-      <c r="C33" s="4">
+      <c r="C35" s="3">
         <v>140</v>
       </c>
-      <c r="D33" s="6">
+      <c r="D35" s="5">
         <v>200</v>
       </c>
-      <c r="E33" s="1">
-        <f t="shared" ref="E33" si="88" xml:space="preserve"> C33/C$2</f>
+      <c r="E35" s="1">
+        <f t="shared" ref="E35" si="88" xml:space="preserve"> C35/C$2</f>
         <v>5.46875E-2</v>
       </c>
-      <c r="F33" s="1">
-        <f t="shared" ref="F33" si="89" xml:space="preserve"> D33/D$2</f>
+      <c r="F35" s="1">
+        <f t="shared" ref="F35" si="89" xml:space="preserve"> D35/D$2</f>
         <v>0.1388888888888889</v>
       </c>
-      <c r="G33" s="4">
-        <f t="shared" ref="G33" si="90">IF(ISBLANK(C33),0,(C33*G$2/C$2))</f>
+      <c r="G35" s="3">
+        <f t="shared" ref="G35" si="90">IF(ISBLANK(C35),0,(C35*G$2/C$2))</f>
         <v>210</v>
       </c>
-      <c r="H33" s="6">
-        <f t="shared" ref="H33" si="91">IF(ISBLANK(D33),0,(D33*H$2/D$2))</f>
+      <c r="H35" s="5">
+        <f t="shared" ref="H35" si="91">IF(ISBLANK(D35),0,(D35*H$2/D$2))</f>
         <v>300</v>
       </c>
-      <c r="J33" s="4">
-        <f t="shared" ref="J33" si="92">IF(ISBLANK(C33),0,(C33*J$2/C$2))</f>
+      <c r="J35" s="3">
+        <f t="shared" ref="J35" si="92">IF(ISBLANK(C35),0,(C35*J$2/C$2))</f>
         <v>105</v>
       </c>
-      <c r="K33" s="6">
-        <f t="shared" ref="K33" si="93">IF(ISBLANK(D33),0,(D33*K$2/D$2))</f>
+      <c r="K35" s="5">
+        <f t="shared" ref="K35" si="93">IF(ISBLANK(D35),0,(D35*K$2/D$2))</f>
         <v>150</v>
       </c>
-      <c r="M33" s="4">
-        <f t="shared" ref="M33" si="94">IF(ISBLANK(C33),0,(C33*M$2/C$2))</f>
+      <c r="M35" s="3">
+        <f t="shared" ref="M35" si="94">IF(ISBLANK(C35),0,(C35*M$2/C$2))</f>
         <v>70</v>
       </c>
-      <c r="N33" s="6">
-        <f t="shared" ref="N33" si="95">IF(ISBLANK(D33),0,(D33*N$2/D$2))</f>
+      <c r="N35" s="5">
+        <f t="shared" ref="N35" si="95">IF(ISBLANK(D35),0,(D35*N$2/D$2))</f>
         <v>100</v>
       </c>
     </row>
-    <row r="34" spans="1:14">
-      <c r="G34" s="4"/>
-      <c r="H34" s="6"/>
-    </row>
-    <row r="35" spans="1:14">
-      <c r="E35" s="1">
-        <f t="shared" ref="E35" si="96" xml:space="preserve"> C35/C$2</f>
-        <v>0</v>
-      </c>
-      <c r="F35" s="1">
-        <f t="shared" ref="F35" si="97" xml:space="preserve"> D35/D$2</f>
-        <v>0</v>
-      </c>
-      <c r="G35" s="4">
-        <f t="shared" ref="G35" si="98">IF(ISBLANK(C35),0,(C35*G$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="H35" s="6">
-        <f t="shared" ref="H35" si="99">IF(ISBLANK(D35),0,(D35*H$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="J35" s="4">
-        <f t="shared" ref="J35" si="100">IF(ISBLANK(C35),0,(C35*J$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="K35" s="6">
-        <f t="shared" ref="K35" si="101">IF(ISBLANK(D35),0,(D35*K$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="M35" s="4">
-        <f t="shared" ref="M35" si="102">IF(ISBLANK(C35),0,(C35*M$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="N35" s="6">
-        <f t="shared" ref="N35" si="103">IF(ISBLANK(D35),0,(D35*N$2/D$2))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14">
-      <c r="G36" s="4"/>
-      <c r="H36" s="6"/>
-    </row>
-    <row r="37" spans="1:14">
+    <row r="36" spans="1:31">
+      <c r="G36" s="3"/>
+      <c r="H36" s="5"/>
+    </row>
+    <row r="37" spans="1:31">
       <c r="E37" s="1">
-        <f t="shared" ref="E37" si="104" xml:space="preserve"> C37/C$2</f>
+        <f t="shared" ref="E37" si="96" xml:space="preserve"> C37/C$2</f>
         <v>0</v>
       </c>
       <c r="F37" s="1">
-        <f t="shared" ref="F37" si="105" xml:space="preserve"> D37/D$2</f>
-        <v>0</v>
-      </c>
-      <c r="G37" s="4">
-        <f t="shared" ref="G37" si="106">IF(ISBLANK(C37),0,(C37*G$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="H37" s="6">
-        <f t="shared" ref="H37" si="107">IF(ISBLANK(D37),0,(D37*H$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="J37" s="4">
-        <f t="shared" ref="J37" si="108">IF(ISBLANK(C37),0,(C37*J$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="K37" s="6">
-        <f t="shared" ref="K37" si="109">IF(ISBLANK(D37),0,(D37*K$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="M37" s="4">
-        <f t="shared" ref="M37" si="110">IF(ISBLANK(C37),0,(C37*M$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="N37" s="6">
-        <f t="shared" ref="N37" si="111">IF(ISBLANK(D37),0,(D37*N$2/D$2))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14">
-      <c r="C38"/>
-      <c r="D38"/>
-      <c r="E38"/>
-      <c r="F38"/>
-      <c r="G38"/>
-      <c r="H38"/>
-      <c r="I38"/>
-      <c r="J38"/>
-      <c r="K38"/>
-      <c r="M38"/>
-      <c r="N38"/>
-    </row>
-    <row r="39" spans="1:14">
-      <c r="C39"/>
-      <c r="D39"/>
-      <c r="E39"/>
-      <c r="F39"/>
-      <c r="G39"/>
-      <c r="H39"/>
-      <c r="I39"/>
-      <c r="J39"/>
-      <c r="K39"/>
-      <c r="M39"/>
-      <c r="N39"/>
-    </row>
-    <row r="40" spans="1:14">
-      <c r="C40"/>
-      <c r="D40"/>
-      <c r="E40"/>
-      <c r="F40"/>
-      <c r="G40"/>
-      <c r="H40"/>
-      <c r="I40"/>
-      <c r="J40"/>
-      <c r="K40"/>
-      <c r="M40"/>
-      <c r="N40"/>
-    </row>
-    <row r="41" spans="1:14">
-      <c r="C41"/>
-      <c r="D41"/>
-      <c r="E41"/>
-      <c r="F41"/>
-      <c r="G41"/>
-      <c r="H41"/>
-      <c r="I41"/>
-      <c r="J41"/>
-      <c r="K41"/>
-      <c r="M41"/>
-      <c r="N41"/>
-    </row>
-    <row r="42" spans="1:14">
-      <c r="C42"/>
-      <c r="D42"/>
-      <c r="E42"/>
-      <c r="F42"/>
-      <c r="G42"/>
-      <c r="H42"/>
-      <c r="I42"/>
-      <c r="J42"/>
-      <c r="K42"/>
-      <c r="M42"/>
-      <c r="N42"/>
-    </row>
-    <row r="43" spans="1:14">
+        <f t="shared" ref="F37" si="97" xml:space="preserve"> D37/D$2</f>
+        <v>0</v>
+      </c>
+      <c r="G37" s="3">
+        <f t="shared" ref="G37" si="98">IF(ISBLANK(C37),0,(C37*G$2/C$2))</f>
+        <v>0</v>
+      </c>
+      <c r="H37" s="5">
+        <f t="shared" ref="H37" si="99">IF(ISBLANK(D37),0,(D37*H$2/D$2))</f>
+        <v>0</v>
+      </c>
+      <c r="J37" s="3">
+        <f t="shared" ref="J37" si="100">IF(ISBLANK(C37),0,(C37*J$2/C$2))</f>
+        <v>0</v>
+      </c>
+      <c r="K37" s="5">
+        <f t="shared" ref="K37" si="101">IF(ISBLANK(D37),0,(D37*K$2/D$2))</f>
+        <v>0</v>
+      </c>
+      <c r="M37" s="3">
+        <f t="shared" ref="M37" si="102">IF(ISBLANK(C37),0,(C37*M$2/C$2))</f>
+        <v>0</v>
+      </c>
+      <c r="N37" s="5">
+        <f t="shared" ref="N37" si="103">IF(ISBLANK(D37),0,(D37*N$2/D$2))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:31" s="10" customFormat="1">
+      <c r="A38"/>
+      <c r="B38"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="5"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="3"/>
+      <c r="K38" s="5"/>
+      <c r="L38"/>
+      <c r="M38" s="3"/>
+      <c r="N38" s="5"/>
+      <c r="O38"/>
+      <c r="P38"/>
+      <c r="Q38"/>
+      <c r="R38"/>
+      <c r="S38"/>
+      <c r="T38"/>
+      <c r="U38"/>
+      <c r="V38"/>
+      <c r="W38"/>
+      <c r="X38"/>
+      <c r="Y38"/>
+      <c r="Z38"/>
+      <c r="AA38"/>
+      <c r="AB38"/>
+      <c r="AC38"/>
+      <c r="AD38"/>
+      <c r="AE38"/>
+    </row>
+    <row r="39" spans="1:31">
+      <c r="E39" s="1">
+        <f t="shared" ref="E39" si="104" xml:space="preserve"> C39/C$2</f>
+        <v>0</v>
+      </c>
+      <c r="F39" s="1">
+        <f t="shared" ref="F39" si="105" xml:space="preserve"> D39/D$2</f>
+        <v>0</v>
+      </c>
+      <c r="G39" s="3">
+        <f t="shared" ref="G39" si="106">IF(ISBLANK(C39),0,(C39*G$2/C$2))</f>
+        <v>0</v>
+      </c>
+      <c r="H39" s="5">
+        <f t="shared" ref="H39" si="107">IF(ISBLANK(D39),0,(D39*H$2/D$2))</f>
+        <v>0</v>
+      </c>
+      <c r="J39" s="3">
+        <f t="shared" ref="J39" si="108">IF(ISBLANK(C39),0,(C39*J$2/C$2))</f>
+        <v>0</v>
+      </c>
+      <c r="K39" s="5">
+        <f t="shared" ref="K39" si="109">IF(ISBLANK(D39),0,(D39*K$2/D$2))</f>
+        <v>0</v>
+      </c>
+      <c r="M39" s="3">
+        <f t="shared" ref="M39" si="110">IF(ISBLANK(C39),0,(C39*M$2/C$2))</f>
+        <v>0</v>
+      </c>
+      <c r="N39" s="5">
+        <f t="shared" ref="N39" si="111">IF(ISBLANK(D39),0,(D39*N$2/D$2))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:31">
+      <c r="G40" s="3"/>
+      <c r="H40" s="5"/>
+    </row>
+    <row r="41" spans="1:31">
+      <c r="A41" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" s="10"/>
+      <c r="C41" s="10"/>
+      <c r="D41" s="10"/>
+      <c r="E41" s="10"/>
+      <c r="F41" s="10"/>
+      <c r="G41" s="10"/>
+      <c r="H41" s="10"/>
+      <c r="I41" s="10"/>
+      <c r="J41" s="10"/>
+      <c r="K41" s="10"/>
+      <c r="L41" s="10"/>
+      <c r="M41" s="10"/>
+      <c r="N41" s="10"/>
+    </row>
+    <row r="42" spans="1:31">
+      <c r="G42" s="3"/>
+      <c r="H42" s="5"/>
+    </row>
+    <row r="43" spans="1:31">
       <c r="A43" t="s">
-        <v>9</v>
-      </c>
-      <c r="C43" s="4">
-        <v>572</v>
-      </c>
-      <c r="D43" s="6">
-        <v>1440</v>
+        <v>46</v>
+      </c>
+      <c r="C43" s="3">
+        <v>1744</v>
+      </c>
+      <c r="D43" s="5">
+        <v>800</v>
       </c>
       <c r="E43" s="1">
-        <f t="shared" si="0"/>
-        <v>0.22343750000000001</v>
+        <f t="shared" ref="E43" si="112" xml:space="preserve"> C43/C$2</f>
+        <v>0.68125000000000002</v>
       </c>
       <c r="F43" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="F43" si="113" xml:space="preserve"> D43/D$2</f>
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="G43" s="3">
+        <f t="shared" ref="G43" si="114">IF(ISBLANK(C43),0,(C43*G$2/C$2))</f>
+        <v>2616</v>
+      </c>
+      <c r="H43" s="5">
+        <f t="shared" ref="H43" si="115">IF(ISBLANK(D43),0,(D43*H$2/D$2))</f>
+        <v>1200</v>
+      </c>
+      <c r="J43" s="3">
+        <f t="shared" ref="J43" si="116">IF(ISBLANK(C43),0,(C43*J$2/C$2))</f>
+        <v>1308</v>
+      </c>
+      <c r="K43" s="5">
+        <f t="shared" ref="K43" si="117">IF(ISBLANK(D43),0,(D43*K$2/D$2))</f>
+        <v>600</v>
+      </c>
+      <c r="M43" s="3">
+        <f t="shared" ref="M43" si="118">IF(ISBLANK(C43),0,(C43*M$2/C$2))</f>
+        <v>872</v>
+      </c>
+      <c r="N43" s="5">
+        <f t="shared" ref="N43" si="119">IF(ISBLANK(D43),0,(D43*N$2/D$2))</f>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="44" spans="1:31">
+      <c r="G44" s="3"/>
+      <c r="H44" s="5"/>
+    </row>
+    <row r="45" spans="1:31">
+      <c r="A45" t="s">
+        <v>47</v>
+      </c>
+      <c r="C45" s="3">
+        <v>160</v>
+      </c>
+      <c r="D45" s="5">
+        <v>692</v>
+      </c>
+      <c r="E45" s="1">
+        <f t="shared" ref="E45" si="120" xml:space="preserve"> C45/C$2</f>
+        <v>6.25E-2</v>
+      </c>
+      <c r="F45" s="1">
+        <f t="shared" ref="F45" si="121" xml:space="preserve"> D45/D$2</f>
+        <v>0.48055555555555557</v>
+      </c>
+      <c r="G45" s="3">
+        <f t="shared" ref="G45" si="122">IF(ISBLANK(C45),0,(C45*G$2/C$2))</f>
+        <v>240</v>
+      </c>
+      <c r="H45" s="5">
+        <f t="shared" ref="H45" si="123">IF(ISBLANK(D45),0,(D45*H$2/D$2))</f>
+        <v>1038</v>
+      </c>
+      <c r="J45" s="3">
+        <f t="shared" ref="J45" si="124">IF(ISBLANK(C45),0,(C45*J$2/C$2))</f>
+        <v>120</v>
+      </c>
+      <c r="K45" s="5">
+        <f t="shared" ref="K45" si="125">IF(ISBLANK(D45),0,(D45*K$2/D$2))</f>
+        <v>519</v>
+      </c>
+      <c r="M45" s="3">
+        <f t="shared" ref="M45" si="126">IF(ISBLANK(C45),0,(C45*M$2/C$2))</f>
+        <v>80</v>
+      </c>
+      <c r="N45" s="5">
+        <f t="shared" ref="N45" si="127">IF(ISBLANK(D45),0,(D45*N$2/D$2))</f>
+        <v>346</v>
+      </c>
+    </row>
+    <row r="46" spans="1:31">
+      <c r="G46" s="3"/>
+      <c r="H46" s="5"/>
+    </row>
+    <row r="47" spans="1:31">
+      <c r="G47" s="3"/>
+      <c r="H47" s="5"/>
+    </row>
+    <row r="48" spans="1:31">
+      <c r="G48" s="3"/>
+      <c r="H48" s="5"/>
+    </row>
+    <row r="49" spans="1:14">
+      <c r="G49" s="3"/>
+      <c r="H49" s="5"/>
+    </row>
+    <row r="50" spans="1:14">
+      <c r="G50" s="3"/>
+      <c r="H50" s="5"/>
+    </row>
+    <row r="51" spans="1:14">
+      <c r="G51" s="3"/>
+      <c r="H51" s="5"/>
+    </row>
+    <row r="52" spans="1:14">
+      <c r="G52" s="3"/>
+      <c r="H52" s="5"/>
+    </row>
+    <row r="53" spans="1:14">
+      <c r="G53" s="3"/>
+      <c r="H53" s="5"/>
+    </row>
+    <row r="54" spans="1:14">
+      <c r="G54" s="3"/>
+      <c r="H54" s="5"/>
+    </row>
+    <row r="55" spans="1:14">
+      <c r="G55" s="3"/>
+      <c r="H55" s="5"/>
+    </row>
+    <row r="56" spans="1:14">
+      <c r="G56" s="3"/>
+      <c r="H56" s="5"/>
+    </row>
+    <row r="57" spans="1:14">
+      <c r="G57" s="3"/>
+      <c r="H57" s="5"/>
+    </row>
+    <row r="58" spans="1:14">
+      <c r="A58" t="s">
         <v>1</v>
       </c>
-      <c r="G43" s="4">
-        <f t="shared" si="2"/>
-        <v>858</v>
-      </c>
-      <c r="H43" s="6">
-        <f t="shared" si="3"/>
-        <v>2160</v>
-      </c>
-      <c r="J43" s="4">
-        <f t="shared" si="4"/>
-        <v>429</v>
-      </c>
-      <c r="K43" s="6">
-        <f t="shared" si="5"/>
-        <v>1080</v>
-      </c>
-      <c r="M43" s="4">
-        <f t="shared" si="6"/>
-        <v>286</v>
-      </c>
-      <c r="N43" s="6">
-        <f t="shared" si="7"/>
-        <v>720</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14">
-      <c r="E44" s="1">
-        <f xml:space="preserve"> C44/C$2</f>
-        <v>0</v>
-      </c>
-      <c r="F44" s="1">
-        <f xml:space="preserve"> D44/D$2</f>
-        <v>0</v>
-      </c>
-      <c r="G44" s="4">
-        <f>IF(ISBLANK(C44),0,(C44*G$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="H44" s="6">
-        <f>IF(ISBLANK(D44),0,(D44*H$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="J44" s="4">
-        <f>IF(ISBLANK(C44),0,(C44*J$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="K44" s="6">
-        <f>IF(ISBLANK(D44),0,(D44*K$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="M44" s="4">
-        <f>IF(ISBLANK(C44),0,(C44*M$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="N44" s="6">
-        <f>IF(ISBLANK(D44),0,(D44*N$2/D$2))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14">
-      <c r="A45" t="s">
-        <v>1</v>
-      </c>
-      <c r="C45" s="4">
+      <c r="C58" s="3">
         <v>1660</v>
       </c>
-      <c r="D45" s="6">
+      <c r="D58" s="5">
         <v>300</v>
       </c>
-      <c r="E45" s="1">
-        <f xml:space="preserve"> C45/C$2</f>
+      <c r="E58" s="1">
+        <f t="shared" ref="E58:F64" si="128" xml:space="preserve"> C58/C$2</f>
         <v>0.6484375</v>
       </c>
-      <c r="F45" s="1">
-        <f xml:space="preserve"> D45/D$2</f>
+      <c r="F58" s="1">
+        <f t="shared" si="128"/>
         <v>0.20833333333333334</v>
       </c>
-      <c r="G45" s="4">
-        <f>IF(ISBLANK(C45),0,(C45*G$2/C$2))</f>
+      <c r="G58" s="3">
+        <f t="shared" ref="G58:H64" si="129">IF(ISBLANK(C58),0,(C58*G$2/C$2))</f>
         <v>2490</v>
       </c>
-      <c r="H45" s="6">
-        <f>IF(ISBLANK(D45),0,(D45*H$2/D$2))</f>
+      <c r="H58" s="5">
+        <f t="shared" si="129"/>
         <v>450</v>
       </c>
-      <c r="J45" s="4">
-        <f>IF(ISBLANK(C45),0,(C45*J$2/C$2))</f>
+      <c r="J58" s="3">
+        <f t="shared" ref="J58:K64" si="130">IF(ISBLANK(C58),0,(C58*J$2/C$2))</f>
         <v>1245</v>
       </c>
-      <c r="K45" s="6">
-        <f>IF(ISBLANK(D45),0,(D45*K$2/D$2))</f>
+      <c r="K58" s="5">
+        <f t="shared" si="130"/>
         <v>225</v>
       </c>
-      <c r="M45" s="4">
-        <f>IF(ISBLANK(C45),0,(C45*M$2/C$2))</f>
+      <c r="M58" s="3">
+        <f t="shared" ref="M58:N64" si="131">IF(ISBLANK(C58),0,(C58*M$2/C$2))</f>
         <v>830</v>
       </c>
-      <c r="N45" s="6">
-        <f>IF(ISBLANK(D45),0,(D45*N$2/D$2))</f>
+      <c r="N58" s="5">
+        <f t="shared" si="131"/>
         <v>150</v>
       </c>
     </row>
-    <row r="46" spans="1:14">
-      <c r="E46" s="1">
-        <f xml:space="preserve"> C46/C$2</f>
-        <v>0</v>
-      </c>
-      <c r="F46" s="1">
-        <f xml:space="preserve"> D46/D$2</f>
-        <v>0</v>
-      </c>
-      <c r="G46" s="4">
-        <f>IF(ISBLANK(C46),0,(C46*G$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="H46" s="6">
-        <f>IF(ISBLANK(D46),0,(D46*H$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="J46" s="4">
-        <f>IF(ISBLANK(C46),0,(C46*J$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="K46" s="6">
-        <f>IF(ISBLANK(D46),0,(D46*K$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="M46" s="4">
-        <f>IF(ISBLANK(C46),0,(C46*M$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="N46" s="6">
-        <f>IF(ISBLANK(D46),0,(D46*N$2/D$2))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14">
-      <c r="A47" t="s">
+    <row r="59" spans="1:14">
+      <c r="E59" s="1">
+        <f t="shared" si="128"/>
+        <v>0</v>
+      </c>
+      <c r="F59" s="1">
+        <f t="shared" si="128"/>
+        <v>0</v>
+      </c>
+      <c r="G59" s="3">
+        <f t="shared" si="129"/>
+        <v>0</v>
+      </c>
+      <c r="H59" s="5">
+        <f t="shared" si="129"/>
+        <v>0</v>
+      </c>
+      <c r="J59" s="3">
+        <f t="shared" si="130"/>
+        <v>0</v>
+      </c>
+      <c r="K59" s="5">
+        <f t="shared" si="130"/>
+        <v>0</v>
+      </c>
+      <c r="M59" s="3">
+        <f t="shared" si="131"/>
+        <v>0</v>
+      </c>
+      <c r="N59" s="5">
+        <f t="shared" si="131"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14">
+      <c r="A60" t="s">
         <v>2</v>
       </c>
-      <c r="C47" s="4">
+      <c r="C60" s="3">
         <v>1372</v>
       </c>
-      <c r="D47" s="6">
+      <c r="D60" s="5">
         <v>588</v>
       </c>
-      <c r="E47" s="1">
-        <f xml:space="preserve"> C47/C$2</f>
+      <c r="E60" s="1">
+        <f t="shared" si="128"/>
         <v>0.53593749999999996</v>
       </c>
-      <c r="F47" s="1">
-        <f xml:space="preserve"> D47/D$2</f>
+      <c r="F60" s="1">
+        <f t="shared" si="128"/>
         <v>0.40833333333333333</v>
       </c>
-      <c r="G47" s="4">
-        <f>IF(ISBLANK(C47),0,(C47*G$2/C$2))</f>
+      <c r="G60" s="3">
+        <f t="shared" si="129"/>
         <v>2058</v>
       </c>
-      <c r="H47" s="6">
-        <f>IF(ISBLANK(D47),0,(D47*H$2/D$2))</f>
+      <c r="H60" s="5">
+        <f t="shared" si="129"/>
         <v>882</v>
       </c>
-      <c r="J47" s="4">
-        <f>IF(ISBLANK(C47),0,(C47*J$2/C$2))</f>
+      <c r="J60" s="3">
+        <f t="shared" si="130"/>
         <v>1029</v>
       </c>
-      <c r="K47" s="6">
-        <f>IF(ISBLANK(D47),0,(D47*K$2/D$2))</f>
+      <c r="K60" s="5">
+        <f t="shared" si="130"/>
         <v>441</v>
       </c>
-      <c r="M47" s="4">
-        <f>IF(ISBLANK(C47),0,(C47*M$2/C$2))</f>
+      <c r="M60" s="3">
+        <f t="shared" si="131"/>
         <v>686</v>
       </c>
-      <c r="N47" s="6">
-        <f>IF(ISBLANK(D47),0,(D47*N$2/D$2))</f>
+      <c r="N60" s="5">
+        <f t="shared" si="131"/>
         <v>294</v>
       </c>
     </row>
-    <row r="48" spans="1:14">
-      <c r="E48" s="1">
-        <f xml:space="preserve"> C48/C$2</f>
-        <v>0</v>
-      </c>
-      <c r="F48" s="1">
-        <f xml:space="preserve"> D48/D$2</f>
-        <v>0</v>
-      </c>
-      <c r="G48" s="4">
-        <f>IF(ISBLANK(C48),0,(C48*G$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="H48" s="6">
-        <f>IF(ISBLANK(D48),0,(D48*H$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="J48" s="4">
-        <f>IF(ISBLANK(C48),0,(C48*J$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="K48" s="6">
-        <f>IF(ISBLANK(D48),0,(D48*K$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="M48" s="4">
-        <f>IF(ISBLANK(C48),0,(C48*M$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="N48" s="6">
-        <f>IF(ISBLANK(D48),0,(D48*N$2/D$2))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14">
-      <c r="A49" t="s">
-        <v>0</v>
-      </c>
-      <c r="C49" s="4">
+    <row r="61" spans="1:14">
+      <c r="E61" s="1">
+        <f t="shared" si="128"/>
+        <v>0</v>
+      </c>
+      <c r="F61" s="1">
+        <f t="shared" si="128"/>
+        <v>0</v>
+      </c>
+      <c r="G61" s="3">
+        <f t="shared" si="129"/>
+        <v>0</v>
+      </c>
+      <c r="H61" s="5">
+        <f t="shared" si="129"/>
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
+        <f t="shared" si="130"/>
+        <v>0</v>
+      </c>
+      <c r="K61" s="5">
+        <f t="shared" si="130"/>
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
+        <f t="shared" si="131"/>
+        <v>0</v>
+      </c>
+      <c r="N61" s="5">
+        <f t="shared" si="131"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14">
+      <c r="A62" t="s">
+        <v>0</v>
+      </c>
+      <c r="C62" s="3">
         <v>280</v>
       </c>
-      <c r="D49" s="6">
+      <c r="D62" s="5">
         <v>156</v>
       </c>
-      <c r="E49" s="1">
-        <f xml:space="preserve"> C49/C$2</f>
+      <c r="E62" s="1">
+        <f t="shared" si="128"/>
         <v>0.109375</v>
       </c>
-      <c r="F49" s="1">
-        <f xml:space="preserve"> D49/D$2</f>
+      <c r="F62" s="1">
+        <f t="shared" si="128"/>
         <v>0.10833333333333334</v>
       </c>
-      <c r="G49" s="4">
-        <f>IF(ISBLANK(C49),0,(C49*G$2/C$2))</f>
+      <c r="G62" s="3">
+        <f t="shared" si="129"/>
         <v>420</v>
       </c>
-      <c r="H49" s="6">
-        <f>IF(ISBLANK(D49),0,(D49*H$2/D$2))</f>
+      <c r="H62" s="5">
+        <f t="shared" si="129"/>
         <v>234</v>
       </c>
-      <c r="J49" s="4">
-        <f>IF(ISBLANK(C49),0,(C49*J$2/C$2))</f>
+      <c r="J62" s="3">
+        <f t="shared" si="130"/>
         <v>210</v>
       </c>
-      <c r="K49" s="6">
-        <f>IF(ISBLANK(D49),0,(D49*K$2/D$2))</f>
+      <c r="K62" s="5">
+        <f t="shared" si="130"/>
         <v>117</v>
       </c>
-      <c r="M49" s="4">
-        <f>IF(ISBLANK(C49),0,(C49*M$2/C$2))</f>
+      <c r="M62" s="3">
+        <f t="shared" si="131"/>
         <v>140</v>
       </c>
-      <c r="N49" s="6">
-        <f>IF(ISBLANK(D49),0,(D49*N$2/D$2))</f>
+      <c r="N62" s="5">
+        <f t="shared" si="131"/>
         <v>78</v>
       </c>
     </row>
-    <row r="50" spans="1:14">
-      <c r="E50" s="1">
-        <f xml:space="preserve"> C50/C$2</f>
-        <v>0</v>
-      </c>
-      <c r="F50" s="1">
-        <f xml:space="preserve"> D50/D$2</f>
-        <v>0</v>
-      </c>
-      <c r="G50" s="4">
-        <f>IF(ISBLANK(C50),0,(C50*G$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="H50" s="6">
-        <f>IF(ISBLANK(D50),0,(D50*H$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="J50" s="4">
-        <f>IF(ISBLANK(C50),0,(C50*J$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="K50" s="6">
-        <f>IF(ISBLANK(D50),0,(D50*K$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="M50" s="4">
-        <f>IF(ISBLANK(C50),0,(C50*M$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="N50" s="6">
-        <f>IF(ISBLANK(D50),0,(D50*N$2/D$2))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14">
-      <c r="A51" t="s">
+    <row r="63" spans="1:14">
+      <c r="E63" s="1">
+        <f t="shared" si="128"/>
+        <v>0</v>
+      </c>
+      <c r="F63" s="1">
+        <f t="shared" si="128"/>
+        <v>0</v>
+      </c>
+      <c r="G63" s="3">
+        <f t="shared" si="129"/>
+        <v>0</v>
+      </c>
+      <c r="H63" s="5">
+        <f t="shared" si="129"/>
+        <v>0</v>
+      </c>
+      <c r="J63" s="3">
+        <f t="shared" si="130"/>
+        <v>0</v>
+      </c>
+      <c r="K63" s="5">
+        <f t="shared" si="130"/>
+        <v>0</v>
+      </c>
+      <c r="M63" s="3">
+        <f t="shared" si="131"/>
+        <v>0</v>
+      </c>
+      <c r="N63" s="5">
+        <f t="shared" si="131"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14">
+      <c r="A64" t="s">
         <v>3</v>
       </c>
-      <c r="C51" s="4">
+      <c r="C64" s="3">
         <v>264</v>
       </c>
-      <c r="D51" s="6">
+      <c r="D64" s="5">
         <v>172</v>
       </c>
-      <c r="E51" s="1">
-        <f xml:space="preserve"> C51/C$2</f>
+      <c r="E64" s="1">
+        <f t="shared" si="128"/>
         <v>0.10312499999999999</v>
       </c>
-      <c r="F51" s="1">
-        <f xml:space="preserve"> D51/D$2</f>
+      <c r="F64" s="1">
+        <f t="shared" si="128"/>
         <v>0.11944444444444445</v>
       </c>
-      <c r="G51" s="4">
-        <f>IF(ISBLANK(C51),0,(C51*G$2/C$2))</f>
+      <c r="G64" s="3">
+        <f t="shared" si="129"/>
         <v>396</v>
       </c>
-      <c r="H51" s="6">
-        <f>IF(ISBLANK(D51),0,(D51*H$2/D$2))</f>
+      <c r="H64" s="5">
+        <f t="shared" si="129"/>
         <v>258</v>
       </c>
-      <c r="J51" s="4">
-        <f>IF(ISBLANK(C51),0,(C51*J$2/C$2))</f>
+      <c r="J64" s="3">
+        <f t="shared" si="130"/>
         <v>198</v>
       </c>
-      <c r="K51" s="6">
-        <f>IF(ISBLANK(D51),0,(D51*K$2/D$2))</f>
+      <c r="K64" s="5">
+        <f t="shared" si="130"/>
         <v>129</v>
       </c>
-      <c r="M51" s="4">
-        <f>IF(ISBLANK(C51),0,(C51*M$2/C$2))</f>
+      <c r="M64" s="3">
+        <f t="shared" si="131"/>
         <v>132</v>
       </c>
-      <c r="N51" s="6">
-        <f>IF(ISBLANK(D51),0,(D51*N$2/D$2))</f>
+      <c r="N64" s="5">
+        <f t="shared" si="131"/>
         <v>86</v>
       </c>
     </row>
-    <row r="52" spans="1:14">
-      <c r="G52" s="4"/>
-      <c r="H52" s="6"/>
-    </row>
-    <row r="53" spans="1:14">
-      <c r="A53" t="s">
+    <row r="65" spans="1:14">
+      <c r="G65" s="3"/>
+      <c r="H65" s="5"/>
+    </row>
+    <row r="66" spans="1:14">
+      <c r="A66" t="s">
         <v>4</v>
       </c>
-      <c r="C53" s="4">
+      <c r="C66" s="3">
         <v>1200</v>
       </c>
-      <c r="D53" s="6">
+      <c r="D66" s="5">
         <v>944</v>
       </c>
-      <c r="E53" s="1">
-        <f xml:space="preserve"> C53/C$2</f>
+      <c r="E66" s="1">
+        <f t="shared" ref="E66:E113" si="132" xml:space="preserve"> C66/C$2</f>
         <v>0.46875</v>
       </c>
-      <c r="F53" s="1">
-        <f xml:space="preserve"> D53/D$2</f>
+      <c r="F66" s="1">
+        <f t="shared" ref="F66:F113" si="133" xml:space="preserve"> D66/D$2</f>
         <v>0.65555555555555556</v>
       </c>
-      <c r="G53" s="4">
-        <f>IF(ISBLANK(C53),0,(C53*G$2/C$2))</f>
+      <c r="G66" s="3">
+        <f t="shared" ref="G66:G113" si="134">IF(ISBLANK(C66),0,(C66*G$2/C$2))</f>
         <v>1800</v>
       </c>
-      <c r="H53" s="6">
-        <f>IF(ISBLANK(D53),0,(D53*H$2/D$2))</f>
+      <c r="H66" s="5">
+        <f t="shared" ref="H66:H113" si="135">IF(ISBLANK(D66),0,(D66*H$2/D$2))</f>
         <v>1416</v>
       </c>
-      <c r="J53" s="4">
-        <f>IF(ISBLANK(C53),0,(C53*J$2/C$2))</f>
+      <c r="J66" s="3">
+        <f t="shared" ref="J66:J113" si="136">IF(ISBLANK(C66),0,(C66*J$2/C$2))</f>
         <v>900</v>
       </c>
-      <c r="K53" s="6">
-        <f>IF(ISBLANK(D53),0,(D53*K$2/D$2))</f>
+      <c r="K66" s="5">
+        <f t="shared" ref="K66:K113" si="137">IF(ISBLANK(D66),0,(D66*K$2/D$2))</f>
         <v>708</v>
       </c>
-      <c r="M53" s="4">
-        <f>IF(ISBLANK(C53),0,(C53*M$2/C$2))</f>
+      <c r="M66" s="3">
+        <f t="shared" ref="M66:M113" si="138">IF(ISBLANK(C66),0,(C66*M$2/C$2))</f>
         <v>600</v>
       </c>
-      <c r="N53" s="6">
-        <f>IF(ISBLANK(D53),0,(D53*N$2/D$2))</f>
+      <c r="N66" s="5">
+        <f t="shared" ref="N66:N113" si="139">IF(ISBLANK(D66),0,(D66*N$2/D$2))</f>
         <v>472</v>
       </c>
     </row>
-    <row r="54" spans="1:14">
-      <c r="E54" s="1">
-        <f xml:space="preserve"> C54/C$2</f>
-        <v>0</v>
-      </c>
-      <c r="F54" s="1">
-        <f xml:space="preserve"> D54/D$2</f>
-        <v>0</v>
-      </c>
-      <c r="G54" s="4">
-        <f>IF(ISBLANK(C54),0,(C54*G$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="H54" s="6">
-        <f>IF(ISBLANK(D54),0,(D54*H$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="J54" s="4">
-        <f>IF(ISBLANK(C54),0,(C54*J$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="K54" s="6">
-        <f>IF(ISBLANK(D54),0,(D54*K$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="M54" s="4">
-        <f>IF(ISBLANK(C54),0,(C54*M$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="N54" s="6">
-        <f>IF(ISBLANK(D54),0,(D54*N$2/D$2))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14">
-      <c r="A55" t="s">
+    <row r="67" spans="1:14">
+      <c r="E67" s="1">
+        <f t="shared" si="132"/>
+        <v>0</v>
+      </c>
+      <c r="F67" s="1">
+        <f t="shared" si="133"/>
+        <v>0</v>
+      </c>
+      <c r="G67" s="3">
+        <f t="shared" si="134"/>
+        <v>0</v>
+      </c>
+      <c r="H67" s="5">
+        <f t="shared" si="135"/>
+        <v>0</v>
+      </c>
+      <c r="J67" s="3">
+        <f t="shared" si="136"/>
+        <v>0</v>
+      </c>
+      <c r="K67" s="5">
+        <f t="shared" si="137"/>
+        <v>0</v>
+      </c>
+      <c r="M67" s="3">
+        <f t="shared" si="138"/>
+        <v>0</v>
+      </c>
+      <c r="N67" s="5">
+        <f t="shared" si="139"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14">
+      <c r="A68" t="s">
         <v>6</v>
       </c>
-      <c r="C55" s="4">
+      <c r="C68" s="3">
         <v>420</v>
       </c>
-      <c r="D55" s="6">
+      <c r="D68" s="5">
         <v>1032</v>
       </c>
-      <c r="E55" s="1">
-        <f xml:space="preserve"> C55/C$2</f>
+      <c r="E68" s="1">
+        <f t="shared" si="132"/>
         <v>0.1640625</v>
       </c>
-      <c r="F55" s="1">
-        <f xml:space="preserve"> D55/D$2</f>
+      <c r="F68" s="1">
+        <f t="shared" si="133"/>
         <v>0.71666666666666667</v>
       </c>
-      <c r="G55" s="4">
-        <f>IF(ISBLANK(C55),0,(C55*G$2/C$2))</f>
+      <c r="G68" s="3">
+        <f t="shared" si="134"/>
         <v>630</v>
       </c>
-      <c r="H55" s="6">
-        <f>IF(ISBLANK(D55),0,(D55*H$2/D$2))</f>
+      <c r="H68" s="5">
+        <f t="shared" si="135"/>
         <v>1548</v>
       </c>
-      <c r="J55" s="4">
-        <f>IF(ISBLANK(C55),0,(C55*J$2/C$2))</f>
+      <c r="J68" s="3">
+        <f t="shared" si="136"/>
         <v>315</v>
       </c>
-      <c r="K55" s="6">
-        <f>IF(ISBLANK(D55),0,(D55*K$2/D$2))</f>
+      <c r="K68" s="5">
+        <f t="shared" si="137"/>
         <v>774</v>
       </c>
-      <c r="M55" s="4">
-        <f>IF(ISBLANK(C55),0,(C55*M$2/C$2))</f>
+      <c r="M68" s="3">
+        <f t="shared" si="138"/>
         <v>210</v>
       </c>
-      <c r="N55" s="6">
-        <f>IF(ISBLANK(D55),0,(D55*N$2/D$2))</f>
+      <c r="N68" s="5">
+        <f t="shared" si="139"/>
         <v>516</v>
       </c>
     </row>
-    <row r="56" spans="1:14">
-      <c r="E56" s="1">
-        <f xml:space="preserve"> C56/C$2</f>
-        <v>0</v>
-      </c>
-      <c r="F56" s="1">
-        <f xml:space="preserve"> D56/D$2</f>
-        <v>0</v>
-      </c>
-      <c r="G56" s="4">
-        <f>IF(ISBLANK(C56),0,(C56*G$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="H56" s="6">
-        <f>IF(ISBLANK(D56),0,(D56*H$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="J56" s="4">
-        <f>IF(ISBLANK(C56),0,(C56*J$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="K56" s="6">
-        <f>IF(ISBLANK(D56),0,(D56*K$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="M56" s="4">
-        <f>IF(ISBLANK(C56),0,(C56*M$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="N56" s="6">
-        <f>IF(ISBLANK(D56),0,(D56*N$2/D$2))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14">
-      <c r="A57" t="s">
+    <row r="69" spans="1:14">
+      <c r="E69" s="1">
+        <f t="shared" si="132"/>
+        <v>0</v>
+      </c>
+      <c r="F69" s="1">
+        <f t="shared" si="133"/>
+        <v>0</v>
+      </c>
+      <c r="G69" s="3">
+        <f t="shared" si="134"/>
+        <v>0</v>
+      </c>
+      <c r="H69" s="5">
+        <f t="shared" si="135"/>
+        <v>0</v>
+      </c>
+      <c r="J69" s="3">
+        <f t="shared" si="136"/>
+        <v>0</v>
+      </c>
+      <c r="K69" s="5">
+        <f t="shared" si="137"/>
+        <v>0</v>
+      </c>
+      <c r="M69" s="3">
+        <f t="shared" si="138"/>
+        <v>0</v>
+      </c>
+      <c r="N69" s="5">
+        <f t="shared" si="139"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14">
+      <c r="A70" t="s">
         <v>7</v>
       </c>
-      <c r="C57" s="4">
+      <c r="C70" s="3">
         <v>1360</v>
       </c>
-      <c r="D57" s="6">
+      <c r="D70" s="5">
         <v>952</v>
       </c>
-      <c r="E57" s="1">
-        <f xml:space="preserve"> C57/C$2</f>
+      <c r="E70" s="1">
+        <f t="shared" si="132"/>
         <v>0.53125</v>
       </c>
-      <c r="F57" s="1">
-        <f xml:space="preserve"> D57/D$2</f>
+      <c r="F70" s="1">
+        <f t="shared" si="133"/>
         <v>0.66111111111111109</v>
       </c>
-      <c r="G57" s="4">
-        <f>IF(ISBLANK(C57),0,(C57*G$2/C$2))</f>
+      <c r="G70" s="3">
+        <f t="shared" si="134"/>
         <v>2040</v>
       </c>
-      <c r="H57" s="6">
-        <f>IF(ISBLANK(D57),0,(D57*H$2/D$2))</f>
+      <c r="H70" s="5">
+        <f t="shared" si="135"/>
         <v>1428</v>
       </c>
-      <c r="J57" s="4">
-        <f>IF(ISBLANK(C57),0,(C57*J$2/C$2))</f>
+      <c r="J70" s="3">
+        <f t="shared" si="136"/>
         <v>1020</v>
       </c>
-      <c r="K57" s="6">
-        <f>IF(ISBLANK(D57),0,(D57*K$2/D$2))</f>
+      <c r="K70" s="5">
+        <f t="shared" si="137"/>
         <v>714</v>
       </c>
-      <c r="M57" s="4">
-        <f>IF(ISBLANK(C57),0,(C57*M$2/C$2))</f>
+      <c r="M70" s="3">
+        <f t="shared" si="138"/>
         <v>680</v>
       </c>
-      <c r="N57" s="6">
-        <f>IF(ISBLANK(D57),0,(D57*N$2/D$2))</f>
+      <c r="N70" s="5">
+        <f t="shared" si="139"/>
         <v>476</v>
       </c>
     </row>
-    <row r="58" spans="1:14">
-      <c r="E58" s="1">
-        <f xml:space="preserve"> C58/C$2</f>
-        <v>0</v>
-      </c>
-      <c r="F58" s="1">
-        <f xml:space="preserve"> D58/D$2</f>
-        <v>0</v>
-      </c>
-      <c r="G58" s="4">
-        <f>IF(ISBLANK(C58),0,(C58*G$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="H58" s="6">
-        <f>IF(ISBLANK(D58),0,(D58*H$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="J58" s="4">
-        <f>IF(ISBLANK(C58),0,(C58*J$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="K58" s="6">
-        <f>IF(ISBLANK(D58),0,(D58*K$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="M58" s="4">
-        <f>IF(ISBLANK(C58),0,(C58*M$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="N58" s="6">
-        <f>IF(ISBLANK(D58),0,(D58*N$2/D$2))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:14">
-      <c r="A59" t="s">
+    <row r="71" spans="1:14">
+      <c r="E71" s="1">
+        <f t="shared" si="132"/>
+        <v>0</v>
+      </c>
+      <c r="F71" s="1">
+        <f t="shared" si="133"/>
+        <v>0</v>
+      </c>
+      <c r="G71" s="3">
+        <f t="shared" si="134"/>
+        <v>0</v>
+      </c>
+      <c r="H71" s="5">
+        <f t="shared" si="135"/>
+        <v>0</v>
+      </c>
+      <c r="J71" s="3">
+        <f t="shared" si="136"/>
+        <v>0</v>
+      </c>
+      <c r="K71" s="5">
+        <f t="shared" si="137"/>
+        <v>0</v>
+      </c>
+      <c r="M71" s="3">
+        <f t="shared" si="138"/>
+        <v>0</v>
+      </c>
+      <c r="N71" s="5">
+        <f t="shared" si="139"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14">
+      <c r="A72" t="s">
         <v>8</v>
       </c>
-      <c r="C59" s="4">
+      <c r="C72" s="3">
         <v>712</v>
       </c>
-      <c r="D59" s="6">
+      <c r="D72" s="5">
         <v>488</v>
       </c>
-      <c r="E59" s="1">
-        <f xml:space="preserve"> C59/C$2</f>
+      <c r="E72" s="1">
+        <f t="shared" si="132"/>
         <v>0.27812500000000001</v>
       </c>
-      <c r="F59" s="1">
-        <f xml:space="preserve"> D59/D$2</f>
+      <c r="F72" s="1">
+        <f t="shared" si="133"/>
         <v>0.33888888888888891</v>
       </c>
-      <c r="G59" s="4">
-        <f>IF(ISBLANK(C59),0,(C59*G$2/C$2))</f>
+      <c r="G72" s="3">
+        <f t="shared" si="134"/>
         <v>1068</v>
       </c>
-      <c r="H59" s="6">
-        <f>IF(ISBLANK(D59),0,(D59*H$2/D$2))</f>
+      <c r="H72" s="5">
+        <f t="shared" si="135"/>
         <v>732</v>
       </c>
-      <c r="J59" s="4">
-        <f>IF(ISBLANK(C59),0,(C59*J$2/C$2))</f>
+      <c r="J72" s="3">
+        <f t="shared" si="136"/>
         <v>534</v>
       </c>
-      <c r="K59" s="6">
-        <f>IF(ISBLANK(D59),0,(D59*K$2/D$2))</f>
+      <c r="K72" s="5">
+        <f t="shared" si="137"/>
         <v>366</v>
       </c>
-      <c r="M59" s="4">
-        <f>IF(ISBLANK(C59),0,(C59*M$2/C$2))</f>
+      <c r="M72" s="3">
+        <f t="shared" si="138"/>
         <v>356</v>
       </c>
-      <c r="N59" s="6">
-        <f>IF(ISBLANK(D59),0,(D59*N$2/D$2))</f>
+      <c r="N72" s="5">
+        <f t="shared" si="139"/>
         <v>244</v>
       </c>
     </row>
-    <row r="60" spans="1:14">
-      <c r="E60" s="1">
-        <f xml:space="preserve"> C60/C$2</f>
-        <v>0</v>
-      </c>
-      <c r="F60" s="1">
-        <f xml:space="preserve"> D60/D$2</f>
-        <v>0</v>
-      </c>
-      <c r="G60" s="4">
-        <f>IF(ISBLANK(C60),0,(C60*G$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="H60" s="6">
-        <f>IF(ISBLANK(D60),0,(D60*H$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="J60" s="4">
-        <f>IF(ISBLANK(C60),0,(C60*J$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="K60" s="6">
-        <f>IF(ISBLANK(D60),0,(D60*K$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="M60" s="4">
-        <f>IF(ISBLANK(C60),0,(C60*M$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="N60" s="6">
-        <f>IF(ISBLANK(D60),0,(D60*N$2/D$2))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:14">
-      <c r="A61" t="s">
+    <row r="73" spans="1:14">
+      <c r="E73" s="1">
+        <f t="shared" si="132"/>
+        <v>0</v>
+      </c>
+      <c r="F73" s="1">
+        <f t="shared" si="133"/>
+        <v>0</v>
+      </c>
+      <c r="G73" s="3">
+        <f t="shared" si="134"/>
+        <v>0</v>
+      </c>
+      <c r="H73" s="5">
+        <f t="shared" si="135"/>
+        <v>0</v>
+      </c>
+      <c r="J73" s="3">
+        <f t="shared" si="136"/>
+        <v>0</v>
+      </c>
+      <c r="K73" s="5">
+        <f t="shared" si="137"/>
+        <v>0</v>
+      </c>
+      <c r="M73" s="3">
+        <f t="shared" si="138"/>
+        <v>0</v>
+      </c>
+      <c r="N73" s="5">
+        <f t="shared" si="139"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14">
+      <c r="A74" t="s">
         <v>10</v>
       </c>
-      <c r="D61" s="6">
+      <c r="D74" s="5">
         <v>412</v>
       </c>
-      <c r="E61" s="1">
-        <f xml:space="preserve"> C61/C$2</f>
-        <v>0</v>
-      </c>
-      <c r="F61" s="1">
-        <f xml:space="preserve"> D61/D$2</f>
+      <c r="E74" s="1">
+        <f t="shared" si="132"/>
+        <v>0</v>
+      </c>
+      <c r="F74" s="1">
+        <f t="shared" si="133"/>
         <v>0.28611111111111109</v>
       </c>
-      <c r="G61" s="4">
-        <f>IF(ISBLANK(C61),0,(C61*G$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="H61" s="6">
-        <f>IF(ISBLANK(D61),0,(D61*H$2/D$2))</f>
+      <c r="G74" s="3">
+        <f t="shared" si="134"/>
+        <v>0</v>
+      </c>
+      <c r="H74" s="5">
+        <f t="shared" si="135"/>
         <v>618</v>
       </c>
-      <c r="J61" s="4">
-        <f>IF(ISBLANK(C61),0,(C61*J$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="K61" s="6">
-        <f>IF(ISBLANK(D61),0,(D61*K$2/D$2))</f>
+      <c r="J74" s="3">
+        <f t="shared" si="136"/>
+        <v>0</v>
+      </c>
+      <c r="K74" s="5">
+        <f t="shared" si="137"/>
         <v>309</v>
       </c>
-      <c r="M61" s="4">
-        <f>IF(ISBLANK(C61),0,(C61*M$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="N61" s="6">
-        <f>IF(ISBLANK(D61),0,(D61*N$2/D$2))</f>
+      <c r="M74" s="3">
+        <f t="shared" si="138"/>
+        <v>0</v>
+      </c>
+      <c r="N74" s="5">
+        <f t="shared" si="139"/>
         <v>206</v>
-      </c>
-    </row>
-    <row r="62" spans="1:14">
-      <c r="E62" s="1">
-        <f xml:space="preserve"> C62/C$2</f>
-        <v>0</v>
-      </c>
-      <c r="F62" s="1">
-        <f xml:space="preserve"> D62/D$2</f>
-        <v>0</v>
-      </c>
-      <c r="G62" s="4">
-        <f>IF(ISBLANK(C62),0,(C62*G$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="H62" s="6">
-        <f>IF(ISBLANK(D62),0,(D62*H$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="J62" s="4">
-        <f>IF(ISBLANK(C62),0,(C62*J$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="K62" s="6">
-        <f>IF(ISBLANK(D62),0,(D62*K$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="M62" s="4">
-        <f>IF(ISBLANK(C62),0,(C62*M$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="N62" s="6">
-        <f>IF(ISBLANK(D62),0,(D62*N$2/D$2))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:14">
-      <c r="A63" t="s">
-        <v>17</v>
-      </c>
-      <c r="C63" s="4">
-        <v>228</v>
-      </c>
-      <c r="D63" s="6">
-        <v>372</v>
-      </c>
-      <c r="E63" s="1">
-        <f xml:space="preserve"> C63/C$2</f>
-        <v>8.9062500000000003E-2</v>
-      </c>
-      <c r="F63" s="1">
-        <f xml:space="preserve"> D63/D$2</f>
-        <v>0.25833333333333336</v>
-      </c>
-      <c r="G63" s="4">
-        <f>IF(ISBLANK(C63),0,(C63*G$2/C$2))</f>
-        <v>342</v>
-      </c>
-      <c r="H63" s="6">
-        <f>IF(ISBLANK(D63),0,(D63*H$2/D$2))</f>
-        <v>558</v>
-      </c>
-      <c r="J63" s="4">
-        <f>IF(ISBLANK(C63),0,(C63*J$2/C$2))</f>
-        <v>171</v>
-      </c>
-      <c r="K63" s="6">
-        <f>IF(ISBLANK(D63),0,(D63*K$2/D$2))</f>
-        <v>279</v>
-      </c>
-      <c r="M63" s="4">
-        <f>IF(ISBLANK(C63),0,(C63*M$2/C$2))</f>
-        <v>114</v>
-      </c>
-      <c r="N63" s="6">
-        <f>IF(ISBLANK(D63),0,(D63*N$2/D$2))</f>
-        <v>186</v>
-      </c>
-    </row>
-    <row r="64" spans="1:14">
-      <c r="E64" s="1">
-        <f xml:space="preserve"> C64/C$2</f>
-        <v>0</v>
-      </c>
-      <c r="F64" s="1">
-        <f xml:space="preserve"> D64/D$2</f>
-        <v>0</v>
-      </c>
-      <c r="G64" s="4">
-        <f>IF(ISBLANK(C64),0,(C64*G$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="H64" s="6">
-        <f>IF(ISBLANK(D64),0,(D64*H$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="J64" s="4">
-        <f>IF(ISBLANK(C64),0,(C64*J$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="K64" s="6">
-        <f>IF(ISBLANK(D64),0,(D64*K$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="M64" s="4">
-        <f>IF(ISBLANK(C64),0,(C64*M$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="N64" s="6">
-        <f>IF(ISBLANK(D64),0,(D64*N$2/D$2))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:14">
-      <c r="A65" t="s">
-        <v>5</v>
-      </c>
-      <c r="C65" s="4">
-        <v>1320</v>
-      </c>
-      <c r="D65" s="6">
-        <v>960</v>
-      </c>
-      <c r="E65" s="1">
-        <f xml:space="preserve"> C65/C$2</f>
-        <v>0.515625</v>
-      </c>
-      <c r="F65" s="1">
-        <f xml:space="preserve"> D65/D$2</f>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="G65" s="4">
-        <f>IF(ISBLANK(C65),0,(C65*G$2/C$2))</f>
-        <v>1980</v>
-      </c>
-      <c r="H65" s="6">
-        <f>IF(ISBLANK(D65),0,(D65*H$2/D$2))</f>
-        <v>1440</v>
-      </c>
-      <c r="J65" s="4">
-        <f>IF(ISBLANK(C65),0,(C65*J$2/C$2))</f>
-        <v>990</v>
-      </c>
-      <c r="K65" s="6">
-        <f>IF(ISBLANK(D65),0,(D65*K$2/D$2))</f>
-        <v>720</v>
-      </c>
-      <c r="M65" s="4">
-        <f>IF(ISBLANK(C65),0,(C65*M$2/C$2))</f>
-        <v>660</v>
-      </c>
-      <c r="N65" s="6">
-        <f>IF(ISBLANK(D65),0,(D65*N$2/D$2))</f>
-        <v>480</v>
-      </c>
-    </row>
-    <row r="66" spans="1:14">
-      <c r="E66" s="1">
-        <f xml:space="preserve"> C66/C$2</f>
-        <v>0</v>
-      </c>
-      <c r="F66" s="1">
-        <f xml:space="preserve"> D66/D$2</f>
-        <v>0</v>
-      </c>
-      <c r="G66" s="4">
-        <f>IF(ISBLANK(C66),0,(C66*G$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="H66" s="6">
-        <f>IF(ISBLANK(D66),0,(D66*H$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="J66" s="4">
-        <f>IF(ISBLANK(C66),0,(C66*J$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="K66" s="6">
-        <f>IF(ISBLANK(D66),0,(D66*K$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="M66" s="4">
-        <f>IF(ISBLANK(C66),0,(C66*M$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="N66" s="6">
-        <f>IF(ISBLANK(D66),0,(D66*N$2/D$2))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:14">
-      <c r="A67" t="s">
-        <v>18</v>
-      </c>
-      <c r="D67" s="6">
-        <v>82</v>
-      </c>
-      <c r="E67" s="1">
-        <f xml:space="preserve"> C67/C$2</f>
-        <v>0</v>
-      </c>
-      <c r="F67" s="1">
-        <f xml:space="preserve"> D67/D$2</f>
-        <v>5.6944444444444443E-2</v>
-      </c>
-      <c r="G67" s="4">
-        <f>IF(ISBLANK(C67),0,(C67*G$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="H67" s="6">
-        <f>IF(ISBLANK(D67),0,(D67*H$2/D$2))</f>
-        <v>123</v>
-      </c>
-      <c r="J67" s="4">
-        <f>IF(ISBLANK(C67),0,(C67*J$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="K67" s="6">
-        <f>IF(ISBLANK(D67),0,(D67*K$2/D$2))</f>
-        <v>61.5</v>
-      </c>
-      <c r="M67" s="4">
-        <f>IF(ISBLANK(C67),0,(C67*M$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="N67" s="6">
-        <f>IF(ISBLANK(D67),0,(D67*N$2/D$2))</f>
-        <v>41</v>
-      </c>
-    </row>
-    <row r="68" spans="1:14">
-      <c r="E68" s="1">
-        <f xml:space="preserve"> C68/C$2</f>
-        <v>0</v>
-      </c>
-      <c r="F68" s="1">
-        <f xml:space="preserve"> D68/D$2</f>
-        <v>0</v>
-      </c>
-      <c r="G68" s="4">
-        <f>IF(ISBLANK(C68),0,(C68*G$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="H68" s="6">
-        <f>IF(ISBLANK(D68),0,(D68*H$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="J68" s="4">
-        <f>IF(ISBLANK(C68),0,(C68*J$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="K68" s="6">
-        <f>IF(ISBLANK(D68),0,(D68*K$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="M68" s="4">
-        <f>IF(ISBLANK(C68),0,(C68*M$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="N68" s="6">
-        <f>IF(ISBLANK(D68),0,(D68*N$2/D$2))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:14">
-      <c r="A69" t="s">
-        <v>22</v>
-      </c>
-      <c r="C69" s="4">
-        <v>124</v>
-      </c>
-      <c r="D69" s="6">
-        <v>80</v>
-      </c>
-      <c r="E69" s="1">
-        <f xml:space="preserve"> C69/C$2</f>
-        <v>4.8437500000000001E-2</v>
-      </c>
-      <c r="F69" s="1">
-        <f xml:space="preserve"> D69/D$2</f>
-        <v>5.5555555555555552E-2</v>
-      </c>
-      <c r="G69" s="4">
-        <f>IF(ISBLANK(C69),0,(C69*G$2/C$2))</f>
-        <v>186</v>
-      </c>
-      <c r="H69" s="6">
-        <f>IF(ISBLANK(D69),0,(D69*H$2/D$2))</f>
-        <v>120</v>
-      </c>
-      <c r="J69" s="4">
-        <f>IF(ISBLANK(C69),0,(C69*J$2/C$2))</f>
-        <v>93</v>
-      </c>
-      <c r="K69" s="6">
-        <f>IF(ISBLANK(D69),0,(D69*K$2/D$2))</f>
-        <v>60</v>
-      </c>
-      <c r="M69" s="4">
-        <f>IF(ISBLANK(C69),0,(C69*M$2/C$2))</f>
-        <v>62</v>
-      </c>
-      <c r="N69" s="6">
-        <f>IF(ISBLANK(D69),0,(D69*N$2/D$2))</f>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="70" spans="1:14">
-      <c r="E70" s="1">
-        <f xml:space="preserve"> C70/C$2</f>
-        <v>0</v>
-      </c>
-      <c r="F70" s="1">
-        <f xml:space="preserve"> D70/D$2</f>
-        <v>0</v>
-      </c>
-      <c r="G70" s="4">
-        <f>IF(ISBLANK(C70),0,(C70*G$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="H70" s="6">
-        <f>IF(ISBLANK(D70),0,(D70*H$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="J70" s="4">
-        <f>IF(ISBLANK(C70),0,(C70*J$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="K70" s="6">
-        <f>IF(ISBLANK(D70),0,(D70*K$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="M70" s="4">
-        <f>IF(ISBLANK(C70),0,(C70*M$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="N70" s="6">
-        <f>IF(ISBLANK(D70),0,(D70*N$2/D$2))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:14">
-      <c r="A71" t="s">
-        <v>23</v>
-      </c>
-      <c r="C71" s="4">
-        <v>124</v>
-      </c>
-      <c r="D71" s="6">
-        <v>100</v>
-      </c>
-      <c r="E71" s="1">
-        <f xml:space="preserve"> C71/C$2</f>
-        <v>4.8437500000000001E-2</v>
-      </c>
-      <c r="F71" s="1">
-        <f xml:space="preserve"> D71/D$2</f>
-        <v>6.9444444444444448E-2</v>
-      </c>
-      <c r="G71" s="4">
-        <f>IF(ISBLANK(C71),0,(C71*G$2/C$2))</f>
-        <v>186</v>
-      </c>
-      <c r="H71" s="6">
-        <f>IF(ISBLANK(D71),0,(D71*H$2/D$2))</f>
-        <v>150</v>
-      </c>
-      <c r="J71" s="4">
-        <f>IF(ISBLANK(C71),0,(C71*J$2/C$2))</f>
-        <v>93</v>
-      </c>
-      <c r="K71" s="6">
-        <f>IF(ISBLANK(D71),0,(D71*K$2/D$2))</f>
-        <v>75</v>
-      </c>
-      <c r="M71" s="4">
-        <f>IF(ISBLANK(C71),0,(C71*M$2/C$2))</f>
-        <v>62</v>
-      </c>
-      <c r="N71" s="6">
-        <f>IF(ISBLANK(D71),0,(D71*N$2/D$2))</f>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="72" spans="1:14">
-      <c r="E72" s="1">
-        <f xml:space="preserve"> C72/C$2</f>
-        <v>0</v>
-      </c>
-      <c r="F72" s="1">
-        <f xml:space="preserve"> D72/D$2</f>
-        <v>0</v>
-      </c>
-      <c r="G72" s="4">
-        <f>IF(ISBLANK(C72),0,(C72*G$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="H72" s="6">
-        <f>IF(ISBLANK(D72),0,(D72*H$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="J72" s="4">
-        <f>IF(ISBLANK(C72),0,(C72*J$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="K72" s="6">
-        <f>IF(ISBLANK(D72),0,(D72*K$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="M72" s="4">
-        <f>IF(ISBLANK(C72),0,(C72*M$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="N72" s="6">
-        <f>IF(ISBLANK(D72),0,(D72*N$2/D$2))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:14">
-      <c r="A73" t="s">
-        <v>24</v>
-      </c>
-      <c r="C73" s="4">
-        <v>116</v>
-      </c>
-      <c r="D73" s="6">
-        <v>112</v>
-      </c>
-      <c r="E73" s="1">
-        <f xml:space="preserve"> C73/C$2</f>
-        <v>4.5312499999999999E-2</v>
-      </c>
-      <c r="F73" s="1">
-        <f xml:space="preserve"> D73/D$2</f>
-        <v>7.7777777777777779E-2</v>
-      </c>
-      <c r="G73" s="4">
-        <f>IF(ISBLANK(C73),0,(C73*G$2/C$2))</f>
-        <v>174</v>
-      </c>
-      <c r="H73" s="6">
-        <f>IF(ISBLANK(D73),0,(D73*H$2/D$2))</f>
-        <v>168</v>
-      </c>
-      <c r="J73" s="4">
-        <f>IF(ISBLANK(C73),0,(C73*J$2/C$2))</f>
-        <v>87</v>
-      </c>
-      <c r="K73" s="6">
-        <f>IF(ISBLANK(D73),0,(D73*K$2/D$2))</f>
-        <v>84</v>
-      </c>
-      <c r="M73" s="4">
-        <f>IF(ISBLANK(C73),0,(C73*M$2/C$2))</f>
-        <v>58</v>
-      </c>
-      <c r="N73" s="6">
-        <f>IF(ISBLANK(D73),0,(D73*N$2/D$2))</f>
-        <v>56</v>
-      </c>
-    </row>
-    <row r="74" spans="1:14">
-      <c r="E74" s="1">
-        <f xml:space="preserve"> C74/C$2</f>
-        <v>0</v>
-      </c>
-      <c r="F74" s="1">
-        <f xml:space="preserve"> D74/D$2</f>
-        <v>0</v>
-      </c>
-      <c r="G74" s="4">
-        <f>IF(ISBLANK(C74),0,(C74*G$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="H74" s="6">
-        <f>IF(ISBLANK(D74),0,(D74*H$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="J74" s="4">
-        <f>IF(ISBLANK(C74),0,(C74*J$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="K74" s="6">
-        <f>IF(ISBLANK(D74),0,(D74*K$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="M74" s="4">
-        <f>IF(ISBLANK(C74),0,(C74*M$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="N74" s="6">
-        <f>IF(ISBLANK(D74),0,(D74*N$2/D$2))</f>
-        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:14">
       <c r="E75" s="1">
-        <f xml:space="preserve"> C75/C$2</f>
+        <f t="shared" si="132"/>
         <v>0</v>
       </c>
       <c r="F75" s="1">
-        <f xml:space="preserve"> D75/D$2</f>
-        <v>0</v>
-      </c>
-      <c r="G75" s="4">
-        <f>IF(ISBLANK(C75),0,(C75*G$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="H75" s="6">
-        <f>IF(ISBLANK(D75),0,(D75*H$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="J75" s="4">
-        <f>IF(ISBLANK(C75),0,(C75*J$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="K75" s="6">
-        <f>IF(ISBLANK(D75),0,(D75*K$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="M75" s="4">
-        <f>IF(ISBLANK(C75),0,(C75*M$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="N75" s="6">
-        <f>IF(ISBLANK(D75),0,(D75*N$2/D$2))</f>
+        <f t="shared" si="133"/>
+        <v>0</v>
+      </c>
+      <c r="G75" s="3">
+        <f t="shared" si="134"/>
+        <v>0</v>
+      </c>
+      <c r="H75" s="5">
+        <f t="shared" si="135"/>
+        <v>0</v>
+      </c>
+      <c r="J75" s="3">
+        <f t="shared" si="136"/>
+        <v>0</v>
+      </c>
+      <c r="K75" s="5">
+        <f t="shared" si="137"/>
+        <v>0</v>
+      </c>
+      <c r="M75" s="3">
+        <f t="shared" si="138"/>
+        <v>0</v>
+      </c>
+      <c r="N75" s="5">
+        <f t="shared" si="139"/>
         <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:14">
       <c r="A76" t="s">
-        <v>26</v>
-      </c>
-      <c r="C76" s="4">
-        <v>280</v>
-      </c>
-      <c r="D76" s="6">
-        <v>84</v>
+        <v>17</v>
+      </c>
+      <c r="C76" s="3">
+        <v>228</v>
+      </c>
+      <c r="D76" s="5">
+        <v>372</v>
       </c>
       <c r="E76" s="1">
-        <f xml:space="preserve"> C76/C$2</f>
-        <v>0.109375</v>
+        <f t="shared" si="132"/>
+        <v>8.9062500000000003E-2</v>
       </c>
       <c r="F76" s="1">
-        <f xml:space="preserve"> D76/D$2</f>
-        <v>5.8333333333333334E-2</v>
-      </c>
-      <c r="G76" s="4">
-        <f>IF(ISBLANK(C76),0,(C76*G$2/C$2))</f>
-        <v>420</v>
-      </c>
-      <c r="H76" s="6">
-        <f>IF(ISBLANK(D76),0,(D76*H$2/D$2))</f>
-        <v>126</v>
-      </c>
-      <c r="J76" s="4">
-        <f>IF(ISBLANK(C76),0,(C76*J$2/C$2))</f>
-        <v>210</v>
-      </c>
-      <c r="K76" s="6">
-        <f>IF(ISBLANK(D76),0,(D76*K$2/D$2))</f>
-        <v>63</v>
-      </c>
-      <c r="M76" s="4">
-        <f>IF(ISBLANK(C76),0,(C76*M$2/C$2))</f>
-        <v>140</v>
-      </c>
-      <c r="N76" s="6">
-        <f>IF(ISBLANK(D76),0,(D76*N$2/D$2))</f>
-        <v>42</v>
+        <f t="shared" si="133"/>
+        <v>0.25833333333333336</v>
+      </c>
+      <c r="G76" s="3">
+        <f t="shared" si="134"/>
+        <v>342</v>
+      </c>
+      <c r="H76" s="5">
+        <f t="shared" si="135"/>
+        <v>558</v>
+      </c>
+      <c r="J76" s="3">
+        <f t="shared" si="136"/>
+        <v>171</v>
+      </c>
+      <c r="K76" s="5">
+        <f t="shared" si="137"/>
+        <v>279</v>
+      </c>
+      <c r="M76" s="3">
+        <f t="shared" si="138"/>
+        <v>114</v>
+      </c>
+      <c r="N76" s="5">
+        <f t="shared" si="139"/>
+        <v>186</v>
       </c>
     </row>
     <row r="77" spans="1:14">
       <c r="E77" s="1">
-        <f xml:space="preserve"> C77/C$2</f>
+        <f t="shared" si="132"/>
         <v>0</v>
       </c>
       <c r="F77" s="1">
-        <f xml:space="preserve"> D77/D$2</f>
-        <v>0</v>
-      </c>
-      <c r="G77" s="4">
-        <f>IF(ISBLANK(C77),0,(C77*G$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="H77" s="6">
-        <f>IF(ISBLANK(D77),0,(D77*H$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="J77" s="4">
-        <f>IF(ISBLANK(C77),0,(C77*J$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="K77" s="6">
-        <f>IF(ISBLANK(D77),0,(D77*K$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="M77" s="4">
-        <f>IF(ISBLANK(C77),0,(C77*M$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="N77" s="6">
-        <f>IF(ISBLANK(D77),0,(D77*N$2/D$2))</f>
+        <f t="shared" si="133"/>
+        <v>0</v>
+      </c>
+      <c r="G77" s="3">
+        <f t="shared" si="134"/>
+        <v>0</v>
+      </c>
+      <c r="H77" s="5">
+        <f t="shared" si="135"/>
+        <v>0</v>
+      </c>
+      <c r="J77" s="3">
+        <f t="shared" si="136"/>
+        <v>0</v>
+      </c>
+      <c r="K77" s="5">
+        <f t="shared" si="137"/>
+        <v>0</v>
+      </c>
+      <c r="M77" s="3">
+        <f t="shared" si="138"/>
+        <v>0</v>
+      </c>
+      <c r="N77" s="5">
+        <f t="shared" si="139"/>
         <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:14">
       <c r="A78" t="s">
+        <v>5</v>
+      </c>
+      <c r="C78" s="3">
+        <v>1320</v>
+      </c>
+      <c r="D78" s="5">
+        <v>960</v>
+      </c>
+      <c r="E78" s="1">
+        <f t="shared" si="132"/>
+        <v>0.515625</v>
+      </c>
+      <c r="F78" s="1">
+        <f t="shared" si="133"/>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="G78" s="3">
+        <f t="shared" si="134"/>
+        <v>1980</v>
+      </c>
+      <c r="H78" s="5">
+        <f t="shared" si="135"/>
+        <v>1440</v>
+      </c>
+      <c r="J78" s="3">
+        <f t="shared" si="136"/>
+        <v>990</v>
+      </c>
+      <c r="K78" s="5">
+        <f t="shared" si="137"/>
+        <v>720</v>
+      </c>
+      <c r="M78" s="3">
+        <f t="shared" si="138"/>
+        <v>660</v>
+      </c>
+      <c r="N78" s="5">
+        <f t="shared" si="139"/>
+        <v>480</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14">
+      <c r="E79" s="1">
+        <f t="shared" si="132"/>
+        <v>0</v>
+      </c>
+      <c r="F79" s="1">
+        <f t="shared" si="133"/>
+        <v>0</v>
+      </c>
+      <c r="G79" s="3">
+        <f t="shared" si="134"/>
+        <v>0</v>
+      </c>
+      <c r="H79" s="5">
+        <f t="shared" si="135"/>
+        <v>0</v>
+      </c>
+      <c r="J79" s="3">
+        <f t="shared" si="136"/>
+        <v>0</v>
+      </c>
+      <c r="K79" s="5">
+        <f t="shared" si="137"/>
+        <v>0</v>
+      </c>
+      <c r="M79" s="3">
+        <f t="shared" si="138"/>
+        <v>0</v>
+      </c>
+      <c r="N79" s="5">
+        <f t="shared" si="139"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14">
+      <c r="A80" t="s">
+        <v>18</v>
+      </c>
+      <c r="D80" s="5">
+        <v>82</v>
+      </c>
+      <c r="E80" s="1">
+        <f t="shared" si="132"/>
+        <v>0</v>
+      </c>
+      <c r="F80" s="1">
+        <f t="shared" si="133"/>
+        <v>5.6944444444444443E-2</v>
+      </c>
+      <c r="G80" s="3">
+        <f t="shared" si="134"/>
+        <v>0</v>
+      </c>
+      <c r="H80" s="5">
+        <f t="shared" si="135"/>
+        <v>123</v>
+      </c>
+      <c r="J80" s="3">
+        <f t="shared" si="136"/>
+        <v>0</v>
+      </c>
+      <c r="K80" s="5">
+        <f t="shared" si="137"/>
+        <v>61.5</v>
+      </c>
+      <c r="M80" s="3">
+        <f t="shared" si="138"/>
+        <v>0</v>
+      </c>
+      <c r="N80" s="5">
+        <f t="shared" si="139"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14">
+      <c r="E81" s="1">
+        <f t="shared" si="132"/>
+        <v>0</v>
+      </c>
+      <c r="F81" s="1">
+        <f t="shared" si="133"/>
+        <v>0</v>
+      </c>
+      <c r="G81" s="3">
+        <f t="shared" si="134"/>
+        <v>0</v>
+      </c>
+      <c r="H81" s="5">
+        <f t="shared" si="135"/>
+        <v>0</v>
+      </c>
+      <c r="J81" s="3">
+        <f t="shared" si="136"/>
+        <v>0</v>
+      </c>
+      <c r="K81" s="5">
+        <f t="shared" si="137"/>
+        <v>0</v>
+      </c>
+      <c r="M81" s="3">
+        <f t="shared" si="138"/>
+        <v>0</v>
+      </c>
+      <c r="N81" s="5">
+        <f t="shared" si="139"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14">
+      <c r="A82" t="s">
+        <v>22</v>
+      </c>
+      <c r="C82" s="3">
+        <v>124</v>
+      </c>
+      <c r="D82" s="5">
+        <v>80</v>
+      </c>
+      <c r="E82" s="1">
+        <f t="shared" si="132"/>
+        <v>4.8437500000000001E-2</v>
+      </c>
+      <c r="F82" s="1">
+        <f t="shared" si="133"/>
+        <v>5.5555555555555552E-2</v>
+      </c>
+      <c r="G82" s="3">
+        <f t="shared" si="134"/>
+        <v>186</v>
+      </c>
+      <c r="H82" s="5">
+        <f t="shared" si="135"/>
+        <v>120</v>
+      </c>
+      <c r="J82" s="3">
+        <f t="shared" si="136"/>
+        <v>93</v>
+      </c>
+      <c r="K82" s="5">
+        <f t="shared" si="137"/>
+        <v>60</v>
+      </c>
+      <c r="M82" s="3">
+        <f t="shared" si="138"/>
+        <v>62</v>
+      </c>
+      <c r="N82" s="5">
+        <f t="shared" si="139"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14">
+      <c r="E83" s="1">
+        <f t="shared" si="132"/>
+        <v>0</v>
+      </c>
+      <c r="F83" s="1">
+        <f t="shared" si="133"/>
+        <v>0</v>
+      </c>
+      <c r="G83" s="3">
+        <f t="shared" si="134"/>
+        <v>0</v>
+      </c>
+      <c r="H83" s="5">
+        <f t="shared" si="135"/>
+        <v>0</v>
+      </c>
+      <c r="J83" s="3">
+        <f t="shared" si="136"/>
+        <v>0</v>
+      </c>
+      <c r="K83" s="5">
+        <f t="shared" si="137"/>
+        <v>0</v>
+      </c>
+      <c r="M83" s="3">
+        <f t="shared" si="138"/>
+        <v>0</v>
+      </c>
+      <c r="N83" s="5">
+        <f t="shared" si="139"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14">
+      <c r="A84" t="s">
+        <v>23</v>
+      </c>
+      <c r="C84" s="3">
+        <v>124</v>
+      </c>
+      <c r="D84" s="5">
+        <v>100</v>
+      </c>
+      <c r="E84" s="1">
+        <f t="shared" si="132"/>
+        <v>4.8437500000000001E-2</v>
+      </c>
+      <c r="F84" s="1">
+        <f t="shared" si="133"/>
+        <v>6.9444444444444448E-2</v>
+      </c>
+      <c r="G84" s="3">
+        <f t="shared" si="134"/>
+        <v>186</v>
+      </c>
+      <c r="H84" s="5">
+        <f t="shared" si="135"/>
+        <v>150</v>
+      </c>
+      <c r="J84" s="3">
+        <f t="shared" si="136"/>
+        <v>93</v>
+      </c>
+      <c r="K84" s="5">
+        <f t="shared" si="137"/>
+        <v>75</v>
+      </c>
+      <c r="M84" s="3">
+        <f t="shared" si="138"/>
+        <v>62</v>
+      </c>
+      <c r="N84" s="5">
+        <f t="shared" si="139"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14">
+      <c r="E85" s="1">
+        <f t="shared" si="132"/>
+        <v>0</v>
+      </c>
+      <c r="F85" s="1">
+        <f t="shared" si="133"/>
+        <v>0</v>
+      </c>
+      <c r="G85" s="3">
+        <f t="shared" si="134"/>
+        <v>0</v>
+      </c>
+      <c r="H85" s="5">
+        <f t="shared" si="135"/>
+        <v>0</v>
+      </c>
+      <c r="J85" s="3">
+        <f t="shared" si="136"/>
+        <v>0</v>
+      </c>
+      <c r="K85" s="5">
+        <f t="shared" si="137"/>
+        <v>0</v>
+      </c>
+      <c r="M85" s="3">
+        <f t="shared" si="138"/>
+        <v>0</v>
+      </c>
+      <c r="N85" s="5">
+        <f t="shared" si="139"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14">
+      <c r="A86" t="s">
+        <v>24</v>
+      </c>
+      <c r="C86" s="3">
+        <v>116</v>
+      </c>
+      <c r="D86" s="5">
+        <v>112</v>
+      </c>
+      <c r="E86" s="1">
+        <f t="shared" si="132"/>
+        <v>4.5312499999999999E-2</v>
+      </c>
+      <c r="F86" s="1">
+        <f t="shared" si="133"/>
+        <v>7.7777777777777779E-2</v>
+      </c>
+      <c r="G86" s="3">
+        <f t="shared" si="134"/>
+        <v>174</v>
+      </c>
+      <c r="H86" s="5">
+        <f t="shared" si="135"/>
+        <v>168</v>
+      </c>
+      <c r="J86" s="3">
+        <f t="shared" si="136"/>
+        <v>87</v>
+      </c>
+      <c r="K86" s="5">
+        <f t="shared" si="137"/>
+        <v>84</v>
+      </c>
+      <c r="M86" s="3">
+        <f t="shared" si="138"/>
+        <v>58</v>
+      </c>
+      <c r="N86" s="5">
+        <f t="shared" si="139"/>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14">
+      <c r="E87" s="1">
+        <f t="shared" si="132"/>
+        <v>0</v>
+      </c>
+      <c r="F87" s="1">
+        <f t="shared" si="133"/>
+        <v>0</v>
+      </c>
+      <c r="G87" s="3">
+        <f t="shared" si="134"/>
+        <v>0</v>
+      </c>
+      <c r="H87" s="5">
+        <f t="shared" si="135"/>
+        <v>0</v>
+      </c>
+      <c r="J87" s="3">
+        <f t="shared" si="136"/>
+        <v>0</v>
+      </c>
+      <c r="K87" s="5">
+        <f t="shared" si="137"/>
+        <v>0</v>
+      </c>
+      <c r="M87" s="3">
+        <f t="shared" si="138"/>
+        <v>0</v>
+      </c>
+      <c r="N87" s="5">
+        <f t="shared" si="139"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14">
+      <c r="E88" s="1">
+        <f t="shared" si="132"/>
+        <v>0</v>
+      </c>
+      <c r="F88" s="1">
+        <f t="shared" si="133"/>
+        <v>0</v>
+      </c>
+      <c r="G88" s="3">
+        <f t="shared" si="134"/>
+        <v>0</v>
+      </c>
+      <c r="H88" s="5">
+        <f t="shared" si="135"/>
+        <v>0</v>
+      </c>
+      <c r="J88" s="3">
+        <f t="shared" si="136"/>
+        <v>0</v>
+      </c>
+      <c r="K88" s="5">
+        <f t="shared" si="137"/>
+        <v>0</v>
+      </c>
+      <c r="M88" s="3">
+        <f t="shared" si="138"/>
+        <v>0</v>
+      </c>
+      <c r="N88" s="5">
+        <f t="shared" si="139"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14">
+      <c r="A89" t="s">
+        <v>26</v>
+      </c>
+      <c r="C89" s="3">
+        <v>280</v>
+      </c>
+      <c r="D89" s="5">
+        <v>84</v>
+      </c>
+      <c r="E89" s="1">
+        <f t="shared" si="132"/>
+        <v>0.109375</v>
+      </c>
+      <c r="F89" s="1">
+        <f t="shared" si="133"/>
+        <v>5.8333333333333334E-2</v>
+      </c>
+      <c r="G89" s="3">
+        <f t="shared" si="134"/>
+        <v>420</v>
+      </c>
+      <c r="H89" s="5">
+        <f t="shared" si="135"/>
+        <v>126</v>
+      </c>
+      <c r="J89" s="3">
+        <f t="shared" si="136"/>
+        <v>210</v>
+      </c>
+      <c r="K89" s="5">
+        <f t="shared" si="137"/>
+        <v>63</v>
+      </c>
+      <c r="M89" s="3">
+        <f t="shared" si="138"/>
+        <v>140</v>
+      </c>
+      <c r="N89" s="5">
+        <f t="shared" si="139"/>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14">
+      <c r="E90" s="1">
+        <f t="shared" si="132"/>
+        <v>0</v>
+      </c>
+      <c r="F90" s="1">
+        <f t="shared" si="133"/>
+        <v>0</v>
+      </c>
+      <c r="G90" s="3">
+        <f t="shared" si="134"/>
+        <v>0</v>
+      </c>
+      <c r="H90" s="5">
+        <f t="shared" si="135"/>
+        <v>0</v>
+      </c>
+      <c r="J90" s="3">
+        <f t="shared" si="136"/>
+        <v>0</v>
+      </c>
+      <c r="K90" s="5">
+        <f t="shared" si="137"/>
+        <v>0</v>
+      </c>
+      <c r="M90" s="3">
+        <f t="shared" si="138"/>
+        <v>0</v>
+      </c>
+      <c r="N90" s="5">
+        <f t="shared" si="139"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14">
+      <c r="A91" t="s">
         <v>27</v>
       </c>
-      <c r="C78" s="4">
+      <c r="C91" s="3">
         <v>660</v>
       </c>
-      <c r="D78" s="6">
+      <c r="D91" s="5">
         <v>140</v>
       </c>
-      <c r="E78" s="1">
-        <f xml:space="preserve"> C78/C$2</f>
+      <c r="E91" s="1">
+        <f t="shared" si="132"/>
         <v>0.2578125</v>
       </c>
-      <c r="F78" s="1">
-        <f xml:space="preserve"> D78/D$2</f>
+      <c r="F91" s="1">
+        <f t="shared" si="133"/>
         <v>9.7222222222222224E-2</v>
       </c>
-      <c r="G78" s="4">
-        <f>IF(ISBLANK(C78),0,(C78*G$2/C$2))</f>
+      <c r="G91" s="3">
+        <f t="shared" si="134"/>
         <v>990</v>
       </c>
-      <c r="H78" s="6">
-        <f>IF(ISBLANK(D78),0,(D78*H$2/D$2))</f>
+      <c r="H91" s="5">
+        <f t="shared" si="135"/>
         <v>210</v>
       </c>
-      <c r="J78" s="4">
-        <f>IF(ISBLANK(C78),0,(C78*J$2/C$2))</f>
+      <c r="J91" s="3">
+        <f t="shared" si="136"/>
         <v>495</v>
       </c>
-      <c r="K78" s="6">
-        <f>IF(ISBLANK(D78),0,(D78*K$2/D$2))</f>
+      <c r="K91" s="5">
+        <f t="shared" si="137"/>
         <v>105</v>
       </c>
-      <c r="M78" s="4">
-        <f>IF(ISBLANK(C78),0,(C78*M$2/C$2))</f>
+      <c r="M91" s="3">
+        <f t="shared" si="138"/>
         <v>330</v>
       </c>
-      <c r="N78" s="6">
-        <f>IF(ISBLANK(D78),0,(D78*N$2/D$2))</f>
+      <c r="N91" s="5">
+        <f t="shared" si="139"/>
         <v>70</v>
       </c>
     </row>
-    <row r="79" spans="1:14">
-      <c r="A79" t="s">
+    <row r="92" spans="1:14">
+      <c r="A92" t="s">
         <v>28</v>
       </c>
-      <c r="C79" s="4">
+      <c r="C92" s="3">
         <v>560</v>
       </c>
-      <c r="D79" s="6">
+      <c r="D92" s="5">
         <v>46</v>
       </c>
-      <c r="E79" s="1">
-        <f xml:space="preserve"> C79/C$2</f>
+      <c r="E92" s="1">
+        <f t="shared" si="132"/>
         <v>0.21875</v>
       </c>
-      <c r="F79" s="1">
-        <f xml:space="preserve"> D79/D$2</f>
+      <c r="F92" s="1">
+        <f t="shared" si="133"/>
         <v>3.1944444444444442E-2</v>
       </c>
-      <c r="G79" s="4">
-        <f>IF(ISBLANK(C79),0,(C79*G$2/C$2))</f>
+      <c r="G92" s="3">
+        <f t="shared" si="134"/>
         <v>840</v>
       </c>
-      <c r="H79" s="6">
-        <f>IF(ISBLANK(D79),0,(D79*H$2/D$2))</f>
+      <c r="H92" s="5">
+        <f t="shared" si="135"/>
         <v>69</v>
       </c>
-      <c r="J79" s="4">
-        <f>IF(ISBLANK(C79),0,(C79*J$2/C$2))</f>
+      <c r="J92" s="3">
+        <f t="shared" si="136"/>
         <v>420</v>
       </c>
-      <c r="K79" s="6">
-        <f>IF(ISBLANK(D79),0,(D79*K$2/D$2))</f>
+      <c r="K92" s="5">
+        <f t="shared" si="137"/>
         <v>34.5</v>
       </c>
-      <c r="M79" s="4">
-        <f>IF(ISBLANK(C79),0,(C79*M$2/C$2))</f>
+      <c r="M92" s="3">
+        <f t="shared" si="138"/>
         <v>280</v>
       </c>
-      <c r="N79" s="6">
-        <f>IF(ISBLANK(D79),0,(D79*N$2/D$2))</f>
+      <c r="N92" s="5">
+        <f t="shared" si="139"/>
         <v>23</v>
       </c>
     </row>
-    <row r="80" spans="1:14">
-      <c r="E80" s="1">
-        <f xml:space="preserve"> C80/C$2</f>
-        <v>0</v>
-      </c>
-      <c r="F80" s="1">
-        <f xml:space="preserve"> D80/D$2</f>
-        <v>0</v>
-      </c>
-      <c r="G80" s="4">
-        <f>IF(ISBLANK(C80),0,(C80*G$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="H80" s="6">
-        <f>IF(ISBLANK(D80),0,(D80*H$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="J80" s="4">
-        <f>IF(ISBLANK(C80),0,(C80*J$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="K80" s="6">
-        <f>IF(ISBLANK(D80),0,(D80*K$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="M80" s="4">
-        <f>IF(ISBLANK(C80),0,(C80*M$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="N80" s="6">
-        <f>IF(ISBLANK(D80),0,(D80*N$2/D$2))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="5:14">
-      <c r="E81" s="1">
-        <f xml:space="preserve"> C81/C$2</f>
-        <v>0</v>
-      </c>
-      <c r="F81" s="1">
-        <f xml:space="preserve"> D81/D$2</f>
-        <v>0</v>
-      </c>
-      <c r="G81" s="4">
-        <f>IF(ISBLANK(C81),0,(C81*G$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="H81" s="6">
-        <f>IF(ISBLANK(D81),0,(D81*H$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="J81" s="4">
-        <f>IF(ISBLANK(C81),0,(C81*J$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="K81" s="6">
-        <f>IF(ISBLANK(D81),0,(D81*K$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="M81" s="4">
-        <f>IF(ISBLANK(C81),0,(C81*M$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="N81" s="6">
-        <f>IF(ISBLANK(D81),0,(D81*N$2/D$2))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="5:14">
-      <c r="E82" s="1">
-        <f xml:space="preserve"> C82/C$2</f>
-        <v>0</v>
-      </c>
-      <c r="F82" s="1">
-        <f xml:space="preserve"> D82/D$2</f>
-        <v>0</v>
-      </c>
-      <c r="G82" s="4">
-        <f>IF(ISBLANK(C82),0,(C82*G$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="H82" s="6">
-        <f>IF(ISBLANK(D82),0,(D82*H$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="J82" s="4">
-        <f>IF(ISBLANK(C82),0,(C82*J$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="K82" s="6">
-        <f>IF(ISBLANK(D82),0,(D82*K$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="M82" s="4">
-        <f>IF(ISBLANK(C82),0,(C82*M$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="N82" s="6">
-        <f>IF(ISBLANK(D82),0,(D82*N$2/D$2))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="5:14">
-      <c r="E83" s="1">
-        <f xml:space="preserve"> C83/C$2</f>
-        <v>0</v>
-      </c>
-      <c r="F83" s="1">
-        <f xml:space="preserve"> D83/D$2</f>
-        <v>0</v>
-      </c>
-      <c r="G83" s="4">
-        <f>IF(ISBLANK(C83),0,(C83*G$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="H83" s="6">
-        <f>IF(ISBLANK(D83),0,(D83*H$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="J83" s="4">
-        <f>IF(ISBLANK(C83),0,(C83*J$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="K83" s="6">
-        <f>IF(ISBLANK(D83),0,(D83*K$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="M83" s="4">
-        <f>IF(ISBLANK(C83),0,(C83*M$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="N83" s="6">
-        <f>IF(ISBLANK(D83),0,(D83*N$2/D$2))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="5:14">
-      <c r="E84" s="1">
-        <f xml:space="preserve"> C84/C$2</f>
-        <v>0</v>
-      </c>
-      <c r="F84" s="1">
-        <f xml:space="preserve"> D84/D$2</f>
-        <v>0</v>
-      </c>
-      <c r="G84" s="4">
-        <f>IF(ISBLANK(C84),0,(C84*G$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="H84" s="6">
-        <f>IF(ISBLANK(D84),0,(D84*H$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="J84" s="4">
-        <f>IF(ISBLANK(C84),0,(C84*J$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="K84" s="6">
-        <f>IF(ISBLANK(D84),0,(D84*K$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="M84" s="4">
-        <f>IF(ISBLANK(C84),0,(C84*M$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="N84" s="6">
-        <f>IF(ISBLANK(D84),0,(D84*N$2/D$2))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="5:14">
-      <c r="E85" s="1">
-        <f xml:space="preserve"> C85/C$2</f>
-        <v>0</v>
-      </c>
-      <c r="F85" s="1">
-        <f xml:space="preserve"> D85/D$2</f>
-        <v>0</v>
-      </c>
-      <c r="G85" s="4">
-        <f>IF(ISBLANK(C85),0,(C85*G$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="H85" s="6">
-        <f>IF(ISBLANK(D85),0,(D85*H$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="J85" s="4">
-        <f>IF(ISBLANK(C85),0,(C85*J$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="K85" s="6">
-        <f>IF(ISBLANK(D85),0,(D85*K$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="M85" s="4">
-        <f>IF(ISBLANK(C85),0,(C85*M$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="N85" s="6">
-        <f>IF(ISBLANK(D85),0,(D85*N$2/D$2))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="5:14">
-      <c r="E86" s="1">
-        <f xml:space="preserve"> C86/C$2</f>
-        <v>0</v>
-      </c>
-      <c r="F86" s="1">
-        <f xml:space="preserve"> D86/D$2</f>
-        <v>0</v>
-      </c>
-      <c r="G86" s="4">
-        <f>IF(ISBLANK(C86),0,(C86*G$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="H86" s="6">
-        <f>IF(ISBLANK(D86),0,(D86*H$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="J86" s="4">
-        <f>IF(ISBLANK(C86),0,(C86*J$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="K86" s="6">
-        <f>IF(ISBLANK(D86),0,(D86*K$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="M86" s="4">
-        <f>IF(ISBLANK(C86),0,(C86*M$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="N86" s="6">
-        <f>IF(ISBLANK(D86),0,(D86*N$2/D$2))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="5:14">
-      <c r="E87" s="1">
-        <f xml:space="preserve"> C87/C$2</f>
-        <v>0</v>
-      </c>
-      <c r="F87" s="1">
-        <f xml:space="preserve"> D87/D$2</f>
-        <v>0</v>
-      </c>
-      <c r="G87" s="4">
-        <f>IF(ISBLANK(C87),0,(C87*G$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="H87" s="6">
-        <f>IF(ISBLANK(D87),0,(D87*H$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="J87" s="4">
-        <f>IF(ISBLANK(C87),0,(C87*J$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="K87" s="6">
-        <f>IF(ISBLANK(D87),0,(D87*K$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="M87" s="4">
-        <f>IF(ISBLANK(C87),0,(C87*M$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="N87" s="6">
-        <f>IF(ISBLANK(D87),0,(D87*N$2/D$2))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="5:14">
-      <c r="E88" s="1">
-        <f xml:space="preserve"> C88/C$2</f>
-        <v>0</v>
-      </c>
-      <c r="F88" s="1">
-        <f xml:space="preserve"> D88/D$2</f>
-        <v>0</v>
-      </c>
-      <c r="G88" s="4">
-        <f>IF(ISBLANK(C88),0,(C88*G$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="H88" s="6">
-        <f>IF(ISBLANK(D88),0,(D88*H$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="J88" s="4">
-        <f>IF(ISBLANK(C88),0,(C88*J$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="K88" s="6">
-        <f>IF(ISBLANK(D88),0,(D88*K$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="M88" s="4">
-        <f>IF(ISBLANK(C88),0,(C88*M$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="N88" s="6">
-        <f>IF(ISBLANK(D88),0,(D88*N$2/D$2))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="5:14">
-      <c r="E89" s="1">
-        <f xml:space="preserve"> C89/C$2</f>
-        <v>0</v>
-      </c>
-      <c r="F89" s="1">
-        <f xml:space="preserve"> D89/D$2</f>
-        <v>0</v>
-      </c>
-      <c r="G89" s="4">
-        <f>IF(ISBLANK(C89),0,(C89*G$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="H89" s="6">
-        <f>IF(ISBLANK(D89),0,(D89*H$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="J89" s="4">
-        <f>IF(ISBLANK(C89),0,(C89*J$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="K89" s="6">
-        <f>IF(ISBLANK(D89),0,(D89*K$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="M89" s="4">
-        <f>IF(ISBLANK(C89),0,(C89*M$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="N89" s="6">
-        <f>IF(ISBLANK(D89),0,(D89*N$2/D$2))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="5:14">
-      <c r="E90" s="1">
-        <f xml:space="preserve"> C90/C$2</f>
-        <v>0</v>
-      </c>
-      <c r="F90" s="1">
-        <f xml:space="preserve"> D90/D$2</f>
-        <v>0</v>
-      </c>
-      <c r="G90" s="4">
-        <f>IF(ISBLANK(C90),0,(C90*G$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="H90" s="6">
-        <f>IF(ISBLANK(D90),0,(D90*H$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="J90" s="4">
-        <f>IF(ISBLANK(C90),0,(C90*J$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="K90" s="6">
-        <f>IF(ISBLANK(D90),0,(D90*K$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="M90" s="4">
-        <f>IF(ISBLANK(C90),0,(C90*M$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="N90" s="6">
-        <f>IF(ISBLANK(D90),0,(D90*N$2/D$2))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="5:14">
-      <c r="E91" s="1">
-        <f xml:space="preserve"> C91/C$2</f>
-        <v>0</v>
-      </c>
-      <c r="F91" s="1">
-        <f xml:space="preserve"> D91/D$2</f>
-        <v>0</v>
-      </c>
-      <c r="G91" s="4">
-        <f>IF(ISBLANK(C91),0,(C91*G$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="H91" s="6">
-        <f>IF(ISBLANK(D91),0,(D91*H$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="J91" s="4">
-        <f>IF(ISBLANK(C91),0,(C91*J$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="K91" s="6">
-        <f>IF(ISBLANK(D91),0,(D91*K$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="M91" s="4">
-        <f>IF(ISBLANK(C91),0,(C91*M$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="N91" s="6">
-        <f>IF(ISBLANK(D91),0,(D91*N$2/D$2))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="5:14">
-      <c r="E92" s="1">
-        <f xml:space="preserve"> C92/C$2</f>
-        <v>0</v>
-      </c>
-      <c r="F92" s="1">
-        <f xml:space="preserve"> D92/D$2</f>
-        <v>0</v>
-      </c>
-      <c r="G92" s="4">
-        <f>IF(ISBLANK(C92),0,(C92*G$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="H92" s="6">
-        <f>IF(ISBLANK(D92),0,(D92*H$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="J92" s="4">
-        <f>IF(ISBLANK(C92),0,(C92*J$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="K92" s="6">
-        <f>IF(ISBLANK(D92),0,(D92*K$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="M92" s="4">
-        <f>IF(ISBLANK(C92),0,(C92*M$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="N92" s="6">
-        <f>IF(ISBLANK(D92),0,(D92*N$2/D$2))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="5:14">
+    <row r="93" spans="1:14">
       <c r="E93" s="1">
-        <f xml:space="preserve"> C93/C$2</f>
+        <f t="shared" si="132"/>
         <v>0</v>
       </c>
       <c r="F93" s="1">
-        <f xml:space="preserve"> D93/D$2</f>
-        <v>0</v>
-      </c>
-      <c r="G93" s="4">
-        <f>IF(ISBLANK(C93),0,(C93*G$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="H93" s="6">
-        <f>IF(ISBLANK(D93),0,(D93*H$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="J93" s="4">
-        <f>IF(ISBLANK(C93),0,(C93*J$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="K93" s="6">
-        <f>IF(ISBLANK(D93),0,(D93*K$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="M93" s="4">
-        <f>IF(ISBLANK(C93),0,(C93*M$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="N93" s="6">
-        <f>IF(ISBLANK(D93),0,(D93*N$2/D$2))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="5:14">
+        <f t="shared" si="133"/>
+        <v>0</v>
+      </c>
+      <c r="G93" s="3">
+        <f t="shared" si="134"/>
+        <v>0</v>
+      </c>
+      <c r="H93" s="5">
+        <f t="shared" si="135"/>
+        <v>0</v>
+      </c>
+      <c r="J93" s="3">
+        <f t="shared" si="136"/>
+        <v>0</v>
+      </c>
+      <c r="K93" s="5">
+        <f t="shared" si="137"/>
+        <v>0</v>
+      </c>
+      <c r="M93" s="3">
+        <f t="shared" si="138"/>
+        <v>0</v>
+      </c>
+      <c r="N93" s="5">
+        <f t="shared" si="139"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14">
       <c r="E94" s="1">
-        <f xml:space="preserve"> C94/C$2</f>
+        <f t="shared" si="132"/>
         <v>0</v>
       </c>
       <c r="F94" s="1">
-        <f xml:space="preserve"> D94/D$2</f>
-        <v>0</v>
-      </c>
-      <c r="G94" s="4">
-        <f>IF(ISBLANK(C94),0,(C94*G$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="H94" s="6">
-        <f>IF(ISBLANK(D94),0,(D94*H$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="J94" s="4">
-        <f>IF(ISBLANK(C94),0,(C94*J$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="K94" s="6">
-        <f>IF(ISBLANK(D94),0,(D94*K$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="M94" s="4">
-        <f>IF(ISBLANK(C94),0,(C94*M$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="N94" s="6">
-        <f>IF(ISBLANK(D94),0,(D94*N$2/D$2))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="5:14">
+        <f t="shared" si="133"/>
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
+        <f t="shared" si="134"/>
+        <v>0</v>
+      </c>
+      <c r="H94" s="5">
+        <f t="shared" si="135"/>
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
+        <f t="shared" si="136"/>
+        <v>0</v>
+      </c>
+      <c r="K94" s="5">
+        <f t="shared" si="137"/>
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
+        <f t="shared" si="138"/>
+        <v>0</v>
+      </c>
+      <c r="N94" s="5">
+        <f t="shared" si="139"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:14">
       <c r="E95" s="1">
-        <f xml:space="preserve"> C95/C$2</f>
+        <f t="shared" si="132"/>
         <v>0</v>
       </c>
       <c r="F95" s="1">
-        <f xml:space="preserve"> D95/D$2</f>
-        <v>0</v>
-      </c>
-      <c r="G95" s="4">
-        <f>IF(ISBLANK(C95),0,(C95*G$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="H95" s="6">
-        <f>IF(ISBLANK(D95),0,(D95*H$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="J95" s="4">
-        <f>IF(ISBLANK(C95),0,(C95*J$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="K95" s="6">
-        <f>IF(ISBLANK(D95),0,(D95*K$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="M95" s="4">
-        <f>IF(ISBLANK(C95),0,(C95*M$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="N95" s="6">
-        <f>IF(ISBLANK(D95),0,(D95*N$2/D$2))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="5:14">
+        <f t="shared" si="133"/>
+        <v>0</v>
+      </c>
+      <c r="G95" s="3">
+        <f t="shared" si="134"/>
+        <v>0</v>
+      </c>
+      <c r="H95" s="5">
+        <f t="shared" si="135"/>
+        <v>0</v>
+      </c>
+      <c r="J95" s="3">
+        <f t="shared" si="136"/>
+        <v>0</v>
+      </c>
+      <c r="K95" s="5">
+        <f t="shared" si="137"/>
+        <v>0</v>
+      </c>
+      <c r="M95" s="3">
+        <f t="shared" si="138"/>
+        <v>0</v>
+      </c>
+      <c r="N95" s="5">
+        <f t="shared" si="139"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14">
       <c r="E96" s="1">
-        <f xml:space="preserve"> C96/C$2</f>
+        <f t="shared" si="132"/>
         <v>0</v>
       </c>
       <c r="F96" s="1">
-        <f xml:space="preserve"> D96/D$2</f>
-        <v>0</v>
-      </c>
-      <c r="G96" s="4">
-        <f>IF(ISBLANK(C96),0,(C96*G$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="H96" s="6">
-        <f>IF(ISBLANK(D96),0,(D96*H$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="J96" s="4">
-        <f>IF(ISBLANK(C96),0,(C96*J$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="K96" s="6">
-        <f>IF(ISBLANK(D96),0,(D96*K$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="M96" s="4">
-        <f>IF(ISBLANK(C96),0,(C96*M$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="N96" s="6">
-        <f>IF(ISBLANK(D96),0,(D96*N$2/D$2))</f>
+        <f t="shared" si="133"/>
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
+        <f t="shared" si="134"/>
+        <v>0</v>
+      </c>
+      <c r="H96" s="5">
+        <f t="shared" si="135"/>
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
+        <f t="shared" si="136"/>
+        <v>0</v>
+      </c>
+      <c r="K96" s="5">
+        <f t="shared" si="137"/>
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
+        <f t="shared" si="138"/>
+        <v>0</v>
+      </c>
+      <c r="N96" s="5">
+        <f t="shared" si="139"/>
         <v>0</v>
       </c>
     </row>
     <row r="97" spans="5:14">
       <c r="E97" s="1">
-        <f xml:space="preserve"> C97/C$2</f>
+        <f t="shared" si="132"/>
         <v>0</v>
       </c>
       <c r="F97" s="1">
-        <f xml:space="preserve"> D97/D$2</f>
-        <v>0</v>
-      </c>
-      <c r="G97" s="4">
-        <f>IF(ISBLANK(C97),0,(C97*G$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="H97" s="6">
-        <f>IF(ISBLANK(D97),0,(D97*H$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="J97" s="4">
-        <f>IF(ISBLANK(C97),0,(C97*J$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="K97" s="6">
-        <f>IF(ISBLANK(D97),0,(D97*K$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="M97" s="4">
-        <f>IF(ISBLANK(C97),0,(C97*M$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="N97" s="6">
-        <f>IF(ISBLANK(D97),0,(D97*N$2/D$2))</f>
+        <f t="shared" si="133"/>
+        <v>0</v>
+      </c>
+      <c r="G97" s="3">
+        <f t="shared" si="134"/>
+        <v>0</v>
+      </c>
+      <c r="H97" s="5">
+        <f t="shared" si="135"/>
+        <v>0</v>
+      </c>
+      <c r="J97" s="3">
+        <f t="shared" si="136"/>
+        <v>0</v>
+      </c>
+      <c r="K97" s="5">
+        <f t="shared" si="137"/>
+        <v>0</v>
+      </c>
+      <c r="M97" s="3">
+        <f t="shared" si="138"/>
+        <v>0</v>
+      </c>
+      <c r="N97" s="5">
+        <f t="shared" si="139"/>
         <v>0</v>
       </c>
     </row>
     <row r="98" spans="5:14">
       <c r="E98" s="1">
-        <f xml:space="preserve"> C98/C$2</f>
+        <f t="shared" si="132"/>
         <v>0</v>
       </c>
       <c r="F98" s="1">
-        <f xml:space="preserve"> D98/D$2</f>
-        <v>0</v>
-      </c>
-      <c r="G98" s="4">
-        <f>IF(ISBLANK(C98),0,(C98*G$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="H98" s="6">
-        <f>IF(ISBLANK(D98),0,(D98*H$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="J98" s="4">
-        <f>IF(ISBLANK(C98),0,(C98*J$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="K98" s="6">
-        <f>IF(ISBLANK(D98),0,(D98*K$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="M98" s="4">
-        <f>IF(ISBLANK(C98),0,(C98*M$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="N98" s="6">
-        <f>IF(ISBLANK(D98),0,(D98*N$2/D$2))</f>
+        <f t="shared" si="133"/>
+        <v>0</v>
+      </c>
+      <c r="G98" s="3">
+        <f t="shared" si="134"/>
+        <v>0</v>
+      </c>
+      <c r="H98" s="5">
+        <f t="shared" si="135"/>
+        <v>0</v>
+      </c>
+      <c r="J98" s="3">
+        <f t="shared" si="136"/>
+        <v>0</v>
+      </c>
+      <c r="K98" s="5">
+        <f t="shared" si="137"/>
+        <v>0</v>
+      </c>
+      <c r="M98" s="3">
+        <f t="shared" si="138"/>
+        <v>0</v>
+      </c>
+      <c r="N98" s="5">
+        <f t="shared" si="139"/>
         <v>0</v>
       </c>
     </row>
     <row r="99" spans="5:14">
       <c r="E99" s="1">
-        <f xml:space="preserve"> C99/C$2</f>
+        <f t="shared" si="132"/>
         <v>0</v>
       </c>
       <c r="F99" s="1">
-        <f xml:space="preserve"> D99/D$2</f>
-        <v>0</v>
-      </c>
-      <c r="G99" s="4">
-        <f>IF(ISBLANK(C99),0,(C99*G$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="H99" s="6">
-        <f>IF(ISBLANK(D99),0,(D99*H$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="J99" s="4">
-        <f>IF(ISBLANK(C99),0,(C99*J$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="K99" s="6">
-        <f>IF(ISBLANK(D99),0,(D99*K$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="M99" s="4">
-        <f>IF(ISBLANK(C99),0,(C99*M$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="N99" s="6">
-        <f>IF(ISBLANK(D99),0,(D99*N$2/D$2))</f>
+        <f t="shared" si="133"/>
+        <v>0</v>
+      </c>
+      <c r="G99" s="3">
+        <f t="shared" si="134"/>
+        <v>0</v>
+      </c>
+      <c r="H99" s="5">
+        <f t="shared" si="135"/>
+        <v>0</v>
+      </c>
+      <c r="J99" s="3">
+        <f t="shared" si="136"/>
+        <v>0</v>
+      </c>
+      <c r="K99" s="5">
+        <f t="shared" si="137"/>
+        <v>0</v>
+      </c>
+      <c r="M99" s="3">
+        <f t="shared" si="138"/>
+        <v>0</v>
+      </c>
+      <c r="N99" s="5">
+        <f t="shared" si="139"/>
         <v>0</v>
       </c>
     </row>
     <row r="100" spans="5:14">
       <c r="E100" s="1">
-        <f xml:space="preserve"> C100/C$2</f>
+        <f t="shared" si="132"/>
         <v>0</v>
       </c>
       <c r="F100" s="1">
-        <f xml:space="preserve"> D100/D$2</f>
-        <v>0</v>
-      </c>
-      <c r="G100" s="4">
-        <f>IF(ISBLANK(C100),0,(C100*G$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="H100" s="6">
-        <f>IF(ISBLANK(D100),0,(D100*H$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="J100" s="4">
-        <f>IF(ISBLANK(C100),0,(C100*J$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="K100" s="6">
-        <f>IF(ISBLANK(D100),0,(D100*K$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="M100" s="4">
-        <f>IF(ISBLANK(C100),0,(C100*M$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="N100" s="6">
-        <f>IF(ISBLANK(D100),0,(D100*N$2/D$2))</f>
+        <f t="shared" si="133"/>
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
+        <f t="shared" si="134"/>
+        <v>0</v>
+      </c>
+      <c r="H100" s="5">
+        <f t="shared" si="135"/>
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
+        <f t="shared" si="136"/>
+        <v>0</v>
+      </c>
+      <c r="K100" s="5">
+        <f t="shared" si="137"/>
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
+        <f t="shared" si="138"/>
+        <v>0</v>
+      </c>
+      <c r="N100" s="5">
+        <f t="shared" si="139"/>
         <v>0</v>
       </c>
     </row>
     <row r="101" spans="5:14">
       <c r="E101" s="1">
-        <f t="shared" ref="E101:E111" si="112" xml:space="preserve"> C101/C$2</f>
+        <f t="shared" si="132"/>
         <v>0</v>
       </c>
       <c r="F101" s="1">
-        <f t="shared" ref="F101:F111" si="113" xml:space="preserve"> D101/D$2</f>
-        <v>0</v>
-      </c>
-      <c r="G101" s="4">
-        <f t="shared" ref="G101:G111" si="114">IF(ISBLANK(C101),0,(C101*G$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="H101" s="6">
-        <f t="shared" ref="H101:H111" si="115">IF(ISBLANK(D101),0,(D101*H$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="J101" s="4">
-        <f t="shared" ref="J101:J111" si="116">IF(ISBLANK(C101),0,(C101*J$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="K101" s="6">
-        <f t="shared" ref="K101:K111" si="117">IF(ISBLANK(D101),0,(D101*K$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="M101" s="4">
-        <f t="shared" ref="M101:M111" si="118">IF(ISBLANK(C101),0,(C101*M$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="N101" s="6">
-        <f t="shared" ref="N101:N111" si="119">IF(ISBLANK(D101),0,(D101*N$2/D$2))</f>
+        <f t="shared" si="133"/>
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
+        <f t="shared" si="134"/>
+        <v>0</v>
+      </c>
+      <c r="H101" s="5">
+        <f t="shared" si="135"/>
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
+        <f t="shared" si="136"/>
+        <v>0</v>
+      </c>
+      <c r="K101" s="5">
+        <f t="shared" si="137"/>
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
+        <f t="shared" si="138"/>
+        <v>0</v>
+      </c>
+      <c r="N101" s="5">
+        <f t="shared" si="139"/>
         <v>0</v>
       </c>
     </row>
     <row r="102" spans="5:14">
       <c r="E102" s="1">
-        <f t="shared" si="112"/>
+        <f t="shared" si="132"/>
         <v>0</v>
       </c>
       <c r="F102" s="1">
-        <f t="shared" si="113"/>
-        <v>0</v>
-      </c>
-      <c r="G102" s="4">
-        <f t="shared" si="114"/>
-        <v>0</v>
-      </c>
-      <c r="H102" s="6">
-        <f t="shared" si="115"/>
-        <v>0</v>
-      </c>
-      <c r="J102" s="4">
-        <f t="shared" si="116"/>
-        <v>0</v>
-      </c>
-      <c r="K102" s="6">
-        <f t="shared" si="117"/>
-        <v>0</v>
-      </c>
-      <c r="M102" s="4">
-        <f t="shared" si="118"/>
-        <v>0</v>
-      </c>
-      <c r="N102" s="6">
-        <f t="shared" si="119"/>
+        <f t="shared" si="133"/>
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
+        <f t="shared" si="134"/>
+        <v>0</v>
+      </c>
+      <c r="H102" s="5">
+        <f t="shared" si="135"/>
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
+        <f t="shared" si="136"/>
+        <v>0</v>
+      </c>
+      <c r="K102" s="5">
+        <f t="shared" si="137"/>
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
+        <f t="shared" si="138"/>
+        <v>0</v>
+      </c>
+      <c r="N102" s="5">
+        <f t="shared" si="139"/>
         <v>0</v>
       </c>
     </row>
     <row r="103" spans="5:14">
       <c r="E103" s="1">
-        <f t="shared" si="112"/>
+        <f t="shared" si="132"/>
         <v>0</v>
       </c>
       <c r="F103" s="1">
-        <f t="shared" si="113"/>
-        <v>0</v>
-      </c>
-      <c r="G103" s="4">
-        <f t="shared" si="114"/>
-        <v>0</v>
-      </c>
-      <c r="H103" s="6">
-        <f t="shared" si="115"/>
-        <v>0</v>
-      </c>
-      <c r="J103" s="4">
-        <f t="shared" si="116"/>
-        <v>0</v>
-      </c>
-      <c r="K103" s="6">
-        <f t="shared" si="117"/>
-        <v>0</v>
-      </c>
-      <c r="M103" s="4">
-        <f t="shared" si="118"/>
-        <v>0</v>
-      </c>
-      <c r="N103" s="6">
-        <f t="shared" si="119"/>
+        <f t="shared" si="133"/>
+        <v>0</v>
+      </c>
+      <c r="G103" s="3">
+        <f t="shared" si="134"/>
+        <v>0</v>
+      </c>
+      <c r="H103" s="5">
+        <f t="shared" si="135"/>
+        <v>0</v>
+      </c>
+      <c r="J103" s="3">
+        <f t="shared" si="136"/>
+        <v>0</v>
+      </c>
+      <c r="K103" s="5">
+        <f t="shared" si="137"/>
+        <v>0</v>
+      </c>
+      <c r="M103" s="3">
+        <f t="shared" si="138"/>
+        <v>0</v>
+      </c>
+      <c r="N103" s="5">
+        <f t="shared" si="139"/>
         <v>0</v>
       </c>
     </row>
     <row r="104" spans="5:14">
       <c r="E104" s="1">
-        <f t="shared" si="112"/>
+        <f t="shared" si="132"/>
         <v>0</v>
       </c>
       <c r="F104" s="1">
-        <f t="shared" si="113"/>
-        <v>0</v>
-      </c>
-      <c r="G104" s="4">
-        <f t="shared" si="114"/>
-        <v>0</v>
-      </c>
-      <c r="H104" s="6">
-        <f t="shared" si="115"/>
-        <v>0</v>
-      </c>
-      <c r="J104" s="4">
-        <f t="shared" si="116"/>
-        <v>0</v>
-      </c>
-      <c r="K104" s="6">
-        <f t="shared" si="117"/>
-        <v>0</v>
-      </c>
-      <c r="M104" s="4">
-        <f t="shared" si="118"/>
-        <v>0</v>
-      </c>
-      <c r="N104" s="6">
-        <f t="shared" si="119"/>
+        <f t="shared" si="133"/>
+        <v>0</v>
+      </c>
+      <c r="G104" s="3">
+        <f t="shared" si="134"/>
+        <v>0</v>
+      </c>
+      <c r="H104" s="5">
+        <f t="shared" si="135"/>
+        <v>0</v>
+      </c>
+      <c r="J104" s="3">
+        <f t="shared" si="136"/>
+        <v>0</v>
+      </c>
+      <c r="K104" s="5">
+        <f t="shared" si="137"/>
+        <v>0</v>
+      </c>
+      <c r="M104" s="3">
+        <f t="shared" si="138"/>
+        <v>0</v>
+      </c>
+      <c r="N104" s="5">
+        <f t="shared" si="139"/>
         <v>0</v>
       </c>
     </row>
     <row r="105" spans="5:14">
       <c r="E105" s="1">
-        <f t="shared" si="112"/>
+        <f t="shared" si="132"/>
         <v>0</v>
       </c>
       <c r="F105" s="1">
-        <f t="shared" si="113"/>
-        <v>0</v>
-      </c>
-      <c r="G105" s="4">
-        <f t="shared" si="114"/>
-        <v>0</v>
-      </c>
-      <c r="H105" s="6">
-        <f t="shared" si="115"/>
-        <v>0</v>
-      </c>
-      <c r="J105" s="4">
-        <f t="shared" si="116"/>
-        <v>0</v>
-      </c>
-      <c r="K105" s="6">
-        <f t="shared" si="117"/>
-        <v>0</v>
-      </c>
-      <c r="M105" s="4">
-        <f t="shared" si="118"/>
-        <v>0</v>
-      </c>
-      <c r="N105" s="6">
-        <f t="shared" si="119"/>
+        <f t="shared" si="133"/>
+        <v>0</v>
+      </c>
+      <c r="G105" s="3">
+        <f t="shared" si="134"/>
+        <v>0</v>
+      </c>
+      <c r="H105" s="5">
+        <f t="shared" si="135"/>
+        <v>0</v>
+      </c>
+      <c r="J105" s="3">
+        <f t="shared" si="136"/>
+        <v>0</v>
+      </c>
+      <c r="K105" s="5">
+        <f t="shared" si="137"/>
+        <v>0</v>
+      </c>
+      <c r="M105" s="3">
+        <f t="shared" si="138"/>
+        <v>0</v>
+      </c>
+      <c r="N105" s="5">
+        <f t="shared" si="139"/>
         <v>0</v>
       </c>
     </row>
     <row r="106" spans="5:14">
       <c r="E106" s="1">
-        <f t="shared" si="112"/>
+        <f t="shared" si="132"/>
         <v>0</v>
       </c>
       <c r="F106" s="1">
-        <f t="shared" si="113"/>
-        <v>0</v>
-      </c>
-      <c r="G106" s="4">
-        <f t="shared" si="114"/>
-        <v>0</v>
-      </c>
-      <c r="H106" s="6">
-        <f t="shared" si="115"/>
-        <v>0</v>
-      </c>
-      <c r="J106" s="4">
-        <f t="shared" si="116"/>
-        <v>0</v>
-      </c>
-      <c r="K106" s="6">
-        <f t="shared" si="117"/>
-        <v>0</v>
-      </c>
-      <c r="M106" s="4">
-        <f t="shared" si="118"/>
-        <v>0</v>
-      </c>
-      <c r="N106" s="6">
-        <f t="shared" si="119"/>
+        <f t="shared" si="133"/>
+        <v>0</v>
+      </c>
+      <c r="G106" s="3">
+        <f t="shared" si="134"/>
+        <v>0</v>
+      </c>
+      <c r="H106" s="5">
+        <f t="shared" si="135"/>
+        <v>0</v>
+      </c>
+      <c r="J106" s="3">
+        <f t="shared" si="136"/>
+        <v>0</v>
+      </c>
+      <c r="K106" s="5">
+        <f t="shared" si="137"/>
+        <v>0</v>
+      </c>
+      <c r="M106" s="3">
+        <f t="shared" si="138"/>
+        <v>0</v>
+      </c>
+      <c r="N106" s="5">
+        <f t="shared" si="139"/>
         <v>0</v>
       </c>
     </row>
     <row r="107" spans="5:14">
       <c r="E107" s="1">
-        <f t="shared" si="112"/>
+        <f t="shared" si="132"/>
         <v>0</v>
       </c>
       <c r="F107" s="1">
-        <f t="shared" si="113"/>
-        <v>0</v>
-      </c>
-      <c r="G107" s="4">
-        <f t="shared" si="114"/>
-        <v>0</v>
-      </c>
-      <c r="H107" s="6">
-        <f t="shared" si="115"/>
-        <v>0</v>
-      </c>
-      <c r="J107" s="4">
-        <f t="shared" si="116"/>
-        <v>0</v>
-      </c>
-      <c r="K107" s="6">
-        <f t="shared" si="117"/>
-        <v>0</v>
-      </c>
-      <c r="M107" s="4">
-        <f t="shared" si="118"/>
-        <v>0</v>
-      </c>
-      <c r="N107" s="6">
-        <f t="shared" si="119"/>
+        <f t="shared" si="133"/>
+        <v>0</v>
+      </c>
+      <c r="G107" s="3">
+        <f t="shared" si="134"/>
+        <v>0</v>
+      </c>
+      <c r="H107" s="5">
+        <f t="shared" si="135"/>
+        <v>0</v>
+      </c>
+      <c r="J107" s="3">
+        <f t="shared" si="136"/>
+        <v>0</v>
+      </c>
+      <c r="K107" s="5">
+        <f t="shared" si="137"/>
+        <v>0</v>
+      </c>
+      <c r="M107" s="3">
+        <f t="shared" si="138"/>
+        <v>0</v>
+      </c>
+      <c r="N107" s="5">
+        <f t="shared" si="139"/>
         <v>0</v>
       </c>
     </row>
     <row r="108" spans="5:14">
       <c r="E108" s="1">
-        <f t="shared" si="112"/>
+        <f t="shared" si="132"/>
         <v>0</v>
       </c>
       <c r="F108" s="1">
-        <f t="shared" si="113"/>
-        <v>0</v>
-      </c>
-      <c r="G108" s="4">
-        <f t="shared" si="114"/>
-        <v>0</v>
-      </c>
-      <c r="H108" s="6">
-        <f t="shared" si="115"/>
-        <v>0</v>
-      </c>
-      <c r="J108" s="4">
-        <f t="shared" si="116"/>
-        <v>0</v>
-      </c>
-      <c r="K108" s="6">
-        <f t="shared" si="117"/>
-        <v>0</v>
-      </c>
-      <c r="M108" s="4">
-        <f t="shared" si="118"/>
-        <v>0</v>
-      </c>
-      <c r="N108" s="6">
-        <f t="shared" si="119"/>
+        <f t="shared" si="133"/>
+        <v>0</v>
+      </c>
+      <c r="G108" s="3">
+        <f t="shared" si="134"/>
+        <v>0</v>
+      </c>
+      <c r="H108" s="5">
+        <f t="shared" si="135"/>
+        <v>0</v>
+      </c>
+      <c r="J108" s="3">
+        <f t="shared" si="136"/>
+        <v>0</v>
+      </c>
+      <c r="K108" s="5">
+        <f t="shared" si="137"/>
+        <v>0</v>
+      </c>
+      <c r="M108" s="3">
+        <f t="shared" si="138"/>
+        <v>0</v>
+      </c>
+      <c r="N108" s="5">
+        <f t="shared" si="139"/>
         <v>0</v>
       </c>
     </row>
     <row r="109" spans="5:14">
       <c r="E109" s="1">
-        <f t="shared" si="112"/>
+        <f t="shared" si="132"/>
         <v>0</v>
       </c>
       <c r="F109" s="1">
-        <f t="shared" si="113"/>
-        <v>0</v>
-      </c>
-      <c r="G109" s="4">
-        <f t="shared" si="114"/>
-        <v>0</v>
-      </c>
-      <c r="H109" s="6">
-        <f t="shared" si="115"/>
-        <v>0</v>
-      </c>
-      <c r="J109" s="4">
-        <f t="shared" si="116"/>
-        <v>0</v>
-      </c>
-      <c r="K109" s="6">
-        <f t="shared" si="117"/>
-        <v>0</v>
-      </c>
-      <c r="M109" s="4">
-        <f t="shared" si="118"/>
-        <v>0</v>
-      </c>
-      <c r="N109" s="6">
-        <f t="shared" si="119"/>
+        <f t="shared" si="133"/>
+        <v>0</v>
+      </c>
+      <c r="G109" s="3">
+        <f t="shared" si="134"/>
+        <v>0</v>
+      </c>
+      <c r="H109" s="5">
+        <f t="shared" si="135"/>
+        <v>0</v>
+      </c>
+      <c r="J109" s="3">
+        <f t="shared" si="136"/>
+        <v>0</v>
+      </c>
+      <c r="K109" s="5">
+        <f t="shared" si="137"/>
+        <v>0</v>
+      </c>
+      <c r="M109" s="3">
+        <f t="shared" si="138"/>
+        <v>0</v>
+      </c>
+      <c r="N109" s="5">
+        <f t="shared" si="139"/>
         <v>0</v>
       </c>
     </row>
     <row r="110" spans="5:14">
       <c r="E110" s="1">
-        <f t="shared" si="112"/>
+        <f t="shared" si="132"/>
         <v>0</v>
       </c>
       <c r="F110" s="1">
-        <f t="shared" si="113"/>
-        <v>0</v>
-      </c>
-      <c r="G110" s="4">
-        <f t="shared" si="114"/>
-        <v>0</v>
-      </c>
-      <c r="H110" s="6">
-        <f t="shared" si="115"/>
-        <v>0</v>
-      </c>
-      <c r="J110" s="4">
-        <f t="shared" si="116"/>
-        <v>0</v>
-      </c>
-      <c r="K110" s="6">
-        <f t="shared" si="117"/>
-        <v>0</v>
-      </c>
-      <c r="M110" s="4">
-        <f t="shared" si="118"/>
-        <v>0</v>
-      </c>
-      <c r="N110" s="6">
-        <f t="shared" si="119"/>
+        <f t="shared" si="133"/>
+        <v>0</v>
+      </c>
+      <c r="G110" s="3">
+        <f t="shared" si="134"/>
+        <v>0</v>
+      </c>
+      <c r="H110" s="5">
+        <f t="shared" si="135"/>
+        <v>0</v>
+      </c>
+      <c r="J110" s="3">
+        <f t="shared" si="136"/>
+        <v>0</v>
+      </c>
+      <c r="K110" s="5">
+        <f t="shared" si="137"/>
+        <v>0</v>
+      </c>
+      <c r="M110" s="3">
+        <f t="shared" si="138"/>
+        <v>0</v>
+      </c>
+      <c r="N110" s="5">
+        <f t="shared" si="139"/>
         <v>0</v>
       </c>
     </row>
     <row r="111" spans="5:14">
       <c r="E111" s="1">
-        <f t="shared" si="112"/>
+        <f t="shared" si="132"/>
         <v>0</v>
       </c>
       <c r="F111" s="1">
-        <f t="shared" si="113"/>
-        <v>0</v>
-      </c>
-      <c r="G111" s="4">
-        <f t="shared" si="114"/>
-        <v>0</v>
-      </c>
-      <c r="H111" s="6">
-        <f t="shared" si="115"/>
-        <v>0</v>
-      </c>
-      <c r="J111" s="4">
-        <f t="shared" si="116"/>
-        <v>0</v>
-      </c>
-      <c r="K111" s="6">
-        <f t="shared" si="117"/>
-        <v>0</v>
-      </c>
-      <c r="M111" s="4">
-        <f t="shared" si="118"/>
-        <v>0</v>
-      </c>
-      <c r="N111" s="6">
-        <f t="shared" si="119"/>
+        <f t="shared" si="133"/>
+        <v>0</v>
+      </c>
+      <c r="G111" s="3">
+        <f t="shared" si="134"/>
+        <v>0</v>
+      </c>
+      <c r="H111" s="5">
+        <f t="shared" si="135"/>
+        <v>0</v>
+      </c>
+      <c r="J111" s="3">
+        <f t="shared" si="136"/>
+        <v>0</v>
+      </c>
+      <c r="K111" s="5">
+        <f t="shared" si="137"/>
+        <v>0</v>
+      </c>
+      <c r="M111" s="3">
+        <f t="shared" si="138"/>
+        <v>0</v>
+      </c>
+      <c r="N111" s="5">
+        <f t="shared" si="139"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="5:14">
+      <c r="E112" s="1">
+        <f t="shared" si="132"/>
+        <v>0</v>
+      </c>
+      <c r="F112" s="1">
+        <f t="shared" si="133"/>
+        <v>0</v>
+      </c>
+      <c r="G112" s="3">
+        <f t="shared" si="134"/>
+        <v>0</v>
+      </c>
+      <c r="H112" s="5">
+        <f t="shared" si="135"/>
+        <v>0</v>
+      </c>
+      <c r="J112" s="3">
+        <f t="shared" si="136"/>
+        <v>0</v>
+      </c>
+      <c r="K112" s="5">
+        <f t="shared" si="137"/>
+        <v>0</v>
+      </c>
+      <c r="M112" s="3">
+        <f t="shared" si="138"/>
+        <v>0</v>
+      </c>
+      <c r="N112" s="5">
+        <f t="shared" si="139"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="5:14">
+      <c r="E113" s="1">
+        <f t="shared" si="132"/>
+        <v>0</v>
+      </c>
+      <c r="F113" s="1">
+        <f t="shared" si="133"/>
+        <v>0</v>
+      </c>
+      <c r="G113" s="3">
+        <f t="shared" si="134"/>
+        <v>0</v>
+      </c>
+      <c r="H113" s="5">
+        <f t="shared" si="135"/>
+        <v>0</v>
+      </c>
+      <c r="J113" s="3">
+        <f t="shared" si="136"/>
+        <v>0</v>
+      </c>
+      <c r="K113" s="5">
+        <f t="shared" si="137"/>
+        <v>0</v>
+      </c>
+      <c r="M113" s="3">
+        <f t="shared" si="138"/>
+        <v>0</v>
+      </c>
+      <c r="N113" s="5">
+        <f t="shared" si="139"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="5:14">
+      <c r="E114" s="1">
+        <f t="shared" ref="E114:E124" si="140" xml:space="preserve"> C114/C$2</f>
+        <v>0</v>
+      </c>
+      <c r="F114" s="1">
+        <f t="shared" ref="F114:F124" si="141" xml:space="preserve"> D114/D$2</f>
+        <v>0</v>
+      </c>
+      <c r="G114" s="3">
+        <f t="shared" ref="G114:G124" si="142">IF(ISBLANK(C114),0,(C114*G$2/C$2))</f>
+        <v>0</v>
+      </c>
+      <c r="H114" s="5">
+        <f t="shared" ref="H114:H124" si="143">IF(ISBLANK(D114),0,(D114*H$2/D$2))</f>
+        <v>0</v>
+      </c>
+      <c r="J114" s="3">
+        <f t="shared" ref="J114:J124" si="144">IF(ISBLANK(C114),0,(C114*J$2/C$2))</f>
+        <v>0</v>
+      </c>
+      <c r="K114" s="5">
+        <f t="shared" ref="K114:K124" si="145">IF(ISBLANK(D114),0,(D114*K$2/D$2))</f>
+        <v>0</v>
+      </c>
+      <c r="M114" s="3">
+        <f t="shared" ref="M114:M124" si="146">IF(ISBLANK(C114),0,(C114*M$2/C$2))</f>
+        <v>0</v>
+      </c>
+      <c r="N114" s="5">
+        <f t="shared" ref="N114:N124" si="147">IF(ISBLANK(D114),0,(D114*N$2/D$2))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="5:14">
+      <c r="E115" s="1">
+        <f t="shared" si="140"/>
+        <v>0</v>
+      </c>
+      <c r="F115" s="1">
+        <f t="shared" si="141"/>
+        <v>0</v>
+      </c>
+      <c r="G115" s="3">
+        <f t="shared" si="142"/>
+        <v>0</v>
+      </c>
+      <c r="H115" s="5">
+        <f t="shared" si="143"/>
+        <v>0</v>
+      </c>
+      <c r="J115" s="3">
+        <f t="shared" si="144"/>
+        <v>0</v>
+      </c>
+      <c r="K115" s="5">
+        <f t="shared" si="145"/>
+        <v>0</v>
+      </c>
+      <c r="M115" s="3">
+        <f t="shared" si="146"/>
+        <v>0</v>
+      </c>
+      <c r="N115" s="5">
+        <f t="shared" si="147"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="5:14">
+      <c r="E116" s="1">
+        <f t="shared" si="140"/>
+        <v>0</v>
+      </c>
+      <c r="F116" s="1">
+        <f t="shared" si="141"/>
+        <v>0</v>
+      </c>
+      <c r="G116" s="3">
+        <f t="shared" si="142"/>
+        <v>0</v>
+      </c>
+      <c r="H116" s="5">
+        <f t="shared" si="143"/>
+        <v>0</v>
+      </c>
+      <c r="J116" s="3">
+        <f t="shared" si="144"/>
+        <v>0</v>
+      </c>
+      <c r="K116" s="5">
+        <f t="shared" si="145"/>
+        <v>0</v>
+      </c>
+      <c r="M116" s="3">
+        <f t="shared" si="146"/>
+        <v>0</v>
+      </c>
+      <c r="N116" s="5">
+        <f t="shared" si="147"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="5:14">
+      <c r="E117" s="1">
+        <f t="shared" si="140"/>
+        <v>0</v>
+      </c>
+      <c r="F117" s="1">
+        <f t="shared" si="141"/>
+        <v>0</v>
+      </c>
+      <c r="G117" s="3">
+        <f t="shared" si="142"/>
+        <v>0</v>
+      </c>
+      <c r="H117" s="5">
+        <f t="shared" si="143"/>
+        <v>0</v>
+      </c>
+      <c r="J117" s="3">
+        <f t="shared" si="144"/>
+        <v>0</v>
+      </c>
+      <c r="K117" s="5">
+        <f t="shared" si="145"/>
+        <v>0</v>
+      </c>
+      <c r="M117" s="3">
+        <f t="shared" si="146"/>
+        <v>0</v>
+      </c>
+      <c r="N117" s="5">
+        <f t="shared" si="147"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="5:14">
+      <c r="E118" s="1">
+        <f t="shared" si="140"/>
+        <v>0</v>
+      </c>
+      <c r="F118" s="1">
+        <f t="shared" si="141"/>
+        <v>0</v>
+      </c>
+      <c r="G118" s="3">
+        <f t="shared" si="142"/>
+        <v>0</v>
+      </c>
+      <c r="H118" s="5">
+        <f t="shared" si="143"/>
+        <v>0</v>
+      </c>
+      <c r="J118" s="3">
+        <f t="shared" si="144"/>
+        <v>0</v>
+      </c>
+      <c r="K118" s="5">
+        <f t="shared" si="145"/>
+        <v>0</v>
+      </c>
+      <c r="M118" s="3">
+        <f t="shared" si="146"/>
+        <v>0</v>
+      </c>
+      <c r="N118" s="5">
+        <f t="shared" si="147"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="5:14">
+      <c r="E119" s="1">
+        <f t="shared" si="140"/>
+        <v>0</v>
+      </c>
+      <c r="F119" s="1">
+        <f t="shared" si="141"/>
+        <v>0</v>
+      </c>
+      <c r="G119" s="3">
+        <f t="shared" si="142"/>
+        <v>0</v>
+      </c>
+      <c r="H119" s="5">
+        <f t="shared" si="143"/>
+        <v>0</v>
+      </c>
+      <c r="J119" s="3">
+        <f t="shared" si="144"/>
+        <v>0</v>
+      </c>
+      <c r="K119" s="5">
+        <f t="shared" si="145"/>
+        <v>0</v>
+      </c>
+      <c r="M119" s="3">
+        <f t="shared" si="146"/>
+        <v>0</v>
+      </c>
+      <c r="N119" s="5">
+        <f t="shared" si="147"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="5:14">
+      <c r="E120" s="1">
+        <f t="shared" si="140"/>
+        <v>0</v>
+      </c>
+      <c r="F120" s="1">
+        <f t="shared" si="141"/>
+        <v>0</v>
+      </c>
+      <c r="G120" s="3">
+        <f t="shared" si="142"/>
+        <v>0</v>
+      </c>
+      <c r="H120" s="5">
+        <f t="shared" si="143"/>
+        <v>0</v>
+      </c>
+      <c r="J120" s="3">
+        <f t="shared" si="144"/>
+        <v>0</v>
+      </c>
+      <c r="K120" s="5">
+        <f t="shared" si="145"/>
+        <v>0</v>
+      </c>
+      <c r="M120" s="3">
+        <f t="shared" si="146"/>
+        <v>0</v>
+      </c>
+      <c r="N120" s="5">
+        <f t="shared" si="147"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="5:14">
+      <c r="E121" s="1">
+        <f t="shared" si="140"/>
+        <v>0</v>
+      </c>
+      <c r="F121" s="1">
+        <f t="shared" si="141"/>
+        <v>0</v>
+      </c>
+      <c r="G121" s="3">
+        <f t="shared" si="142"/>
+        <v>0</v>
+      </c>
+      <c r="H121" s="5">
+        <f t="shared" si="143"/>
+        <v>0</v>
+      </c>
+      <c r="J121" s="3">
+        <f t="shared" si="144"/>
+        <v>0</v>
+      </c>
+      <c r="K121" s="5">
+        <f t="shared" si="145"/>
+        <v>0</v>
+      </c>
+      <c r="M121" s="3">
+        <f t="shared" si="146"/>
+        <v>0</v>
+      </c>
+      <c r="N121" s="5">
+        <f t="shared" si="147"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="5:14">
+      <c r="E122" s="1">
+        <f t="shared" si="140"/>
+        <v>0</v>
+      </c>
+      <c r="F122" s="1">
+        <f t="shared" si="141"/>
+        <v>0</v>
+      </c>
+      <c r="G122" s="3">
+        <f t="shared" si="142"/>
+        <v>0</v>
+      </c>
+      <c r="H122" s="5">
+        <f t="shared" si="143"/>
+        <v>0</v>
+      </c>
+      <c r="J122" s="3">
+        <f t="shared" si="144"/>
+        <v>0</v>
+      </c>
+      <c r="K122" s="5">
+        <f t="shared" si="145"/>
+        <v>0</v>
+      </c>
+      <c r="M122" s="3">
+        <f t="shared" si="146"/>
+        <v>0</v>
+      </c>
+      <c r="N122" s="5">
+        <f t="shared" si="147"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="5:14">
+      <c r="E123" s="1">
+        <f t="shared" si="140"/>
+        <v>0</v>
+      </c>
+      <c r="F123" s="1">
+        <f t="shared" si="141"/>
+        <v>0</v>
+      </c>
+      <c r="G123" s="3">
+        <f t="shared" si="142"/>
+        <v>0</v>
+      </c>
+      <c r="H123" s="5">
+        <f t="shared" si="143"/>
+        <v>0</v>
+      </c>
+      <c r="J123" s="3">
+        <f t="shared" si="144"/>
+        <v>0</v>
+      </c>
+      <c r="K123" s="5">
+        <f t="shared" si="145"/>
+        <v>0</v>
+      </c>
+      <c r="M123" s="3">
+        <f t="shared" si="146"/>
+        <v>0</v>
+      </c>
+      <c r="N123" s="5">
+        <f t="shared" si="147"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="5:14">
+      <c r="E124" s="1">
+        <f t="shared" si="140"/>
+        <v>0</v>
+      </c>
+      <c r="F124" s="1">
+        <f t="shared" si="141"/>
+        <v>0</v>
+      </c>
+      <c r="G124" s="3">
+        <f t="shared" si="142"/>
+        <v>0</v>
+      </c>
+      <c r="H124" s="5">
+        <f t="shared" si="143"/>
+        <v>0</v>
+      </c>
+      <c r="J124" s="3">
+        <f t="shared" si="144"/>
+        <v>0</v>
+      </c>
+      <c r="K124" s="5">
+        <f t="shared" si="145"/>
+        <v>0</v>
+      </c>
+      <c r="M124" s="3">
+        <f t="shared" si="146"/>
+        <v>0</v>
+      </c>
+      <c r="N124" s="5">
+        <f t="shared" si="147"/>
         <v>0</v>
       </c>
     </row>
@@ -3956,31 +4094,31 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:23">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3" t="s">
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3" t="s">
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3" t="s">
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3" t="s">
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
     </row>
     <row r="2" spans="1:23">
       <c r="A2">

--- a/target/classes/com/ratioTable.xlsx
+++ b/target/classes/com/ratioTable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IT\Documents\GitHub\Balatro\src\main\resources\com\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1523D162-3FB6-489F-845C-565FFD912ECB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF157623-1F54-4F1B-A7AC-496AF6941768}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7890" xr2:uid="{706E2108-D16A-4E70-A675-C3702A172F02}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="49">
   <si>
     <t>Play Button</t>
   </si>
@@ -171,6 +171,9 @@
   <si>
     <t>Stat Column</t>
   </si>
+  <si>
+    <t>Joker Collection</t>
+  </si>
 </sst>
 </file>
 
@@ -246,7 +249,7 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -265,6 +268,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="3" fontId="1" fillId="3" borderId="0" xfId="3" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="1" fillId="4" borderId="0" xfId="4" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="20 % - Akzent1" xfId="3" builtinId="30"/>
@@ -583,7 +588,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AE52DC3-6553-4C6D-A135-8A8C4D8FA77D}">
-  <dimension ref="A1:AE124"/>
+  <dimension ref="A1:AE135"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="11.42578125" style="3"/>
@@ -1190,43 +1195,49 @@
       <c r="H26" s="5"/>
     </row>
     <row r="27" spans="1:31" s="10" customFormat="1">
-      <c r="A27"/>
+      <c r="A27" t="s">
+        <v>48</v>
+      </c>
       <c r="B27"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="5"/>
+      <c r="C27" s="14">
+        <v>1248</v>
+      </c>
+      <c r="D27" s="15">
+        <v>1274</v>
+      </c>
       <c r="E27" s="1">
         <f t="shared" ref="E27" si="64" xml:space="preserve"> C27/C$2</f>
-        <v>0</v>
+        <v>0.48749999999999999</v>
       </c>
       <c r="F27" s="1">
         <f t="shared" ref="F27" si="65" xml:space="preserve"> D27/D$2</f>
-        <v>0</v>
+        <v>0.88472222222222219</v>
       </c>
       <c r="G27" s="3">
         <f t="shared" ref="G27" si="66">IF(ISBLANK(C27),0,(C27*G$2/C$2))</f>
-        <v>0</v>
+        <v>1872</v>
       </c>
       <c r="H27" s="5">
         <f t="shared" ref="H27" si="67">IF(ISBLANK(D27),0,(D27*H$2/D$2))</f>
-        <v>0</v>
+        <v>1911</v>
       </c>
       <c r="I27" s="1"/>
       <c r="J27" s="3">
         <f t="shared" ref="J27" si="68">IF(ISBLANK(C27),0,(C27*J$2/C$2))</f>
-        <v>0</v>
+        <v>936</v>
       </c>
       <c r="K27" s="5">
         <f t="shared" ref="K27" si="69">IF(ISBLANK(D27),0,(D27*K$2/D$2))</f>
-        <v>0</v>
+        <v>955.5</v>
       </c>
       <c r="L27"/>
       <c r="M27" s="3">
         <f t="shared" ref="M27" si="70">IF(ISBLANK(C27),0,(C27*M$2/C$2))</f>
-        <v>0</v>
+        <v>624</v>
       </c>
       <c r="N27" s="5">
         <f t="shared" ref="N27" si="71">IF(ISBLANK(D27),0,(D27*N$2/D$2))</f>
-        <v>0</v>
+        <v>637</v>
       </c>
       <c r="O27"/>
       <c r="P27"/>
@@ -1251,68 +1262,75 @@
       <c r="H28" s="5"/>
     </row>
     <row r="29" spans="1:31">
-      <c r="A29" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29" s="10"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="11"/>
-      <c r="H29" s="10"/>
-      <c r="I29" s="12"/>
-      <c r="J29" s="11"/>
-      <c r="K29" s="10"/>
-      <c r="L29" s="10"/>
-      <c r="M29" s="11"/>
-      <c r="N29" s="10"/>
+      <c r="E29" s="1">
+        <f t="shared" ref="E29" si="72" xml:space="preserve"> C29/C$2</f>
+        <v>0</v>
+      </c>
+      <c r="F29" s="1">
+        <f t="shared" ref="F29" si="73" xml:space="preserve"> D29/D$2</f>
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <f t="shared" ref="G29" si="74">IF(ISBLANK(C29),0,(C29*G$2/C$2))</f>
+        <v>0</v>
+      </c>
+      <c r="H29" s="5">
+        <f t="shared" ref="H29" si="75">IF(ISBLANK(D29),0,(D29*H$2/D$2))</f>
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
+        <f t="shared" ref="J29" si="76">IF(ISBLANK(C29),0,(C29*J$2/C$2))</f>
+        <v>0</v>
+      </c>
+      <c r="K29" s="5">
+        <f t="shared" ref="K29" si="77">IF(ISBLANK(D29),0,(D29*K$2/D$2))</f>
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
+        <f t="shared" ref="M29" si="78">IF(ISBLANK(C29),0,(C29*M$2/C$2))</f>
+        <v>0</v>
+      </c>
+      <c r="N29" s="5">
+        <f t="shared" ref="N29" si="79">IF(ISBLANK(D29),0,(D29*N$2/D$2))</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="30" spans="1:31">
       <c r="G30" s="3"/>
       <c r="H30" s="5"/>
     </row>
     <row r="31" spans="1:31">
-      <c r="A31" t="s">
-        <v>9</v>
-      </c>
-      <c r="C31" s="3">
-        <v>572</v>
-      </c>
-      <c r="D31" s="5">
-        <v>1440</v>
-      </c>
       <c r="E31" s="1">
-        <f t="shared" ref="E31" si="72" xml:space="preserve"> C31/C$2</f>
-        <v>0.22343750000000001</v>
+        <f t="shared" ref="E31" si="80" xml:space="preserve"> C31/C$2</f>
+        <v>0</v>
       </c>
       <c r="F31" s="1">
-        <f t="shared" ref="F31" si="73" xml:space="preserve"> D31/D$2</f>
-        <v>1</v>
+        <f t="shared" ref="F31" si="81" xml:space="preserve"> D31/D$2</f>
+        <v>0</v>
       </c>
       <c r="G31" s="3">
-        <f t="shared" ref="G31" si="74">IF(ISBLANK(C31),0,(C31*G$2/C$2))</f>
-        <v>858</v>
+        <f t="shared" ref="G31" si="82">IF(ISBLANK(C31),0,(C31*G$2/C$2))</f>
+        <v>0</v>
       </c>
       <c r="H31" s="5">
-        <f t="shared" ref="H31" si="75">IF(ISBLANK(D31),0,(D31*H$2/D$2))</f>
-        <v>2160</v>
+        <f t="shared" ref="H31" si="83">IF(ISBLANK(D31),0,(D31*H$2/D$2))</f>
+        <v>0</v>
       </c>
       <c r="J31" s="3">
-        <f t="shared" ref="J31" si="76">IF(ISBLANK(C31),0,(C31*J$2/C$2))</f>
-        <v>429</v>
+        <f t="shared" ref="J31" si="84">IF(ISBLANK(C31),0,(C31*J$2/C$2))</f>
+        <v>0</v>
       </c>
       <c r="K31" s="5">
-        <f t="shared" ref="K31" si="77">IF(ISBLANK(D31),0,(D31*K$2/D$2))</f>
-        <v>1080</v>
+        <f t="shared" ref="K31" si="85">IF(ISBLANK(D31),0,(D31*K$2/D$2))</f>
+        <v>0</v>
       </c>
       <c r="M31" s="3">
-        <f t="shared" ref="M31" si="78">IF(ISBLANK(C31),0,(C31*M$2/C$2))</f>
-        <v>286</v>
+        <f t="shared" ref="M31" si="86">IF(ISBLANK(C31),0,(C31*M$2/C$2))</f>
+        <v>0</v>
       </c>
       <c r="N31" s="5">
-        <f t="shared" ref="N31" si="79">IF(ISBLANK(D31),0,(D31*N$2/D$2))</f>
-        <v>720</v>
+        <f t="shared" ref="N31" si="87">IF(ISBLANK(D31),0,(D31*N$2/D$2))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:31">
@@ -1320,46 +1338,37 @@
       <c r="H32" s="5"/>
     </row>
     <row r="33" spans="1:31">
-      <c r="A33" t="s">
-        <v>42</v>
-      </c>
-      <c r="C33" s="3">
-        <v>220</v>
-      </c>
-      <c r="D33" s="5">
-        <v>292</v>
-      </c>
       <c r="E33" s="1">
-        <f t="shared" ref="E33" si="80" xml:space="preserve"> C33/C$2</f>
-        <v>8.59375E-2</v>
+        <f t="shared" ref="E33" si="88" xml:space="preserve"> C33/C$2</f>
+        <v>0</v>
       </c>
       <c r="F33" s="1">
-        <f t="shared" ref="F33" si="81" xml:space="preserve"> D33/D$2</f>
-        <v>0.20277777777777778</v>
+        <f t="shared" ref="F33" si="89" xml:space="preserve"> D33/D$2</f>
+        <v>0</v>
       </c>
       <c r="G33" s="3">
-        <f t="shared" ref="G33" si="82">IF(ISBLANK(C33),0,(C33*G$2/C$2))</f>
-        <v>330</v>
+        <f t="shared" ref="G33" si="90">IF(ISBLANK(C33),0,(C33*G$2/C$2))</f>
+        <v>0</v>
       </c>
       <c r="H33" s="5">
-        <f t="shared" ref="H33" si="83">IF(ISBLANK(D33),0,(D33*H$2/D$2))</f>
-        <v>438</v>
+        <f t="shared" ref="H33" si="91">IF(ISBLANK(D33),0,(D33*H$2/D$2))</f>
+        <v>0</v>
       </c>
       <c r="J33" s="3">
-        <f t="shared" ref="J33" si="84">IF(ISBLANK(C33),0,(C33*J$2/C$2))</f>
-        <v>165</v>
+        <f t="shared" ref="J33" si="92">IF(ISBLANK(C33),0,(C33*J$2/C$2))</f>
+        <v>0</v>
       </c>
       <c r="K33" s="5">
-        <f t="shared" ref="K33" si="85">IF(ISBLANK(D33),0,(D33*K$2/D$2))</f>
-        <v>219</v>
+        <f t="shared" ref="K33" si="93">IF(ISBLANK(D33),0,(D33*K$2/D$2))</f>
+        <v>0</v>
       </c>
       <c r="M33" s="3">
-        <f t="shared" ref="M33" si="86">IF(ISBLANK(C33),0,(C33*M$2/C$2))</f>
-        <v>110</v>
+        <f t="shared" ref="M33" si="94">IF(ISBLANK(C33),0,(C33*M$2/C$2))</f>
+        <v>0</v>
       </c>
       <c r="N33" s="5">
-        <f t="shared" ref="N33" si="87">IF(ISBLANK(D33),0,(D33*N$2/D$2))</f>
-        <v>146</v>
+        <f t="shared" ref="N33" si="95">IF(ISBLANK(D33),0,(D33*N$2/D$2))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:31">
@@ -1367,46 +1376,37 @@
       <c r="H34" s="5"/>
     </row>
     <row r="35" spans="1:31">
-      <c r="A35" t="s">
-        <v>43</v>
-      </c>
-      <c r="C35" s="3">
-        <v>140</v>
-      </c>
-      <c r="D35" s="5">
-        <v>200</v>
-      </c>
       <c r="E35" s="1">
-        <f t="shared" ref="E35" si="88" xml:space="preserve"> C35/C$2</f>
-        <v>5.46875E-2</v>
+        <f t="shared" ref="E35" si="96" xml:space="preserve"> C35/C$2</f>
+        <v>0</v>
       </c>
       <c r="F35" s="1">
-        <f t="shared" ref="F35" si="89" xml:space="preserve"> D35/D$2</f>
-        <v>0.1388888888888889</v>
+        <f t="shared" ref="F35" si="97" xml:space="preserve"> D35/D$2</f>
+        <v>0</v>
       </c>
       <c r="G35" s="3">
-        <f t="shared" ref="G35" si="90">IF(ISBLANK(C35),0,(C35*G$2/C$2))</f>
-        <v>210</v>
+        <f t="shared" ref="G35" si="98">IF(ISBLANK(C35),0,(C35*G$2/C$2))</f>
+        <v>0</v>
       </c>
       <c r="H35" s="5">
-        <f t="shared" ref="H35" si="91">IF(ISBLANK(D35),0,(D35*H$2/D$2))</f>
-        <v>300</v>
+        <f t="shared" ref="H35" si="99">IF(ISBLANK(D35),0,(D35*H$2/D$2))</f>
+        <v>0</v>
       </c>
       <c r="J35" s="3">
-        <f t="shared" ref="J35" si="92">IF(ISBLANK(C35),0,(C35*J$2/C$2))</f>
-        <v>105</v>
+        <f t="shared" ref="J35" si="100">IF(ISBLANK(C35),0,(C35*J$2/C$2))</f>
+        <v>0</v>
       </c>
       <c r="K35" s="5">
-        <f t="shared" ref="K35" si="93">IF(ISBLANK(D35),0,(D35*K$2/D$2))</f>
-        <v>150</v>
+        <f t="shared" ref="K35" si="101">IF(ISBLANK(D35),0,(D35*K$2/D$2))</f>
+        <v>0</v>
       </c>
       <c r="M35" s="3">
-        <f t="shared" ref="M35" si="94">IF(ISBLANK(C35),0,(C35*M$2/C$2))</f>
-        <v>70</v>
+        <f t="shared" ref="M35" si="102">IF(ISBLANK(C35),0,(C35*M$2/C$2))</f>
+        <v>0</v>
       </c>
       <c r="N35" s="5">
-        <f t="shared" ref="N35" si="95">IF(ISBLANK(D35),0,(D35*N$2/D$2))</f>
-        <v>100</v>
+        <f t="shared" ref="N35" si="103">IF(ISBLANK(D35),0,(D35*N$2/D$2))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:31">
@@ -1415,2670 +1415,2875 @@
     </row>
     <row r="37" spans="1:31">
       <c r="E37" s="1">
-        <f t="shared" ref="E37" si="96" xml:space="preserve"> C37/C$2</f>
+        <f t="shared" ref="E37" si="104" xml:space="preserve"> C37/C$2</f>
         <v>0</v>
       </c>
       <c r="F37" s="1">
-        <f t="shared" ref="F37" si="97" xml:space="preserve"> D37/D$2</f>
+        <f t="shared" ref="F37" si="105" xml:space="preserve"> D37/D$2</f>
         <v>0</v>
       </c>
       <c r="G37" s="3">
-        <f t="shared" ref="G37" si="98">IF(ISBLANK(C37),0,(C37*G$2/C$2))</f>
+        <f t="shared" ref="G37" si="106">IF(ISBLANK(C37),0,(C37*G$2/C$2))</f>
         <v>0</v>
       </c>
       <c r="H37" s="5">
-        <f t="shared" ref="H37" si="99">IF(ISBLANK(D37),0,(D37*H$2/D$2))</f>
+        <f t="shared" ref="H37" si="107">IF(ISBLANK(D37),0,(D37*H$2/D$2))</f>
         <v>0</v>
       </c>
       <c r="J37" s="3">
-        <f t="shared" ref="J37" si="100">IF(ISBLANK(C37),0,(C37*J$2/C$2))</f>
+        <f t="shared" ref="J37" si="108">IF(ISBLANK(C37),0,(C37*J$2/C$2))</f>
         <v>0</v>
       </c>
       <c r="K37" s="5">
-        <f t="shared" ref="K37" si="101">IF(ISBLANK(D37),0,(D37*K$2/D$2))</f>
+        <f t="shared" ref="K37" si="109">IF(ISBLANK(D37),0,(D37*K$2/D$2))</f>
         <v>0</v>
       </c>
       <c r="M37" s="3">
-        <f t="shared" ref="M37" si="102">IF(ISBLANK(C37),0,(C37*M$2/C$2))</f>
+        <f t="shared" ref="M37" si="110">IF(ISBLANK(C37),0,(C37*M$2/C$2))</f>
         <v>0</v>
       </c>
       <c r="N37" s="5">
-        <f t="shared" ref="N37" si="103">IF(ISBLANK(D37),0,(D37*N$2/D$2))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:31" s="10" customFormat="1">
-      <c r="A38"/>
-      <c r="B38"/>
-      <c r="C38" s="3"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
+        <f t="shared" ref="N37" si="111">IF(ISBLANK(D37),0,(D37*N$2/D$2))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:31">
       <c r="G38" s="3"/>
       <c r="H38" s="5"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="3"/>
-      <c r="K38" s="5"/>
-      <c r="L38"/>
-      <c r="M38" s="3"/>
-      <c r="N38" s="5"/>
-      <c r="O38"/>
-      <c r="P38"/>
-      <c r="Q38"/>
-      <c r="R38"/>
-      <c r="S38"/>
-      <c r="T38"/>
-      <c r="U38"/>
-      <c r="V38"/>
-      <c r="W38"/>
-      <c r="X38"/>
-      <c r="Y38"/>
-      <c r="Z38"/>
-      <c r="AA38"/>
-      <c r="AB38"/>
-      <c r="AC38"/>
-      <c r="AD38"/>
-      <c r="AE38"/>
     </row>
     <row r="39" spans="1:31">
-      <c r="E39" s="1">
-        <f t="shared" ref="E39" si="104" xml:space="preserve"> C39/C$2</f>
-        <v>0</v>
-      </c>
-      <c r="F39" s="1">
-        <f t="shared" ref="F39" si="105" xml:space="preserve"> D39/D$2</f>
-        <v>0</v>
-      </c>
-      <c r="G39" s="3">
-        <f t="shared" ref="G39" si="106">IF(ISBLANK(C39),0,(C39*G$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="H39" s="5">
-        <f t="shared" ref="H39" si="107">IF(ISBLANK(D39),0,(D39*H$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="J39" s="3">
-        <f t="shared" ref="J39" si="108">IF(ISBLANK(C39),0,(C39*J$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="K39" s="5">
-        <f t="shared" ref="K39" si="109">IF(ISBLANK(D39),0,(D39*K$2/D$2))</f>
-        <v>0</v>
-      </c>
-      <c r="M39" s="3">
-        <f t="shared" ref="M39" si="110">IF(ISBLANK(C39),0,(C39*M$2/C$2))</f>
-        <v>0</v>
-      </c>
-      <c r="N39" s="5">
-        <f t="shared" ref="N39" si="111">IF(ISBLANK(D39),0,(D39*N$2/D$2))</f>
-        <v>0</v>
-      </c>
+      <c r="G39" s="3"/>
+      <c r="H39" s="5"/>
     </row>
     <row r="40" spans="1:31">
-      <c r="G40" s="3"/>
-      <c r="H40" s="5"/>
+      <c r="A40" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40" s="10"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="10"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="12"/>
+      <c r="G40" s="11"/>
+      <c r="H40" s="10"/>
+      <c r="I40" s="12"/>
+      <c r="J40" s="11"/>
+      <c r="K40" s="10"/>
+      <c r="L40" s="10"/>
+      <c r="M40" s="11"/>
+      <c r="N40" s="10"/>
     </row>
     <row r="41" spans="1:31">
-      <c r="A41" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B41" s="10"/>
-      <c r="C41" s="10"/>
-      <c r="D41" s="10"/>
-      <c r="E41" s="10"/>
-      <c r="F41" s="10"/>
-      <c r="G41" s="10"/>
-      <c r="H41" s="10"/>
-      <c r="I41" s="10"/>
-      <c r="J41" s="10"/>
-      <c r="K41" s="10"/>
-      <c r="L41" s="10"/>
-      <c r="M41" s="10"/>
-      <c r="N41" s="10"/>
+      <c r="G41" s="3"/>
+      <c r="H41" s="5"/>
     </row>
     <row r="42" spans="1:31">
-      <c r="G42" s="3"/>
-      <c r="H42" s="5"/>
+      <c r="A42" t="s">
+        <v>9</v>
+      </c>
+      <c r="C42" s="3">
+        <v>572</v>
+      </c>
+      <c r="D42" s="5">
+        <v>1440</v>
+      </c>
+      <c r="E42" s="1">
+        <f t="shared" ref="E42" si="112" xml:space="preserve"> C42/C$2</f>
+        <v>0.22343750000000001</v>
+      </c>
+      <c r="F42" s="1">
+        <f t="shared" ref="F42" si="113" xml:space="preserve"> D42/D$2</f>
+        <v>1</v>
+      </c>
+      <c r="G42" s="3">
+        <f t="shared" ref="G42" si="114">IF(ISBLANK(C42),0,(C42*G$2/C$2))</f>
+        <v>858</v>
+      </c>
+      <c r="H42" s="5">
+        <f t="shared" ref="H42" si="115">IF(ISBLANK(D42),0,(D42*H$2/D$2))</f>
+        <v>2160</v>
+      </c>
+      <c r="J42" s="3">
+        <f t="shared" ref="J42" si="116">IF(ISBLANK(C42),0,(C42*J$2/C$2))</f>
+        <v>429</v>
+      </c>
+      <c r="K42" s="5">
+        <f t="shared" ref="K42" si="117">IF(ISBLANK(D42),0,(D42*K$2/D$2))</f>
+        <v>1080</v>
+      </c>
+      <c r="M42" s="3">
+        <f t="shared" ref="M42" si="118">IF(ISBLANK(C42),0,(C42*M$2/C$2))</f>
+        <v>286</v>
+      </c>
+      <c r="N42" s="5">
+        <f t="shared" ref="N42" si="119">IF(ISBLANK(D42),0,(D42*N$2/D$2))</f>
+        <v>720</v>
+      </c>
     </row>
     <row r="43" spans="1:31">
-      <c r="A43" t="s">
-        <v>46</v>
-      </c>
-      <c r="C43" s="3">
-        <v>1744</v>
-      </c>
-      <c r="D43" s="5">
-        <v>800</v>
-      </c>
-      <c r="E43" s="1">
-        <f t="shared" ref="E43" si="112" xml:space="preserve"> C43/C$2</f>
-        <v>0.68125000000000002</v>
-      </c>
-      <c r="F43" s="1">
-        <f t="shared" ref="F43" si="113" xml:space="preserve"> D43/D$2</f>
-        <v>0.55555555555555558</v>
-      </c>
-      <c r="G43" s="3">
-        <f t="shared" ref="G43" si="114">IF(ISBLANK(C43),0,(C43*G$2/C$2))</f>
-        <v>2616</v>
-      </c>
-      <c r="H43" s="5">
-        <f t="shared" ref="H43" si="115">IF(ISBLANK(D43),0,(D43*H$2/D$2))</f>
-        <v>1200</v>
-      </c>
-      <c r="J43" s="3">
-        <f t="shared" ref="J43" si="116">IF(ISBLANK(C43),0,(C43*J$2/C$2))</f>
-        <v>1308</v>
-      </c>
-      <c r="K43" s="5">
-        <f t="shared" ref="K43" si="117">IF(ISBLANK(D43),0,(D43*K$2/D$2))</f>
-        <v>600</v>
-      </c>
-      <c r="M43" s="3">
-        <f t="shared" ref="M43" si="118">IF(ISBLANK(C43),0,(C43*M$2/C$2))</f>
-        <v>872</v>
-      </c>
-      <c r="N43" s="5">
-        <f t="shared" ref="N43" si="119">IF(ISBLANK(D43),0,(D43*N$2/D$2))</f>
-        <v>400</v>
-      </c>
+      <c r="G43" s="3"/>
+      <c r="H43" s="5"/>
     </row>
     <row r="44" spans="1:31">
-      <c r="G44" s="3"/>
-      <c r="H44" s="5"/>
+      <c r="A44" t="s">
+        <v>42</v>
+      </c>
+      <c r="C44" s="3">
+        <v>220</v>
+      </c>
+      <c r="D44" s="5">
+        <v>292</v>
+      </c>
+      <c r="E44" s="1">
+        <f t="shared" ref="E44" si="120" xml:space="preserve"> C44/C$2</f>
+        <v>8.59375E-2</v>
+      </c>
+      <c r="F44" s="1">
+        <f t="shared" ref="F44" si="121" xml:space="preserve"> D44/D$2</f>
+        <v>0.20277777777777778</v>
+      </c>
+      <c r="G44" s="3">
+        <f t="shared" ref="G44" si="122">IF(ISBLANK(C44),0,(C44*G$2/C$2))</f>
+        <v>330</v>
+      </c>
+      <c r="H44" s="5">
+        <f t="shared" ref="H44" si="123">IF(ISBLANK(D44),0,(D44*H$2/D$2))</f>
+        <v>438</v>
+      </c>
+      <c r="J44" s="3">
+        <f t="shared" ref="J44" si="124">IF(ISBLANK(C44),0,(C44*J$2/C$2))</f>
+        <v>165</v>
+      </c>
+      <c r="K44" s="5">
+        <f t="shared" ref="K44" si="125">IF(ISBLANK(D44),0,(D44*K$2/D$2))</f>
+        <v>219</v>
+      </c>
+      <c r="M44" s="3">
+        <f t="shared" ref="M44" si="126">IF(ISBLANK(C44),0,(C44*M$2/C$2))</f>
+        <v>110</v>
+      </c>
+      <c r="N44" s="5">
+        <f t="shared" ref="N44" si="127">IF(ISBLANK(D44),0,(D44*N$2/D$2))</f>
+        <v>146</v>
+      </c>
     </row>
     <row r="45" spans="1:31">
-      <c r="A45" t="s">
-        <v>47</v>
-      </c>
-      <c r="C45" s="3">
-        <v>160</v>
-      </c>
-      <c r="D45" s="5">
-        <v>692</v>
-      </c>
-      <c r="E45" s="1">
-        <f t="shared" ref="E45" si="120" xml:space="preserve"> C45/C$2</f>
-        <v>6.25E-2</v>
-      </c>
-      <c r="F45" s="1">
-        <f t="shared" ref="F45" si="121" xml:space="preserve"> D45/D$2</f>
-        <v>0.48055555555555557</v>
-      </c>
-      <c r="G45" s="3">
-        <f t="shared" ref="G45" si="122">IF(ISBLANK(C45),0,(C45*G$2/C$2))</f>
-        <v>240</v>
-      </c>
-      <c r="H45" s="5">
-        <f t="shared" ref="H45" si="123">IF(ISBLANK(D45),0,(D45*H$2/D$2))</f>
-        <v>1038</v>
-      </c>
-      <c r="J45" s="3">
-        <f t="shared" ref="J45" si="124">IF(ISBLANK(C45),0,(C45*J$2/C$2))</f>
-        <v>120</v>
-      </c>
-      <c r="K45" s="5">
-        <f t="shared" ref="K45" si="125">IF(ISBLANK(D45),0,(D45*K$2/D$2))</f>
-        <v>519</v>
-      </c>
-      <c r="M45" s="3">
-        <f t="shared" ref="M45" si="126">IF(ISBLANK(C45),0,(C45*M$2/C$2))</f>
-        <v>80</v>
-      </c>
-      <c r="N45" s="5">
-        <f t="shared" ref="N45" si="127">IF(ISBLANK(D45),0,(D45*N$2/D$2))</f>
-        <v>346</v>
-      </c>
+      <c r="G45" s="3"/>
+      <c r="H45" s="5"/>
     </row>
     <row r="46" spans="1:31">
-      <c r="G46" s="3"/>
-      <c r="H46" s="5"/>
-    </row>
-    <row r="47" spans="1:31">
+      <c r="A46" t="s">
+        <v>43</v>
+      </c>
+      <c r="C46" s="3">
+        <v>140</v>
+      </c>
+      <c r="D46" s="5">
+        <v>200</v>
+      </c>
+      <c r="E46" s="1">
+        <f t="shared" ref="E46" si="128" xml:space="preserve"> C46/C$2</f>
+        <v>5.46875E-2</v>
+      </c>
+      <c r="F46" s="1">
+        <f t="shared" ref="F46" si="129" xml:space="preserve"> D46/D$2</f>
+        <v>0.1388888888888889</v>
+      </c>
+      <c r="G46" s="3">
+        <f t="shared" ref="G46" si="130">IF(ISBLANK(C46),0,(C46*G$2/C$2))</f>
+        <v>210</v>
+      </c>
+      <c r="H46" s="5">
+        <f t="shared" ref="H46" si="131">IF(ISBLANK(D46),0,(D46*H$2/D$2))</f>
+        <v>300</v>
+      </c>
+      <c r="J46" s="3">
+        <f t="shared" ref="J46" si="132">IF(ISBLANK(C46),0,(C46*J$2/C$2))</f>
+        <v>105</v>
+      </c>
+      <c r="K46" s="5">
+        <f t="shared" ref="K46" si="133">IF(ISBLANK(D46),0,(D46*K$2/D$2))</f>
+        <v>150</v>
+      </c>
+      <c r="M46" s="3">
+        <f t="shared" ref="M46" si="134">IF(ISBLANK(C46),0,(C46*M$2/C$2))</f>
+        <v>70</v>
+      </c>
+      <c r="N46" s="5">
+        <f t="shared" ref="N46" si="135">IF(ISBLANK(D46),0,(D46*N$2/D$2))</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="1:31" s="10" customFormat="1">
+      <c r="A47"/>
+      <c r="B47"/>
+      <c r="C47" s="3"/>
+      <c r="D47" s="5"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
       <c r="G47" s="3"/>
       <c r="H47" s="5"/>
+      <c r="I47" s="1"/>
+      <c r="J47" s="3"/>
+      <c r="K47" s="5"/>
+      <c r="L47"/>
+      <c r="M47" s="3"/>
+      <c r="N47" s="5"/>
+      <c r="O47"/>
+      <c r="P47"/>
+      <c r="Q47"/>
+      <c r="R47"/>
+      <c r="S47"/>
+      <c r="T47"/>
+      <c r="U47"/>
+      <c r="V47"/>
+      <c r="W47"/>
+      <c r="X47"/>
+      <c r="Y47"/>
+      <c r="Z47"/>
+      <c r="AA47"/>
+      <c r="AB47"/>
+      <c r="AC47"/>
+      <c r="AD47"/>
+      <c r="AE47"/>
     </row>
     <row r="48" spans="1:31">
-      <c r="G48" s="3"/>
-      <c r="H48" s="5"/>
+      <c r="E48" s="1">
+        <f t="shared" ref="E48" si="136" xml:space="preserve"> C48/C$2</f>
+        <v>0</v>
+      </c>
+      <c r="F48" s="1">
+        <f t="shared" ref="F48" si="137" xml:space="preserve"> D48/D$2</f>
+        <v>0</v>
+      </c>
+      <c r="G48" s="3">
+        <f t="shared" ref="G48" si="138">IF(ISBLANK(C48),0,(C48*G$2/C$2))</f>
+        <v>0</v>
+      </c>
+      <c r="H48" s="5">
+        <f t="shared" ref="H48" si="139">IF(ISBLANK(D48),0,(D48*H$2/D$2))</f>
+        <v>0</v>
+      </c>
+      <c r="J48" s="3">
+        <f t="shared" ref="J48" si="140">IF(ISBLANK(C48),0,(C48*J$2/C$2))</f>
+        <v>0</v>
+      </c>
+      <c r="K48" s="5">
+        <f t="shared" ref="K48" si="141">IF(ISBLANK(D48),0,(D48*K$2/D$2))</f>
+        <v>0</v>
+      </c>
+      <c r="M48" s="3">
+        <f t="shared" ref="M48" si="142">IF(ISBLANK(C48),0,(C48*M$2/C$2))</f>
+        <v>0</v>
+      </c>
+      <c r="N48" s="5">
+        <f t="shared" ref="N48" si="143">IF(ISBLANK(D48),0,(D48*N$2/D$2))</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="49" spans="1:14">
       <c r="G49" s="3"/>
       <c r="H49" s="5"/>
     </row>
     <row r="50" spans="1:14">
-      <c r="G50" s="3"/>
-      <c r="H50" s="5"/>
+      <c r="E50" s="1">
+        <f t="shared" ref="E50" si="144" xml:space="preserve"> C50/C$2</f>
+        <v>0</v>
+      </c>
+      <c r="F50" s="1">
+        <f t="shared" ref="F50" si="145" xml:space="preserve"> D50/D$2</f>
+        <v>0</v>
+      </c>
+      <c r="G50" s="3">
+        <f t="shared" ref="G50" si="146">IF(ISBLANK(C50),0,(C50*G$2/C$2))</f>
+        <v>0</v>
+      </c>
+      <c r="H50" s="5">
+        <f t="shared" ref="H50" si="147">IF(ISBLANK(D50),0,(D50*H$2/D$2))</f>
+        <v>0</v>
+      </c>
+      <c r="J50" s="3">
+        <f t="shared" ref="J50" si="148">IF(ISBLANK(C50),0,(C50*J$2/C$2))</f>
+        <v>0</v>
+      </c>
+      <c r="K50" s="5">
+        <f t="shared" ref="K50" si="149">IF(ISBLANK(D50),0,(D50*K$2/D$2))</f>
+        <v>0</v>
+      </c>
+      <c r="M50" s="3">
+        <f t="shared" ref="M50" si="150">IF(ISBLANK(C50),0,(C50*M$2/C$2))</f>
+        <v>0</v>
+      </c>
+      <c r="N50" s="5">
+        <f t="shared" ref="N50" si="151">IF(ISBLANK(D50),0,(D50*N$2/D$2))</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="51" spans="1:14">
       <c r="G51" s="3"/>
       <c r="H51" s="5"/>
     </row>
     <row r="52" spans="1:14">
-      <c r="G52" s="3"/>
-      <c r="H52" s="5"/>
+      <c r="A52" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B52" s="10"/>
+      <c r="C52" s="10"/>
+      <c r="D52" s="10"/>
+      <c r="E52" s="10"/>
+      <c r="F52" s="10"/>
+      <c r="G52" s="10"/>
+      <c r="H52" s="10"/>
+      <c r="I52" s="10"/>
+      <c r="J52" s="10"/>
+      <c r="K52" s="10"/>
+      <c r="L52" s="10"/>
+      <c r="M52" s="10"/>
+      <c r="N52" s="10"/>
     </row>
     <row r="53" spans="1:14">
       <c r="G53" s="3"/>
       <c r="H53" s="5"/>
     </row>
     <row r="54" spans="1:14">
-      <c r="G54" s="3"/>
-      <c r="H54" s="5"/>
+      <c r="A54" t="s">
+        <v>46</v>
+      </c>
+      <c r="C54" s="3">
+        <v>1744</v>
+      </c>
+      <c r="D54" s="5">
+        <v>800</v>
+      </c>
+      <c r="E54" s="1">
+        <f t="shared" ref="E54" si="152" xml:space="preserve"> C54/C$2</f>
+        <v>0.68125000000000002</v>
+      </c>
+      <c r="F54" s="1">
+        <f t="shared" ref="F54" si="153" xml:space="preserve"> D54/D$2</f>
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="G54" s="3">
+        <f t="shared" ref="G54" si="154">IF(ISBLANK(C54),0,(C54*G$2/C$2))</f>
+        <v>2616</v>
+      </c>
+      <c r="H54" s="5">
+        <f t="shared" ref="H54" si="155">IF(ISBLANK(D54),0,(D54*H$2/D$2))</f>
+        <v>1200</v>
+      </c>
+      <c r="J54" s="3">
+        <f t="shared" ref="J54" si="156">IF(ISBLANK(C54),0,(C54*J$2/C$2))</f>
+        <v>1308</v>
+      </c>
+      <c r="K54" s="5">
+        <f t="shared" ref="K54" si="157">IF(ISBLANK(D54),0,(D54*K$2/D$2))</f>
+        <v>600</v>
+      </c>
+      <c r="M54" s="3">
+        <f t="shared" ref="M54" si="158">IF(ISBLANK(C54),0,(C54*M$2/C$2))</f>
+        <v>872</v>
+      </c>
+      <c r="N54" s="5">
+        <f t="shared" ref="N54" si="159">IF(ISBLANK(D54),0,(D54*N$2/D$2))</f>
+        <v>400</v>
+      </c>
     </row>
     <row r="55" spans="1:14">
       <c r="G55" s="3"/>
       <c r="H55" s="5"/>
     </row>
     <row r="56" spans="1:14">
-      <c r="G56" s="3"/>
-      <c r="H56" s="5"/>
+      <c r="A56" t="s">
+        <v>47</v>
+      </c>
+      <c r="C56" s="3">
+        <v>160</v>
+      </c>
+      <c r="D56" s="5">
+        <v>692</v>
+      </c>
+      <c r="E56" s="1">
+        <f t="shared" ref="E56" si="160" xml:space="preserve"> C56/C$2</f>
+        <v>6.25E-2</v>
+      </c>
+      <c r="F56" s="1">
+        <f t="shared" ref="F56" si="161" xml:space="preserve"> D56/D$2</f>
+        <v>0.48055555555555557</v>
+      </c>
+      <c r="G56" s="3">
+        <f t="shared" ref="G56" si="162">IF(ISBLANK(C56),0,(C56*G$2/C$2))</f>
+        <v>240</v>
+      </c>
+      <c r="H56" s="5">
+        <f t="shared" ref="H56" si="163">IF(ISBLANK(D56),0,(D56*H$2/D$2))</f>
+        <v>1038</v>
+      </c>
+      <c r="J56" s="3">
+        <f t="shared" ref="J56" si="164">IF(ISBLANK(C56),0,(C56*J$2/C$2))</f>
+        <v>120</v>
+      </c>
+      <c r="K56" s="5">
+        <f t="shared" ref="K56" si="165">IF(ISBLANK(D56),0,(D56*K$2/D$2))</f>
+        <v>519</v>
+      </c>
+      <c r="M56" s="3">
+        <f t="shared" ref="M56" si="166">IF(ISBLANK(C56),0,(C56*M$2/C$2))</f>
+        <v>80</v>
+      </c>
+      <c r="N56" s="5">
+        <f t="shared" ref="N56" si="167">IF(ISBLANK(D56),0,(D56*N$2/D$2))</f>
+        <v>346</v>
+      </c>
     </row>
     <row r="57" spans="1:14">
       <c r="G57" s="3"/>
       <c r="H57" s="5"/>
     </row>
     <row r="58" spans="1:14">
-      <c r="A58" t="s">
-        <v>1</v>
-      </c>
-      <c r="C58" s="3">
-        <v>1660</v>
-      </c>
-      <c r="D58" s="5">
-        <v>300</v>
-      </c>
-      <c r="E58" s="1">
-        <f t="shared" ref="E58:F64" si="128" xml:space="preserve"> C58/C$2</f>
-        <v>0.6484375</v>
-      </c>
-      <c r="F58" s="1">
-        <f t="shared" si="128"/>
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="G58" s="3">
-        <f t="shared" ref="G58:H64" si="129">IF(ISBLANK(C58),0,(C58*G$2/C$2))</f>
-        <v>2490</v>
-      </c>
-      <c r="H58" s="5">
-        <f t="shared" si="129"/>
-        <v>450</v>
-      </c>
-      <c r="J58" s="3">
-        <f t="shared" ref="J58:K64" si="130">IF(ISBLANK(C58),0,(C58*J$2/C$2))</f>
-        <v>1245</v>
-      </c>
-      <c r="K58" s="5">
-        <f t="shared" si="130"/>
-        <v>225</v>
-      </c>
-      <c r="M58" s="3">
-        <f t="shared" ref="M58:N64" si="131">IF(ISBLANK(C58),0,(C58*M$2/C$2))</f>
-        <v>830</v>
-      </c>
-      <c r="N58" s="5">
-        <f t="shared" si="131"/>
-        <v>150</v>
-      </c>
+      <c r="G58" s="3"/>
+      <c r="H58" s="5"/>
     </row>
     <row r="59" spans="1:14">
-      <c r="E59" s="1">
-        <f t="shared" si="128"/>
-        <v>0</v>
-      </c>
-      <c r="F59" s="1">
-        <f t="shared" si="128"/>
-        <v>0</v>
-      </c>
-      <c r="G59" s="3">
-        <f t="shared" si="129"/>
-        <v>0</v>
-      </c>
-      <c r="H59" s="5">
-        <f t="shared" si="129"/>
-        <v>0</v>
-      </c>
-      <c r="J59" s="3">
-        <f t="shared" si="130"/>
-        <v>0</v>
-      </c>
-      <c r="K59" s="5">
-        <f t="shared" si="130"/>
-        <v>0</v>
-      </c>
-      <c r="M59" s="3">
-        <f t="shared" si="131"/>
-        <v>0</v>
-      </c>
-      <c r="N59" s="5">
-        <f t="shared" si="131"/>
-        <v>0</v>
-      </c>
+      <c r="G59" s="3"/>
+      <c r="H59" s="5"/>
     </row>
     <row r="60" spans="1:14">
-      <c r="A60" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="3">
-        <v>1372</v>
-      </c>
-      <c r="D60" s="5">
-        <v>588</v>
-      </c>
-      <c r="E60" s="1">
-        <f t="shared" si="128"/>
-        <v>0.53593749999999996</v>
-      </c>
-      <c r="F60" s="1">
-        <f t="shared" si="128"/>
-        <v>0.40833333333333333</v>
-      </c>
-      <c r="G60" s="3">
-        <f t="shared" si="129"/>
-        <v>2058</v>
-      </c>
-      <c r="H60" s="5">
-        <f t="shared" si="129"/>
-        <v>882</v>
-      </c>
-      <c r="J60" s="3">
-        <f t="shared" si="130"/>
-        <v>1029</v>
-      </c>
-      <c r="K60" s="5">
-        <f t="shared" si="130"/>
-        <v>441</v>
-      </c>
-      <c r="M60" s="3">
-        <f t="shared" si="131"/>
-        <v>686</v>
-      </c>
-      <c r="N60" s="5">
-        <f t="shared" si="131"/>
-        <v>294</v>
-      </c>
+      <c r="G60" s="3"/>
+      <c r="H60" s="5"/>
     </row>
     <row r="61" spans="1:14">
-      <c r="E61" s="1">
-        <f t="shared" si="128"/>
-        <v>0</v>
-      </c>
-      <c r="F61" s="1">
-        <f t="shared" si="128"/>
-        <v>0</v>
-      </c>
-      <c r="G61" s="3">
-        <f t="shared" si="129"/>
-        <v>0</v>
-      </c>
-      <c r="H61" s="5">
-        <f t="shared" si="129"/>
-        <v>0</v>
-      </c>
-      <c r="J61" s="3">
-        <f t="shared" si="130"/>
-        <v>0</v>
-      </c>
-      <c r="K61" s="5">
-        <f t="shared" si="130"/>
-        <v>0</v>
-      </c>
-      <c r="M61" s="3">
-        <f t="shared" si="131"/>
-        <v>0</v>
-      </c>
-      <c r="N61" s="5">
-        <f t="shared" si="131"/>
-        <v>0</v>
-      </c>
+      <c r="G61" s="3"/>
+      <c r="H61" s="5"/>
     </row>
     <row r="62" spans="1:14">
-      <c r="A62" t="s">
-        <v>0</v>
-      </c>
-      <c r="C62" s="3">
-        <v>280</v>
-      </c>
-      <c r="D62" s="5">
-        <v>156</v>
-      </c>
-      <c r="E62" s="1">
-        <f t="shared" si="128"/>
-        <v>0.109375</v>
-      </c>
-      <c r="F62" s="1">
-        <f t="shared" si="128"/>
-        <v>0.10833333333333334</v>
-      </c>
-      <c r="G62" s="3">
-        <f t="shared" si="129"/>
-        <v>420</v>
-      </c>
-      <c r="H62" s="5">
-        <f t="shared" si="129"/>
-        <v>234</v>
-      </c>
-      <c r="J62" s="3">
-        <f t="shared" si="130"/>
-        <v>210</v>
-      </c>
-      <c r="K62" s="5">
-        <f t="shared" si="130"/>
-        <v>117</v>
-      </c>
-      <c r="M62" s="3">
-        <f t="shared" si="131"/>
-        <v>140</v>
-      </c>
-      <c r="N62" s="5">
-        <f t="shared" si="131"/>
-        <v>78</v>
-      </c>
+      <c r="G62" s="3"/>
+      <c r="H62" s="5"/>
     </row>
     <row r="63" spans="1:14">
-      <c r="E63" s="1">
-        <f t="shared" si="128"/>
-        <v>0</v>
-      </c>
-      <c r="F63" s="1">
-        <f t="shared" si="128"/>
-        <v>0</v>
-      </c>
-      <c r="G63" s="3">
-        <f t="shared" si="129"/>
-        <v>0</v>
-      </c>
-      <c r="H63" s="5">
-        <f t="shared" si="129"/>
-        <v>0</v>
-      </c>
-      <c r="J63" s="3">
-        <f t="shared" si="130"/>
-        <v>0</v>
-      </c>
-      <c r="K63" s="5">
-        <f t="shared" si="130"/>
-        <v>0</v>
-      </c>
-      <c r="M63" s="3">
-        <f t="shared" si="131"/>
-        <v>0</v>
-      </c>
-      <c r="N63" s="5">
-        <f t="shared" si="131"/>
-        <v>0</v>
-      </c>
+      <c r="G63" s="3"/>
+      <c r="H63" s="5"/>
     </row>
     <row r="64" spans="1:14">
-      <c r="A64" t="s">
-        <v>3</v>
-      </c>
-      <c r="C64" s="3">
-        <v>264</v>
-      </c>
-      <c r="D64" s="5">
-        <v>172</v>
-      </c>
-      <c r="E64" s="1">
-        <f t="shared" si="128"/>
-        <v>0.10312499999999999</v>
-      </c>
-      <c r="F64" s="1">
-        <f t="shared" si="128"/>
-        <v>0.11944444444444445</v>
-      </c>
-      <c r="G64" s="3">
-        <f t="shared" si="129"/>
-        <v>396</v>
-      </c>
-      <c r="H64" s="5">
-        <f t="shared" si="129"/>
-        <v>258</v>
-      </c>
-      <c r="J64" s="3">
-        <f t="shared" si="130"/>
-        <v>198</v>
-      </c>
-      <c r="K64" s="5">
-        <f t="shared" si="130"/>
-        <v>129</v>
-      </c>
-      <c r="M64" s="3">
-        <f t="shared" si="131"/>
-        <v>132</v>
-      </c>
-      <c r="N64" s="5">
-        <f t="shared" si="131"/>
-        <v>86</v>
-      </c>
+      <c r="G64" s="3"/>
+      <c r="H64" s="5"/>
     </row>
     <row r="65" spans="1:14">
       <c r="G65" s="3"/>
       <c r="H65" s="5"/>
     </row>
     <row r="66" spans="1:14">
-      <c r="A66" t="s">
+      <c r="G66" s="3"/>
+      <c r="H66" s="5"/>
+    </row>
+    <row r="67" spans="1:14">
+      <c r="G67" s="3"/>
+      <c r="H67" s="5"/>
+    </row>
+    <row r="68" spans="1:14">
+      <c r="G68" s="3"/>
+      <c r="H68" s="5"/>
+    </row>
+    <row r="69" spans="1:14">
+      <c r="A69" t="s">
+        <v>1</v>
+      </c>
+      <c r="C69" s="3">
+        <v>1660</v>
+      </c>
+      <c r="D69" s="5">
+        <v>300</v>
+      </c>
+      <c r="E69" s="1">
+        <f t="shared" ref="E69:F75" si="168" xml:space="preserve"> C69/C$2</f>
+        <v>0.6484375</v>
+      </c>
+      <c r="F69" s="1">
+        <f t="shared" si="168"/>
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="G69" s="3">
+        <f t="shared" ref="G69:H75" si="169">IF(ISBLANK(C69),0,(C69*G$2/C$2))</f>
+        <v>2490</v>
+      </c>
+      <c r="H69" s="5">
+        <f t="shared" si="169"/>
+        <v>450</v>
+      </c>
+      <c r="J69" s="3">
+        <f t="shared" ref="J69:K75" si="170">IF(ISBLANK(C69),0,(C69*J$2/C$2))</f>
+        <v>1245</v>
+      </c>
+      <c r="K69" s="5">
+        <f t="shared" si="170"/>
+        <v>225</v>
+      </c>
+      <c r="M69" s="3">
+        <f t="shared" ref="M69:N75" si="171">IF(ISBLANK(C69),0,(C69*M$2/C$2))</f>
+        <v>830</v>
+      </c>
+      <c r="N69" s="5">
+        <f t="shared" si="171"/>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14">
+      <c r="E70" s="1">
+        <f t="shared" si="168"/>
+        <v>0</v>
+      </c>
+      <c r="F70" s="1">
+        <f t="shared" si="168"/>
+        <v>0</v>
+      </c>
+      <c r="G70" s="3">
+        <f t="shared" si="169"/>
+        <v>0</v>
+      </c>
+      <c r="H70" s="5">
+        <f t="shared" si="169"/>
+        <v>0</v>
+      </c>
+      <c r="J70" s="3">
+        <f t="shared" si="170"/>
+        <v>0</v>
+      </c>
+      <c r="K70" s="5">
+        <f t="shared" si="170"/>
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
+        <f t="shared" si="171"/>
+        <v>0</v>
+      </c>
+      <c r="N70" s="5">
+        <f t="shared" si="171"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14">
+      <c r="A71" t="s">
+        <v>2</v>
+      </c>
+      <c r="C71" s="3">
+        <v>1372</v>
+      </c>
+      <c r="D71" s="5">
+        <v>588</v>
+      </c>
+      <c r="E71" s="1">
+        <f t="shared" si="168"/>
+        <v>0.53593749999999996</v>
+      </c>
+      <c r="F71" s="1">
+        <f t="shared" si="168"/>
+        <v>0.40833333333333333</v>
+      </c>
+      <c r="G71" s="3">
+        <f t="shared" si="169"/>
+        <v>2058</v>
+      </c>
+      <c r="H71" s="5">
+        <f t="shared" si="169"/>
+        <v>882</v>
+      </c>
+      <c r="J71" s="3">
+        <f t="shared" si="170"/>
+        <v>1029</v>
+      </c>
+      <c r="K71" s="5">
+        <f t="shared" si="170"/>
+        <v>441</v>
+      </c>
+      <c r="M71" s="3">
+        <f t="shared" si="171"/>
+        <v>686</v>
+      </c>
+      <c r="N71" s="5">
+        <f t="shared" si="171"/>
+        <v>294</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14">
+      <c r="E72" s="1">
+        <f t="shared" si="168"/>
+        <v>0</v>
+      </c>
+      <c r="F72" s="1">
+        <f t="shared" si="168"/>
+        <v>0</v>
+      </c>
+      <c r="G72" s="3">
+        <f t="shared" si="169"/>
+        <v>0</v>
+      </c>
+      <c r="H72" s="5">
+        <f t="shared" si="169"/>
+        <v>0</v>
+      </c>
+      <c r="J72" s="3">
+        <f t="shared" si="170"/>
+        <v>0</v>
+      </c>
+      <c r="K72" s="5">
+        <f t="shared" si="170"/>
+        <v>0</v>
+      </c>
+      <c r="M72" s="3">
+        <f t="shared" si="171"/>
+        <v>0</v>
+      </c>
+      <c r="N72" s="5">
+        <f t="shared" si="171"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14">
+      <c r="A73" t="s">
+        <v>0</v>
+      </c>
+      <c r="C73" s="3">
+        <v>280</v>
+      </c>
+      <c r="D73" s="5">
+        <v>156</v>
+      </c>
+      <c r="E73" s="1">
+        <f t="shared" si="168"/>
+        <v>0.109375</v>
+      </c>
+      <c r="F73" s="1">
+        <f t="shared" si="168"/>
+        <v>0.10833333333333334</v>
+      </c>
+      <c r="G73" s="3">
+        <f t="shared" si="169"/>
+        <v>420</v>
+      </c>
+      <c r="H73" s="5">
+        <f t="shared" si="169"/>
+        <v>234</v>
+      </c>
+      <c r="J73" s="3">
+        <f t="shared" si="170"/>
+        <v>210</v>
+      </c>
+      <c r="K73" s="5">
+        <f t="shared" si="170"/>
+        <v>117</v>
+      </c>
+      <c r="M73" s="3">
+        <f t="shared" si="171"/>
+        <v>140</v>
+      </c>
+      <c r="N73" s="5">
+        <f t="shared" si="171"/>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14">
+      <c r="E74" s="1">
+        <f t="shared" si="168"/>
+        <v>0</v>
+      </c>
+      <c r="F74" s="1">
+        <f t="shared" si="168"/>
+        <v>0</v>
+      </c>
+      <c r="G74" s="3">
+        <f t="shared" si="169"/>
+        <v>0</v>
+      </c>
+      <c r="H74" s="5">
+        <f t="shared" si="169"/>
+        <v>0</v>
+      </c>
+      <c r="J74" s="3">
+        <f t="shared" si="170"/>
+        <v>0</v>
+      </c>
+      <c r="K74" s="5">
+        <f t="shared" si="170"/>
+        <v>0</v>
+      </c>
+      <c r="M74" s="3">
+        <f t="shared" si="171"/>
+        <v>0</v>
+      </c>
+      <c r="N74" s="5">
+        <f t="shared" si="171"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14">
+      <c r="A75" t="s">
+        <v>3</v>
+      </c>
+      <c r="C75" s="3">
+        <v>264</v>
+      </c>
+      <c r="D75" s="5">
+        <v>172</v>
+      </c>
+      <c r="E75" s="1">
+        <f t="shared" si="168"/>
+        <v>0.10312499999999999</v>
+      </c>
+      <c r="F75" s="1">
+        <f t="shared" si="168"/>
+        <v>0.11944444444444445</v>
+      </c>
+      <c r="G75" s="3">
+        <f t="shared" si="169"/>
+        <v>396</v>
+      </c>
+      <c r="H75" s="5">
+        <f t="shared" si="169"/>
+        <v>258</v>
+      </c>
+      <c r="J75" s="3">
+        <f t="shared" si="170"/>
+        <v>198</v>
+      </c>
+      <c r="K75" s="5">
+        <f t="shared" si="170"/>
+        <v>129</v>
+      </c>
+      <c r="M75" s="3">
+        <f t="shared" si="171"/>
+        <v>132</v>
+      </c>
+      <c r="N75" s="5">
+        <f t="shared" si="171"/>
+        <v>86</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14">
+      <c r="G76" s="3"/>
+      <c r="H76" s="5"/>
+    </row>
+    <row r="77" spans="1:14">
+      <c r="A77" t="s">
         <v>4</v>
       </c>
-      <c r="C66" s="3">
+      <c r="C77" s="3">
         <v>1200</v>
       </c>
-      <c r="D66" s="5">
+      <c r="D77" s="5">
         <v>944</v>
       </c>
-      <c r="E66" s="1">
-        <f t="shared" ref="E66:E113" si="132" xml:space="preserve"> C66/C$2</f>
+      <c r="E77" s="1">
+        <f t="shared" ref="E77:E124" si="172" xml:space="preserve"> C77/C$2</f>
         <v>0.46875</v>
       </c>
-      <c r="F66" s="1">
-        <f t="shared" ref="F66:F113" si="133" xml:space="preserve"> D66/D$2</f>
+      <c r="F77" s="1">
+        <f t="shared" ref="F77:F124" si="173" xml:space="preserve"> D77/D$2</f>
         <v>0.65555555555555556</v>
       </c>
-      <c r="G66" s="3">
-        <f t="shared" ref="G66:G113" si="134">IF(ISBLANK(C66),0,(C66*G$2/C$2))</f>
+      <c r="G77" s="3">
+        <f t="shared" ref="G77:G124" si="174">IF(ISBLANK(C77),0,(C77*G$2/C$2))</f>
         <v>1800</v>
       </c>
-      <c r="H66" s="5">
-        <f t="shared" ref="H66:H113" si="135">IF(ISBLANK(D66),0,(D66*H$2/D$2))</f>
+      <c r="H77" s="5">
+        <f t="shared" ref="H77:H124" si="175">IF(ISBLANK(D77),0,(D77*H$2/D$2))</f>
         <v>1416</v>
       </c>
-      <c r="J66" s="3">
-        <f t="shared" ref="J66:J113" si="136">IF(ISBLANK(C66),0,(C66*J$2/C$2))</f>
+      <c r="J77" s="3">
+        <f t="shared" ref="J77:J124" si="176">IF(ISBLANK(C77),0,(C77*J$2/C$2))</f>
         <v>900</v>
       </c>
-      <c r="K66" s="5">
-        <f t="shared" ref="K66:K113" si="137">IF(ISBLANK(D66),0,(D66*K$2/D$2))</f>
+      <c r="K77" s="5">
+        <f t="shared" ref="K77:K124" si="177">IF(ISBLANK(D77),0,(D77*K$2/D$2))</f>
         <v>708</v>
       </c>
-      <c r="M66" s="3">
-        <f t="shared" ref="M66:M113" si="138">IF(ISBLANK(C66),0,(C66*M$2/C$2))</f>
+      <c r="M77" s="3">
+        <f t="shared" ref="M77:M124" si="178">IF(ISBLANK(C77),0,(C77*M$2/C$2))</f>
         <v>600</v>
       </c>
-      <c r="N66" s="5">
-        <f t="shared" ref="N66:N113" si="139">IF(ISBLANK(D66),0,(D66*N$2/D$2))</f>
+      <c r="N77" s="5">
+        <f t="shared" ref="N77:N124" si="179">IF(ISBLANK(D77),0,(D77*N$2/D$2))</f>
         <v>472</v>
       </c>
     </row>
-    <row r="67" spans="1:14">
-      <c r="E67" s="1">
-        <f t="shared" si="132"/>
-        <v>0</v>
-      </c>
-      <c r="F67" s="1">
-        <f t="shared" si="133"/>
-        <v>0</v>
-      </c>
-      <c r="G67" s="3">
-        <f t="shared" si="134"/>
-        <v>0</v>
-      </c>
-      <c r="H67" s="5">
-        <f t="shared" si="135"/>
-        <v>0</v>
-      </c>
-      <c r="J67" s="3">
-        <f t="shared" si="136"/>
-        <v>0</v>
-      </c>
-      <c r="K67" s="5">
-        <f t="shared" si="137"/>
-        <v>0</v>
-      </c>
-      <c r="M67" s="3">
-        <f t="shared" si="138"/>
-        <v>0</v>
-      </c>
-      <c r="N67" s="5">
-        <f t="shared" si="139"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:14">
-      <c r="A68" t="s">
+    <row r="78" spans="1:14">
+      <c r="E78" s="1">
+        <f t="shared" si="172"/>
+        <v>0</v>
+      </c>
+      <c r="F78" s="1">
+        <f t="shared" si="173"/>
+        <v>0</v>
+      </c>
+      <c r="G78" s="3">
+        <f t="shared" si="174"/>
+        <v>0</v>
+      </c>
+      <c r="H78" s="5">
+        <f t="shared" si="175"/>
+        <v>0</v>
+      </c>
+      <c r="J78" s="3">
+        <f t="shared" si="176"/>
+        <v>0</v>
+      </c>
+      <c r="K78" s="5">
+        <f t="shared" si="177"/>
+        <v>0</v>
+      </c>
+      <c r="M78" s="3">
+        <f t="shared" si="178"/>
+        <v>0</v>
+      </c>
+      <c r="N78" s="5">
+        <f t="shared" si="179"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14">
+      <c r="A79" t="s">
         <v>6</v>
       </c>
-      <c r="C68" s="3">
+      <c r="C79" s="3">
         <v>420</v>
       </c>
-      <c r="D68" s="5">
+      <c r="D79" s="5">
         <v>1032</v>
       </c>
-      <c r="E68" s="1">
-        <f t="shared" si="132"/>
+      <c r="E79" s="1">
+        <f t="shared" si="172"/>
         <v>0.1640625</v>
       </c>
-      <c r="F68" s="1">
-        <f t="shared" si="133"/>
+      <c r="F79" s="1">
+        <f t="shared" si="173"/>
         <v>0.71666666666666667</v>
       </c>
-      <c r="G68" s="3">
-        <f t="shared" si="134"/>
+      <c r="G79" s="3">
+        <f t="shared" si="174"/>
         <v>630</v>
       </c>
-      <c r="H68" s="5">
-        <f t="shared" si="135"/>
+      <c r="H79" s="5">
+        <f t="shared" si="175"/>
         <v>1548</v>
       </c>
-      <c r="J68" s="3">
-        <f t="shared" si="136"/>
+      <c r="J79" s="3">
+        <f t="shared" si="176"/>
         <v>315</v>
       </c>
-      <c r="K68" s="5">
-        <f t="shared" si="137"/>
+      <c r="K79" s="5">
+        <f t="shared" si="177"/>
         <v>774</v>
       </c>
-      <c r="M68" s="3">
-        <f t="shared" si="138"/>
+      <c r="M79" s="3">
+        <f t="shared" si="178"/>
         <v>210</v>
       </c>
-      <c r="N68" s="5">
-        <f t="shared" si="139"/>
+      <c r="N79" s="5">
+        <f t="shared" si="179"/>
         <v>516</v>
       </c>
     </row>
-    <row r="69" spans="1:14">
-      <c r="E69" s="1">
-        <f t="shared" si="132"/>
-        <v>0</v>
-      </c>
-      <c r="F69" s="1">
-        <f t="shared" si="133"/>
-        <v>0</v>
-      </c>
-      <c r="G69" s="3">
-        <f t="shared" si="134"/>
-        <v>0</v>
-      </c>
-      <c r="H69" s="5">
-        <f t="shared" si="135"/>
-        <v>0</v>
-      </c>
-      <c r="J69" s="3">
-        <f t="shared" si="136"/>
-        <v>0</v>
-      </c>
-      <c r="K69" s="5">
-        <f t="shared" si="137"/>
-        <v>0</v>
-      </c>
-      <c r="M69" s="3">
-        <f t="shared" si="138"/>
-        <v>0</v>
-      </c>
-      <c r="N69" s="5">
-        <f t="shared" si="139"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:14">
-      <c r="A70" t="s">
+    <row r="80" spans="1:14">
+      <c r="E80" s="1">
+        <f t="shared" si="172"/>
+        <v>0</v>
+      </c>
+      <c r="F80" s="1">
+        <f t="shared" si="173"/>
+        <v>0</v>
+      </c>
+      <c r="G80" s="3">
+        <f t="shared" si="174"/>
+        <v>0</v>
+      </c>
+      <c r="H80" s="5">
+        <f t="shared" si="175"/>
+        <v>0</v>
+      </c>
+      <c r="J80" s="3">
+        <f t="shared" si="176"/>
+        <v>0</v>
+      </c>
+      <c r="K80" s="5">
+        <f t="shared" si="177"/>
+        <v>0</v>
+      </c>
+      <c r="M80" s="3">
+        <f t="shared" si="178"/>
+        <v>0</v>
+      </c>
+      <c r="N80" s="5">
+        <f t="shared" si="179"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14">
+      <c r="A81" t="s">
         <v>7</v>
       </c>
-      <c r="C70" s="3">
+      <c r="C81" s="3">
         <v>1360</v>
       </c>
-      <c r="D70" s="5">
+      <c r="D81" s="5">
         <v>952</v>
       </c>
-      <c r="E70" s="1">
-        <f t="shared" si="132"/>
+      <c r="E81" s="1">
+        <f t="shared" si="172"/>
         <v>0.53125</v>
       </c>
-      <c r="F70" s="1">
-        <f t="shared" si="133"/>
+      <c r="F81" s="1">
+        <f t="shared" si="173"/>
         <v>0.66111111111111109</v>
       </c>
-      <c r="G70" s="3">
-        <f t="shared" si="134"/>
+      <c r="G81" s="3">
+        <f t="shared" si="174"/>
         <v>2040</v>
       </c>
-      <c r="H70" s="5">
-        <f t="shared" si="135"/>
+      <c r="H81" s="5">
+        <f t="shared" si="175"/>
         <v>1428</v>
       </c>
-      <c r="J70" s="3">
-        <f t="shared" si="136"/>
+      <c r="J81" s="3">
+        <f t="shared" si="176"/>
         <v>1020</v>
       </c>
-      <c r="K70" s="5">
-        <f t="shared" si="137"/>
+      <c r="K81" s="5">
+        <f t="shared" si="177"/>
         <v>714</v>
       </c>
-      <c r="M70" s="3">
-        <f t="shared" si="138"/>
+      <c r="M81" s="3">
+        <f t="shared" si="178"/>
         <v>680</v>
       </c>
-      <c r="N70" s="5">
-        <f t="shared" si="139"/>
+      <c r="N81" s="5">
+        <f t="shared" si="179"/>
         <v>476</v>
       </c>
     </row>
-    <row r="71" spans="1:14">
-      <c r="E71" s="1">
-        <f t="shared" si="132"/>
-        <v>0</v>
-      </c>
-      <c r="F71" s="1">
-        <f t="shared" si="133"/>
-        <v>0</v>
-      </c>
-      <c r="G71" s="3">
-        <f t="shared" si="134"/>
-        <v>0</v>
-      </c>
-      <c r="H71" s="5">
-        <f t="shared" si="135"/>
-        <v>0</v>
-      </c>
-      <c r="J71" s="3">
-        <f t="shared" si="136"/>
-        <v>0</v>
-      </c>
-      <c r="K71" s="5">
-        <f t="shared" si="137"/>
-        <v>0</v>
-      </c>
-      <c r="M71" s="3">
-        <f t="shared" si="138"/>
-        <v>0</v>
-      </c>
-      <c r="N71" s="5">
-        <f t="shared" si="139"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:14">
-      <c r="A72" t="s">
+    <row r="82" spans="1:14">
+      <c r="E82" s="1">
+        <f t="shared" si="172"/>
+        <v>0</v>
+      </c>
+      <c r="F82" s="1">
+        <f t="shared" si="173"/>
+        <v>0</v>
+      </c>
+      <c r="G82" s="3">
+        <f t="shared" si="174"/>
+        <v>0</v>
+      </c>
+      <c r="H82" s="5">
+        <f t="shared" si="175"/>
+        <v>0</v>
+      </c>
+      <c r="J82" s="3">
+        <f t="shared" si="176"/>
+        <v>0</v>
+      </c>
+      <c r="K82" s="5">
+        <f t="shared" si="177"/>
+        <v>0</v>
+      </c>
+      <c r="M82" s="3">
+        <f t="shared" si="178"/>
+        <v>0</v>
+      </c>
+      <c r="N82" s="5">
+        <f t="shared" si="179"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14">
+      <c r="A83" t="s">
         <v>8</v>
       </c>
-      <c r="C72" s="3">
+      <c r="C83" s="3">
         <v>712</v>
       </c>
-      <c r="D72" s="5">
+      <c r="D83" s="5">
         <v>488</v>
       </c>
-      <c r="E72" s="1">
-        <f t="shared" si="132"/>
+      <c r="E83" s="1">
+        <f t="shared" si="172"/>
         <v>0.27812500000000001</v>
       </c>
-      <c r="F72" s="1">
-        <f t="shared" si="133"/>
+      <c r="F83" s="1">
+        <f t="shared" si="173"/>
         <v>0.33888888888888891</v>
       </c>
-      <c r="G72" s="3">
-        <f t="shared" si="134"/>
+      <c r="G83" s="3">
+        <f t="shared" si="174"/>
         <v>1068</v>
       </c>
-      <c r="H72" s="5">
-        <f t="shared" si="135"/>
+      <c r="H83" s="5">
+        <f t="shared" si="175"/>
         <v>732</v>
       </c>
-      <c r="J72" s="3">
-        <f t="shared" si="136"/>
+      <c r="J83" s="3">
+        <f t="shared" si="176"/>
         <v>534</v>
       </c>
-      <c r="K72" s="5">
-        <f t="shared" si="137"/>
+      <c r="K83" s="5">
+        <f t="shared" si="177"/>
         <v>366</v>
       </c>
-      <c r="M72" s="3">
-        <f t="shared" si="138"/>
+      <c r="M83" s="3">
+        <f t="shared" si="178"/>
         <v>356</v>
       </c>
-      <c r="N72" s="5">
-        <f t="shared" si="139"/>
+      <c r="N83" s="5">
+        <f t="shared" si="179"/>
         <v>244</v>
       </c>
     </row>
-    <row r="73" spans="1:14">
-      <c r="E73" s="1">
-        <f t="shared" si="132"/>
-        <v>0</v>
-      </c>
-      <c r="F73" s="1">
-        <f t="shared" si="133"/>
-        <v>0</v>
-      </c>
-      <c r="G73" s="3">
-        <f t="shared" si="134"/>
-        <v>0</v>
-      </c>
-      <c r="H73" s="5">
-        <f t="shared" si="135"/>
-        <v>0</v>
-      </c>
-      <c r="J73" s="3">
-        <f t="shared" si="136"/>
-        <v>0</v>
-      </c>
-      <c r="K73" s="5">
-        <f t="shared" si="137"/>
-        <v>0</v>
-      </c>
-      <c r="M73" s="3">
-        <f t="shared" si="138"/>
-        <v>0</v>
-      </c>
-      <c r="N73" s="5">
-        <f t="shared" si="139"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:14">
-      <c r="A74" t="s">
+    <row r="84" spans="1:14">
+      <c r="E84" s="1">
+        <f t="shared" si="172"/>
+        <v>0</v>
+      </c>
+      <c r="F84" s="1">
+        <f t="shared" si="173"/>
+        <v>0</v>
+      </c>
+      <c r="G84" s="3">
+        <f t="shared" si="174"/>
+        <v>0</v>
+      </c>
+      <c r="H84" s="5">
+        <f t="shared" si="175"/>
+        <v>0</v>
+      </c>
+      <c r="J84" s="3">
+        <f t="shared" si="176"/>
+        <v>0</v>
+      </c>
+      <c r="K84" s="5">
+        <f t="shared" si="177"/>
+        <v>0</v>
+      </c>
+      <c r="M84" s="3">
+        <f t="shared" si="178"/>
+        <v>0</v>
+      </c>
+      <c r="N84" s="5">
+        <f t="shared" si="179"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14">
+      <c r="A85" t="s">
         <v>10</v>
       </c>
-      <c r="D74" s="5">
+      <c r="D85" s="5">
         <v>412</v>
       </c>
-      <c r="E74" s="1">
-        <f t="shared" si="132"/>
-        <v>0</v>
-      </c>
-      <c r="F74" s="1">
-        <f t="shared" si="133"/>
+      <c r="E85" s="1">
+        <f t="shared" si="172"/>
+        <v>0</v>
+      </c>
+      <c r="F85" s="1">
+        <f t="shared" si="173"/>
         <v>0.28611111111111109</v>
       </c>
-      <c r="G74" s="3">
-        <f t="shared" si="134"/>
-        <v>0</v>
-      </c>
-      <c r="H74" s="5">
-        <f t="shared" si="135"/>
+      <c r="G85" s="3">
+        <f t="shared" si="174"/>
+        <v>0</v>
+      </c>
+      <c r="H85" s="5">
+        <f t="shared" si="175"/>
         <v>618</v>
       </c>
-      <c r="J74" s="3">
-        <f t="shared" si="136"/>
-        <v>0</v>
-      </c>
-      <c r="K74" s="5">
-        <f t="shared" si="137"/>
+      <c r="J85" s="3">
+        <f t="shared" si="176"/>
+        <v>0</v>
+      </c>
+      <c r="K85" s="5">
+        <f t="shared" si="177"/>
         <v>309</v>
       </c>
-      <c r="M74" s="3">
-        <f t="shared" si="138"/>
-        <v>0</v>
-      </c>
-      <c r="N74" s="5">
-        <f t="shared" si="139"/>
+      <c r="M85" s="3">
+        <f t="shared" si="178"/>
+        <v>0</v>
+      </c>
+      <c r="N85" s="5">
+        <f t="shared" si="179"/>
         <v>206</v>
       </c>
     </row>
-    <row r="75" spans="1:14">
-      <c r="E75" s="1">
-        <f t="shared" si="132"/>
-        <v>0</v>
-      </c>
-      <c r="F75" s="1">
-        <f t="shared" si="133"/>
-        <v>0</v>
-      </c>
-      <c r="G75" s="3">
-        <f t="shared" si="134"/>
-        <v>0</v>
-      </c>
-      <c r="H75" s="5">
-        <f t="shared" si="135"/>
-        <v>0</v>
-      </c>
-      <c r="J75" s="3">
-        <f t="shared" si="136"/>
-        <v>0</v>
-      </c>
-      <c r="K75" s="5">
-        <f t="shared" si="137"/>
-        <v>0</v>
-      </c>
-      <c r="M75" s="3">
-        <f t="shared" si="138"/>
-        <v>0</v>
-      </c>
-      <c r="N75" s="5">
-        <f t="shared" si="139"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:14">
-      <c r="A76" t="s">
+    <row r="86" spans="1:14">
+      <c r="E86" s="1">
+        <f t="shared" si="172"/>
+        <v>0</v>
+      </c>
+      <c r="F86" s="1">
+        <f t="shared" si="173"/>
+        <v>0</v>
+      </c>
+      <c r="G86" s="3">
+        <f t="shared" si="174"/>
+        <v>0</v>
+      </c>
+      <c r="H86" s="5">
+        <f t="shared" si="175"/>
+        <v>0</v>
+      </c>
+      <c r="J86" s="3">
+        <f t="shared" si="176"/>
+        <v>0</v>
+      </c>
+      <c r="K86" s="5">
+        <f t="shared" si="177"/>
+        <v>0</v>
+      </c>
+      <c r="M86" s="3">
+        <f t="shared" si="178"/>
+        <v>0</v>
+      </c>
+      <c r="N86" s="5">
+        <f t="shared" si="179"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14">
+      <c r="A87" t="s">
         <v>17</v>
       </c>
-      <c r="C76" s="3">
+      <c r="C87" s="3">
         <v>228</v>
       </c>
-      <c r="D76" s="5">
+      <c r="D87" s="5">
         <v>372</v>
       </c>
-      <c r="E76" s="1">
-        <f t="shared" si="132"/>
+      <c r="E87" s="1">
+        <f t="shared" si="172"/>
         <v>8.9062500000000003E-2</v>
       </c>
-      <c r="F76" s="1">
-        <f t="shared" si="133"/>
+      <c r="F87" s="1">
+        <f t="shared" si="173"/>
         <v>0.25833333333333336</v>
       </c>
-      <c r="G76" s="3">
-        <f t="shared" si="134"/>
+      <c r="G87" s="3">
+        <f t="shared" si="174"/>
         <v>342</v>
       </c>
-      <c r="H76" s="5">
-        <f t="shared" si="135"/>
+      <c r="H87" s="5">
+        <f t="shared" si="175"/>
         <v>558</v>
       </c>
-      <c r="J76" s="3">
-        <f t="shared" si="136"/>
+      <c r="J87" s="3">
+        <f t="shared" si="176"/>
         <v>171</v>
       </c>
-      <c r="K76" s="5">
-        <f t="shared" si="137"/>
+      <c r="K87" s="5">
+        <f t="shared" si="177"/>
         <v>279</v>
       </c>
-      <c r="M76" s="3">
-        <f t="shared" si="138"/>
+      <c r="M87" s="3">
+        <f t="shared" si="178"/>
         <v>114</v>
       </c>
-      <c r="N76" s="5">
-        <f t="shared" si="139"/>
+      <c r="N87" s="5">
+        <f t="shared" si="179"/>
         <v>186</v>
-      </c>
-    </row>
-    <row r="77" spans="1:14">
-      <c r="E77" s="1">
-        <f t="shared" si="132"/>
-        <v>0</v>
-      </c>
-      <c r="F77" s="1">
-        <f t="shared" si="133"/>
-        <v>0</v>
-      </c>
-      <c r="G77" s="3">
-        <f t="shared" si="134"/>
-        <v>0</v>
-      </c>
-      <c r="H77" s="5">
-        <f t="shared" si="135"/>
-        <v>0</v>
-      </c>
-      <c r="J77" s="3">
-        <f t="shared" si="136"/>
-        <v>0</v>
-      </c>
-      <c r="K77" s="5">
-        <f t="shared" si="137"/>
-        <v>0</v>
-      </c>
-      <c r="M77" s="3">
-        <f t="shared" si="138"/>
-        <v>0</v>
-      </c>
-      <c r="N77" s="5">
-        <f t="shared" si="139"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:14">
-      <c r="A78" t="s">
-        <v>5</v>
-      </c>
-      <c r="C78" s="3">
-        <v>1320</v>
-      </c>
-      <c r="D78" s="5">
-        <v>960</v>
-      </c>
-      <c r="E78" s="1">
-        <f t="shared" si="132"/>
-        <v>0.515625</v>
-      </c>
-      <c r="F78" s="1">
-        <f t="shared" si="133"/>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="G78" s="3">
-        <f t="shared" si="134"/>
-        <v>1980</v>
-      </c>
-      <c r="H78" s="5">
-        <f t="shared" si="135"/>
-        <v>1440</v>
-      </c>
-      <c r="J78" s="3">
-        <f t="shared" si="136"/>
-        <v>990</v>
-      </c>
-      <c r="K78" s="5">
-        <f t="shared" si="137"/>
-        <v>720</v>
-      </c>
-      <c r="M78" s="3">
-        <f t="shared" si="138"/>
-        <v>660</v>
-      </c>
-      <c r="N78" s="5">
-        <f t="shared" si="139"/>
-        <v>480</v>
-      </c>
-    </row>
-    <row r="79" spans="1:14">
-      <c r="E79" s="1">
-        <f t="shared" si="132"/>
-        <v>0</v>
-      </c>
-      <c r="F79" s="1">
-        <f t="shared" si="133"/>
-        <v>0</v>
-      </c>
-      <c r="G79" s="3">
-        <f t="shared" si="134"/>
-        <v>0</v>
-      </c>
-      <c r="H79" s="5">
-        <f t="shared" si="135"/>
-        <v>0</v>
-      </c>
-      <c r="J79" s="3">
-        <f t="shared" si="136"/>
-        <v>0</v>
-      </c>
-      <c r="K79" s="5">
-        <f t="shared" si="137"/>
-        <v>0</v>
-      </c>
-      <c r="M79" s="3">
-        <f t="shared" si="138"/>
-        <v>0</v>
-      </c>
-      <c r="N79" s="5">
-        <f t="shared" si="139"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:14">
-      <c r="A80" t="s">
-        <v>18</v>
-      </c>
-      <c r="D80" s="5">
-        <v>82</v>
-      </c>
-      <c r="E80" s="1">
-        <f t="shared" si="132"/>
-        <v>0</v>
-      </c>
-      <c r="F80" s="1">
-        <f t="shared" si="133"/>
-        <v>5.6944444444444443E-2</v>
-      </c>
-      <c r="G80" s="3">
-        <f t="shared" si="134"/>
-        <v>0</v>
-      </c>
-      <c r="H80" s="5">
-        <f t="shared" si="135"/>
-        <v>123</v>
-      </c>
-      <c r="J80" s="3">
-        <f t="shared" si="136"/>
-        <v>0</v>
-      </c>
-      <c r="K80" s="5">
-        <f t="shared" si="137"/>
-        <v>61.5</v>
-      </c>
-      <c r="M80" s="3">
-        <f t="shared" si="138"/>
-        <v>0</v>
-      </c>
-      <c r="N80" s="5">
-        <f t="shared" si="139"/>
-        <v>41</v>
-      </c>
-    </row>
-    <row r="81" spans="1:14">
-      <c r="E81" s="1">
-        <f t="shared" si="132"/>
-        <v>0</v>
-      </c>
-      <c r="F81" s="1">
-        <f t="shared" si="133"/>
-        <v>0</v>
-      </c>
-      <c r="G81" s="3">
-        <f t="shared" si="134"/>
-        <v>0</v>
-      </c>
-      <c r="H81" s="5">
-        <f t="shared" si="135"/>
-        <v>0</v>
-      </c>
-      <c r="J81" s="3">
-        <f t="shared" si="136"/>
-        <v>0</v>
-      </c>
-      <c r="K81" s="5">
-        <f t="shared" si="137"/>
-        <v>0</v>
-      </c>
-      <c r="M81" s="3">
-        <f t="shared" si="138"/>
-        <v>0</v>
-      </c>
-      <c r="N81" s="5">
-        <f t="shared" si="139"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:14">
-      <c r="A82" t="s">
-        <v>22</v>
-      </c>
-      <c r="C82" s="3">
-        <v>124</v>
-      </c>
-      <c r="D82" s="5">
-        <v>80</v>
-      </c>
-      <c r="E82" s="1">
-        <f t="shared" si="132"/>
-        <v>4.8437500000000001E-2</v>
-      </c>
-      <c r="F82" s="1">
-        <f t="shared" si="133"/>
-        <v>5.5555555555555552E-2</v>
-      </c>
-      <c r="G82" s="3">
-        <f t="shared" si="134"/>
-        <v>186</v>
-      </c>
-      <c r="H82" s="5">
-        <f t="shared" si="135"/>
-        <v>120</v>
-      </c>
-      <c r="J82" s="3">
-        <f t="shared" si="136"/>
-        <v>93</v>
-      </c>
-      <c r="K82" s="5">
-        <f t="shared" si="137"/>
-        <v>60</v>
-      </c>
-      <c r="M82" s="3">
-        <f t="shared" si="138"/>
-        <v>62</v>
-      </c>
-      <c r="N82" s="5">
-        <f t="shared" si="139"/>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="83" spans="1:14">
-      <c r="E83" s="1">
-        <f t="shared" si="132"/>
-        <v>0</v>
-      </c>
-      <c r="F83" s="1">
-        <f t="shared" si="133"/>
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <f t="shared" si="134"/>
-        <v>0</v>
-      </c>
-      <c r="H83" s="5">
-        <f t="shared" si="135"/>
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <f t="shared" si="136"/>
-        <v>0</v>
-      </c>
-      <c r="K83" s="5">
-        <f t="shared" si="137"/>
-        <v>0</v>
-      </c>
-      <c r="M83" s="3">
-        <f t="shared" si="138"/>
-        <v>0</v>
-      </c>
-      <c r="N83" s="5">
-        <f t="shared" si="139"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:14">
-      <c r="A84" t="s">
-        <v>23</v>
-      </c>
-      <c r="C84" s="3">
-        <v>124</v>
-      </c>
-      <c r="D84" s="5">
-        <v>100</v>
-      </c>
-      <c r="E84" s="1">
-        <f t="shared" si="132"/>
-        <v>4.8437500000000001E-2</v>
-      </c>
-      <c r="F84" s="1">
-        <f t="shared" si="133"/>
-        <v>6.9444444444444448E-2</v>
-      </c>
-      <c r="G84" s="3">
-        <f t="shared" si="134"/>
-        <v>186</v>
-      </c>
-      <c r="H84" s="5">
-        <f t="shared" si="135"/>
-        <v>150</v>
-      </c>
-      <c r="J84" s="3">
-        <f t="shared" si="136"/>
-        <v>93</v>
-      </c>
-      <c r="K84" s="5">
-        <f t="shared" si="137"/>
-        <v>75</v>
-      </c>
-      <c r="M84" s="3">
-        <f t="shared" si="138"/>
-        <v>62</v>
-      </c>
-      <c r="N84" s="5">
-        <f t="shared" si="139"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="85" spans="1:14">
-      <c r="E85" s="1">
-        <f t="shared" si="132"/>
-        <v>0</v>
-      </c>
-      <c r="F85" s="1">
-        <f t="shared" si="133"/>
-        <v>0</v>
-      </c>
-      <c r="G85" s="3">
-        <f t="shared" si="134"/>
-        <v>0</v>
-      </c>
-      <c r="H85" s="5">
-        <f t="shared" si="135"/>
-        <v>0</v>
-      </c>
-      <c r="J85" s="3">
-        <f t="shared" si="136"/>
-        <v>0</v>
-      </c>
-      <c r="K85" s="5">
-        <f t="shared" si="137"/>
-        <v>0</v>
-      </c>
-      <c r="M85" s="3">
-        <f t="shared" si="138"/>
-        <v>0</v>
-      </c>
-      <c r="N85" s="5">
-        <f t="shared" si="139"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:14">
-      <c r="A86" t="s">
-        <v>24</v>
-      </c>
-      <c r="C86" s="3">
-        <v>116</v>
-      </c>
-      <c r="D86" s="5">
-        <v>112</v>
-      </c>
-      <c r="E86" s="1">
-        <f t="shared" si="132"/>
-        <v>4.5312499999999999E-2</v>
-      </c>
-      <c r="F86" s="1">
-        <f t="shared" si="133"/>
-        <v>7.7777777777777779E-2</v>
-      </c>
-      <c r="G86" s="3">
-        <f t="shared" si="134"/>
-        <v>174</v>
-      </c>
-      <c r="H86" s="5">
-        <f t="shared" si="135"/>
-        <v>168</v>
-      </c>
-      <c r="J86" s="3">
-        <f t="shared" si="136"/>
-        <v>87</v>
-      </c>
-      <c r="K86" s="5">
-        <f t="shared" si="137"/>
-        <v>84</v>
-      </c>
-      <c r="M86" s="3">
-        <f t="shared" si="138"/>
-        <v>58</v>
-      </c>
-      <c r="N86" s="5">
-        <f t="shared" si="139"/>
-        <v>56</v>
-      </c>
-    </row>
-    <row r="87" spans="1:14">
-      <c r="E87" s="1">
-        <f t="shared" si="132"/>
-        <v>0</v>
-      </c>
-      <c r="F87" s="1">
-        <f t="shared" si="133"/>
-        <v>0</v>
-      </c>
-      <c r="G87" s="3">
-        <f t="shared" si="134"/>
-        <v>0</v>
-      </c>
-      <c r="H87" s="5">
-        <f t="shared" si="135"/>
-        <v>0</v>
-      </c>
-      <c r="J87" s="3">
-        <f t="shared" si="136"/>
-        <v>0</v>
-      </c>
-      <c r="K87" s="5">
-        <f t="shared" si="137"/>
-        <v>0</v>
-      </c>
-      <c r="M87" s="3">
-        <f t="shared" si="138"/>
-        <v>0</v>
-      </c>
-      <c r="N87" s="5">
-        <f t="shared" si="139"/>
-        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:14">
       <c r="E88" s="1">
-        <f t="shared" si="132"/>
+        <f t="shared" si="172"/>
         <v>0</v>
       </c>
       <c r="F88" s="1">
-        <f t="shared" si="133"/>
+        <f t="shared" si="173"/>
         <v>0</v>
       </c>
       <c r="G88" s="3">
-        <f t="shared" si="134"/>
+        <f t="shared" si="174"/>
         <v>0</v>
       </c>
       <c r="H88" s="5">
-        <f t="shared" si="135"/>
+        <f t="shared" si="175"/>
         <v>0</v>
       </c>
       <c r="J88" s="3">
-        <f t="shared" si="136"/>
+        <f t="shared" si="176"/>
         <v>0</v>
       </c>
       <c r="K88" s="5">
-        <f t="shared" si="137"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="M88" s="3">
-        <f t="shared" si="138"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="N88" s="5">
-        <f t="shared" si="139"/>
+        <f t="shared" si="179"/>
         <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:14">
       <c r="A89" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="C89" s="3">
-        <v>280</v>
+        <v>1320</v>
       </c>
       <c r="D89" s="5">
-        <v>84</v>
+        <v>960</v>
       </c>
       <c r="E89" s="1">
-        <f t="shared" si="132"/>
-        <v>0.109375</v>
+        <f t="shared" si="172"/>
+        <v>0.515625</v>
       </c>
       <c r="F89" s="1">
-        <f t="shared" si="133"/>
-        <v>5.8333333333333334E-2</v>
+        <f t="shared" si="173"/>
+        <v>0.66666666666666663</v>
       </c>
       <c r="G89" s="3">
-        <f t="shared" si="134"/>
-        <v>420</v>
+        <f t="shared" si="174"/>
+        <v>1980</v>
       </c>
       <c r="H89" s="5">
-        <f t="shared" si="135"/>
-        <v>126</v>
+        <f t="shared" si="175"/>
+        <v>1440</v>
       </c>
       <c r="J89" s="3">
-        <f t="shared" si="136"/>
-        <v>210</v>
+        <f t="shared" si="176"/>
+        <v>990</v>
       </c>
       <c r="K89" s="5">
-        <f t="shared" si="137"/>
-        <v>63</v>
+        <f t="shared" si="177"/>
+        <v>720</v>
       </c>
       <c r="M89" s="3">
-        <f t="shared" si="138"/>
-        <v>140</v>
+        <f t="shared" si="178"/>
+        <v>660</v>
       </c>
       <c r="N89" s="5">
-        <f t="shared" si="139"/>
-        <v>42</v>
+        <f t="shared" si="179"/>
+        <v>480</v>
       </c>
     </row>
     <row r="90" spans="1:14">
       <c r="E90" s="1">
-        <f t="shared" si="132"/>
+        <f t="shared" si="172"/>
         <v>0</v>
       </c>
       <c r="F90" s="1">
-        <f t="shared" si="133"/>
+        <f t="shared" si="173"/>
         <v>0</v>
       </c>
       <c r="G90" s="3">
-        <f t="shared" si="134"/>
+        <f t="shared" si="174"/>
         <v>0</v>
       </c>
       <c r="H90" s="5">
-        <f t="shared" si="135"/>
+        <f t="shared" si="175"/>
         <v>0</v>
       </c>
       <c r="J90" s="3">
-        <f t="shared" si="136"/>
+        <f t="shared" si="176"/>
         <v>0</v>
       </c>
       <c r="K90" s="5">
-        <f t="shared" si="137"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="M90" s="3">
-        <f t="shared" si="138"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="N90" s="5">
-        <f t="shared" si="139"/>
+        <f t="shared" si="179"/>
         <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:14">
       <c r="A91" t="s">
-        <v>27</v>
-      </c>
-      <c r="C91" s="3">
-        <v>660</v>
+        <v>18</v>
       </c>
       <c r="D91" s="5">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="E91" s="1">
-        <f t="shared" si="132"/>
-        <v>0.2578125</v>
+        <f t="shared" si="172"/>
+        <v>0</v>
       </c>
       <c r="F91" s="1">
-        <f t="shared" si="133"/>
-        <v>9.7222222222222224E-2</v>
+        <f t="shared" si="173"/>
+        <v>5.6944444444444443E-2</v>
       </c>
       <c r="G91" s="3">
-        <f t="shared" si="134"/>
-        <v>990</v>
+        <f t="shared" si="174"/>
+        <v>0</v>
       </c>
       <c r="H91" s="5">
-        <f t="shared" si="135"/>
-        <v>210</v>
+        <f t="shared" si="175"/>
+        <v>123</v>
       </c>
       <c r="J91" s="3">
-        <f t="shared" si="136"/>
-        <v>495</v>
+        <f t="shared" si="176"/>
+        <v>0</v>
       </c>
       <c r="K91" s="5">
-        <f t="shared" si="137"/>
-        <v>105</v>
+        <f t="shared" si="177"/>
+        <v>61.5</v>
       </c>
       <c r="M91" s="3">
-        <f t="shared" si="138"/>
-        <v>330</v>
+        <f t="shared" si="178"/>
+        <v>0</v>
       </c>
       <c r="N91" s="5">
-        <f t="shared" si="139"/>
-        <v>70</v>
+        <f t="shared" si="179"/>
+        <v>41</v>
       </c>
     </row>
     <row r="92" spans="1:14">
-      <c r="A92" t="s">
-        <v>28</v>
-      </c>
-      <c r="C92" s="3">
-        <v>560</v>
-      </c>
-      <c r="D92" s="5">
-        <v>46</v>
-      </c>
       <c r="E92" s="1">
-        <f t="shared" si="132"/>
-        <v>0.21875</v>
+        <f t="shared" si="172"/>
+        <v>0</v>
       </c>
       <c r="F92" s="1">
-        <f t="shared" si="133"/>
-        <v>3.1944444444444442E-2</v>
+        <f t="shared" si="173"/>
+        <v>0</v>
       </c>
       <c r="G92" s="3">
-        <f t="shared" si="134"/>
-        <v>840</v>
+        <f t="shared" si="174"/>
+        <v>0</v>
       </c>
       <c r="H92" s="5">
-        <f t="shared" si="135"/>
-        <v>69</v>
+        <f t="shared" si="175"/>
+        <v>0</v>
       </c>
       <c r="J92" s="3">
-        <f t="shared" si="136"/>
-        <v>420</v>
+        <f t="shared" si="176"/>
+        <v>0</v>
       </c>
       <c r="K92" s="5">
-        <f t="shared" si="137"/>
-        <v>34.5</v>
+        <f t="shared" si="177"/>
+        <v>0</v>
       </c>
       <c r="M92" s="3">
-        <f t="shared" si="138"/>
-        <v>280</v>
+        <f t="shared" si="178"/>
+        <v>0</v>
       </c>
       <c r="N92" s="5">
-        <f t="shared" si="139"/>
-        <v>23</v>
+        <f t="shared" si="179"/>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:14">
+      <c r="A93" t="s">
+        <v>22</v>
+      </c>
+      <c r="C93" s="3">
+        <v>124</v>
+      </c>
+      <c r="D93" s="5">
+        <v>80</v>
+      </c>
       <c r="E93" s="1">
-        <f t="shared" si="132"/>
-        <v>0</v>
+        <f t="shared" si="172"/>
+        <v>4.8437500000000001E-2</v>
       </c>
       <c r="F93" s="1">
-        <f t="shared" si="133"/>
-        <v>0</v>
+        <f t="shared" si="173"/>
+        <v>5.5555555555555552E-2</v>
       </c>
       <c r="G93" s="3">
-        <f t="shared" si="134"/>
-        <v>0</v>
+        <f t="shared" si="174"/>
+        <v>186</v>
       </c>
       <c r="H93" s="5">
-        <f t="shared" si="135"/>
-        <v>0</v>
+        <f t="shared" si="175"/>
+        <v>120</v>
       </c>
       <c r="J93" s="3">
-        <f t="shared" si="136"/>
-        <v>0</v>
+        <f t="shared" si="176"/>
+        <v>93</v>
       </c>
       <c r="K93" s="5">
-        <f t="shared" si="137"/>
-        <v>0</v>
+        <f t="shared" si="177"/>
+        <v>60</v>
       </c>
       <c r="M93" s="3">
-        <f t="shared" si="138"/>
-        <v>0</v>
+        <f t="shared" si="178"/>
+        <v>62</v>
       </c>
       <c r="N93" s="5">
-        <f t="shared" si="139"/>
-        <v>0</v>
+        <f t="shared" si="179"/>
+        <v>40</v>
       </c>
     </row>
     <row r="94" spans="1:14">
       <c r="E94" s="1">
-        <f t="shared" si="132"/>
+        <f t="shared" si="172"/>
         <v>0</v>
       </c>
       <c r="F94" s="1">
-        <f t="shared" si="133"/>
+        <f t="shared" si="173"/>
         <v>0</v>
       </c>
       <c r="G94" s="3">
-        <f t="shared" si="134"/>
+        <f t="shared" si="174"/>
         <v>0</v>
       </c>
       <c r="H94" s="5">
-        <f t="shared" si="135"/>
+        <f t="shared" si="175"/>
         <v>0</v>
       </c>
       <c r="J94" s="3">
-        <f t="shared" si="136"/>
+        <f t="shared" si="176"/>
         <v>0</v>
       </c>
       <c r="K94" s="5">
-        <f t="shared" si="137"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="M94" s="3">
-        <f t="shared" si="138"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="N94" s="5">
-        <f t="shared" si="139"/>
+        <f t="shared" si="179"/>
         <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:14">
+      <c r="A95" t="s">
+        <v>23</v>
+      </c>
+      <c r="C95" s="3">
+        <v>124</v>
+      </c>
+      <c r="D95" s="5">
+        <v>100</v>
+      </c>
       <c r="E95" s="1">
-        <f t="shared" si="132"/>
-        <v>0</v>
+        <f t="shared" si="172"/>
+        <v>4.8437500000000001E-2</v>
       </c>
       <c r="F95" s="1">
-        <f t="shared" si="133"/>
-        <v>0</v>
+        <f t="shared" si="173"/>
+        <v>6.9444444444444448E-2</v>
       </c>
       <c r="G95" s="3">
-        <f t="shared" si="134"/>
-        <v>0</v>
+        <f t="shared" si="174"/>
+        <v>186</v>
       </c>
       <c r="H95" s="5">
-        <f t="shared" si="135"/>
-        <v>0</v>
+        <f t="shared" si="175"/>
+        <v>150</v>
       </c>
       <c r="J95" s="3">
-        <f t="shared" si="136"/>
-        <v>0</v>
+        <f t="shared" si="176"/>
+        <v>93</v>
       </c>
       <c r="K95" s="5">
-        <f t="shared" si="137"/>
-        <v>0</v>
+        <f t="shared" si="177"/>
+        <v>75</v>
       </c>
       <c r="M95" s="3">
-        <f t="shared" si="138"/>
-        <v>0</v>
+        <f t="shared" si="178"/>
+        <v>62</v>
       </c>
       <c r="N95" s="5">
-        <f t="shared" si="139"/>
-        <v>0</v>
+        <f t="shared" si="179"/>
+        <v>50</v>
       </c>
     </row>
     <row r="96" spans="1:14">
       <c r="E96" s="1">
-        <f t="shared" si="132"/>
+        <f t="shared" si="172"/>
         <v>0</v>
       </c>
       <c r="F96" s="1">
-        <f t="shared" si="133"/>
+        <f t="shared" si="173"/>
         <v>0</v>
       </c>
       <c r="G96" s="3">
-        <f t="shared" si="134"/>
+        <f t="shared" si="174"/>
         <v>0</v>
       </c>
       <c r="H96" s="5">
-        <f t="shared" si="135"/>
+        <f t="shared" si="175"/>
         <v>0</v>
       </c>
       <c r="J96" s="3">
-        <f t="shared" si="136"/>
+        <f t="shared" si="176"/>
         <v>0</v>
       </c>
       <c r="K96" s="5">
-        <f t="shared" si="137"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="M96" s="3">
-        <f t="shared" si="138"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="N96" s="5">
-        <f t="shared" si="139"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="5:14">
+        <f t="shared" si="179"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14">
+      <c r="A97" t="s">
+        <v>24</v>
+      </c>
+      <c r="C97" s="3">
+        <v>116</v>
+      </c>
+      <c r="D97" s="5">
+        <v>112</v>
+      </c>
       <c r="E97" s="1">
-        <f t="shared" si="132"/>
-        <v>0</v>
+        <f t="shared" si="172"/>
+        <v>4.5312499999999999E-2</v>
       </c>
       <c r="F97" s="1">
-        <f t="shared" si="133"/>
-        <v>0</v>
+        <f t="shared" si="173"/>
+        <v>7.7777777777777779E-2</v>
       </c>
       <c r="G97" s="3">
-        <f t="shared" si="134"/>
-        <v>0</v>
+        <f t="shared" si="174"/>
+        <v>174</v>
       </c>
       <c r="H97" s="5">
-        <f t="shared" si="135"/>
-        <v>0</v>
+        <f t="shared" si="175"/>
+        <v>168</v>
       </c>
       <c r="J97" s="3">
-        <f t="shared" si="136"/>
-        <v>0</v>
+        <f t="shared" si="176"/>
+        <v>87</v>
       </c>
       <c r="K97" s="5">
-        <f t="shared" si="137"/>
-        <v>0</v>
+        <f t="shared" si="177"/>
+        <v>84</v>
       </c>
       <c r="M97" s="3">
-        <f t="shared" si="138"/>
-        <v>0</v>
+        <f t="shared" si="178"/>
+        <v>58</v>
       </c>
       <c r="N97" s="5">
-        <f t="shared" si="139"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="5:14">
+        <f t="shared" si="179"/>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14">
       <c r="E98" s="1">
-        <f t="shared" si="132"/>
+        <f t="shared" si="172"/>
         <v>0</v>
       </c>
       <c r="F98" s="1">
-        <f t="shared" si="133"/>
+        <f t="shared" si="173"/>
         <v>0</v>
       </c>
       <c r="G98" s="3">
-        <f t="shared" si="134"/>
+        <f t="shared" si="174"/>
         <v>0</v>
       </c>
       <c r="H98" s="5">
-        <f t="shared" si="135"/>
+        <f t="shared" si="175"/>
         <v>0</v>
       </c>
       <c r="J98" s="3">
-        <f t="shared" si="136"/>
+        <f t="shared" si="176"/>
         <v>0</v>
       </c>
       <c r="K98" s="5">
-        <f t="shared" si="137"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="M98" s="3">
-        <f t="shared" si="138"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="N98" s="5">
-        <f t="shared" si="139"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="5:14">
+        <f t="shared" si="179"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14">
       <c r="E99" s="1">
-        <f t="shared" si="132"/>
+        <f t="shared" si="172"/>
         <v>0</v>
       </c>
       <c r="F99" s="1">
-        <f t="shared" si="133"/>
+        <f t="shared" si="173"/>
         <v>0</v>
       </c>
       <c r="G99" s="3">
-        <f t="shared" si="134"/>
+        <f t="shared" si="174"/>
         <v>0</v>
       </c>
       <c r="H99" s="5">
-        <f t="shared" si="135"/>
+        <f t="shared" si="175"/>
         <v>0</v>
       </c>
       <c r="J99" s="3">
-        <f t="shared" si="136"/>
+        <f t="shared" si="176"/>
         <v>0</v>
       </c>
       <c r="K99" s="5">
-        <f t="shared" si="137"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="M99" s="3">
-        <f t="shared" si="138"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="N99" s="5">
-        <f t="shared" si="139"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="5:14">
+        <f t="shared" si="179"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14">
+      <c r="A100" t="s">
+        <v>26</v>
+      </c>
+      <c r="C100" s="3">
+        <v>280</v>
+      </c>
+      <c r="D100" s="5">
+        <v>84</v>
+      </c>
       <c r="E100" s="1">
-        <f t="shared" si="132"/>
-        <v>0</v>
+        <f t="shared" si="172"/>
+        <v>0.109375</v>
       </c>
       <c r="F100" s="1">
-        <f t="shared" si="133"/>
-        <v>0</v>
+        <f t="shared" si="173"/>
+        <v>5.8333333333333334E-2</v>
       </c>
       <c r="G100" s="3">
-        <f t="shared" si="134"/>
-        <v>0</v>
+        <f t="shared" si="174"/>
+        <v>420</v>
       </c>
       <c r="H100" s="5">
-        <f t="shared" si="135"/>
-        <v>0</v>
+        <f t="shared" si="175"/>
+        <v>126</v>
       </c>
       <c r="J100" s="3">
-        <f t="shared" si="136"/>
-        <v>0</v>
+        <f t="shared" si="176"/>
+        <v>210</v>
       </c>
       <c r="K100" s="5">
-        <f t="shared" si="137"/>
-        <v>0</v>
+        <f t="shared" si="177"/>
+        <v>63</v>
       </c>
       <c r="M100" s="3">
-        <f t="shared" si="138"/>
-        <v>0</v>
+        <f t="shared" si="178"/>
+        <v>140</v>
       </c>
       <c r="N100" s="5">
-        <f t="shared" si="139"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="5:14">
+        <f t="shared" si="179"/>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14">
       <c r="E101" s="1">
-        <f t="shared" si="132"/>
+        <f t="shared" si="172"/>
         <v>0</v>
       </c>
       <c r="F101" s="1">
-        <f t="shared" si="133"/>
+        <f t="shared" si="173"/>
         <v>0</v>
       </c>
       <c r="G101" s="3">
-        <f t="shared" si="134"/>
+        <f t="shared" si="174"/>
         <v>0</v>
       </c>
       <c r="H101" s="5">
-        <f t="shared" si="135"/>
+        <f t="shared" si="175"/>
         <v>0</v>
       </c>
       <c r="J101" s="3">
-        <f t="shared" si="136"/>
+        <f t="shared" si="176"/>
         <v>0</v>
       </c>
       <c r="K101" s="5">
-        <f t="shared" si="137"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="M101" s="3">
-        <f t="shared" si="138"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="N101" s="5">
-        <f t="shared" si="139"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="5:14">
+        <f t="shared" si="179"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14">
+      <c r="A102" t="s">
+        <v>27</v>
+      </c>
+      <c r="C102" s="3">
+        <v>660</v>
+      </c>
+      <c r="D102" s="5">
+        <v>140</v>
+      </c>
       <c r="E102" s="1">
-        <f t="shared" si="132"/>
-        <v>0</v>
+        <f t="shared" si="172"/>
+        <v>0.2578125</v>
       </c>
       <c r="F102" s="1">
-        <f t="shared" si="133"/>
-        <v>0</v>
+        <f t="shared" si="173"/>
+        <v>9.7222222222222224E-2</v>
       </c>
       <c r="G102" s="3">
-        <f t="shared" si="134"/>
-        <v>0</v>
+        <f t="shared" si="174"/>
+        <v>990</v>
       </c>
       <c r="H102" s="5">
-        <f t="shared" si="135"/>
-        <v>0</v>
+        <f t="shared" si="175"/>
+        <v>210</v>
       </c>
       <c r="J102" s="3">
-        <f t="shared" si="136"/>
-        <v>0</v>
+        <f t="shared" si="176"/>
+        <v>495</v>
       </c>
       <c r="K102" s="5">
-        <f t="shared" si="137"/>
-        <v>0</v>
+        <f t="shared" si="177"/>
+        <v>105</v>
       </c>
       <c r="M102" s="3">
-        <f t="shared" si="138"/>
-        <v>0</v>
+        <f t="shared" si="178"/>
+        <v>330</v>
       </c>
       <c r="N102" s="5">
-        <f t="shared" si="139"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="5:14">
+        <f t="shared" si="179"/>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="103" spans="1:14">
+      <c r="A103" t="s">
+        <v>28</v>
+      </c>
+      <c r="C103" s="3">
+        <v>560</v>
+      </c>
+      <c r="D103" s="5">
+        <v>46</v>
+      </c>
       <c r="E103" s="1">
-        <f t="shared" si="132"/>
-        <v>0</v>
+        <f t="shared" si="172"/>
+        <v>0.21875</v>
       </c>
       <c r="F103" s="1">
-        <f t="shared" si="133"/>
-        <v>0</v>
+        <f t="shared" si="173"/>
+        <v>3.1944444444444442E-2</v>
       </c>
       <c r="G103" s="3">
-        <f t="shared" si="134"/>
-        <v>0</v>
+        <f t="shared" si="174"/>
+        <v>840</v>
       </c>
       <c r="H103" s="5">
-        <f t="shared" si="135"/>
-        <v>0</v>
+        <f t="shared" si="175"/>
+        <v>69</v>
       </c>
       <c r="J103" s="3">
-        <f t="shared" si="136"/>
-        <v>0</v>
+        <f t="shared" si="176"/>
+        <v>420</v>
       </c>
       <c r="K103" s="5">
-        <f t="shared" si="137"/>
-        <v>0</v>
+        <f t="shared" si="177"/>
+        <v>34.5</v>
       </c>
       <c r="M103" s="3">
-        <f t="shared" si="138"/>
-        <v>0</v>
+        <f t="shared" si="178"/>
+        <v>280</v>
       </c>
       <c r="N103" s="5">
-        <f t="shared" si="139"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="5:14">
+        <f t="shared" si="179"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="104" spans="1:14">
       <c r="E104" s="1">
-        <f t="shared" si="132"/>
+        <f t="shared" si="172"/>
         <v>0</v>
       </c>
       <c r="F104" s="1">
-        <f t="shared" si="133"/>
+        <f t="shared" si="173"/>
         <v>0</v>
       </c>
       <c r="G104" s="3">
-        <f t="shared" si="134"/>
+        <f t="shared" si="174"/>
         <v>0</v>
       </c>
       <c r="H104" s="5">
-        <f t="shared" si="135"/>
+        <f t="shared" si="175"/>
         <v>0</v>
       </c>
       <c r="J104" s="3">
-        <f t="shared" si="136"/>
+        <f t="shared" si="176"/>
         <v>0</v>
       </c>
       <c r="K104" s="5">
-        <f t="shared" si="137"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="M104" s="3">
-        <f t="shared" si="138"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="N104" s="5">
-        <f t="shared" si="139"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="5:14">
+        <f t="shared" si="179"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:14">
       <c r="E105" s="1">
-        <f t="shared" si="132"/>
+        <f t="shared" si="172"/>
         <v>0</v>
       </c>
       <c r="F105" s="1">
-        <f t="shared" si="133"/>
+        <f t="shared" si="173"/>
         <v>0</v>
       </c>
       <c r="G105" s="3">
-        <f t="shared" si="134"/>
+        <f t="shared" si="174"/>
         <v>0</v>
       </c>
       <c r="H105" s="5">
-        <f t="shared" si="135"/>
+        <f t="shared" si="175"/>
         <v>0</v>
       </c>
       <c r="J105" s="3">
-        <f t="shared" si="136"/>
+        <f t="shared" si="176"/>
         <v>0</v>
       </c>
       <c r="K105" s="5">
-        <f t="shared" si="137"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="M105" s="3">
-        <f t="shared" si="138"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="N105" s="5">
-        <f t="shared" si="139"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="5:14">
+        <f t="shared" si="179"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:14">
       <c r="E106" s="1">
-        <f t="shared" si="132"/>
+        <f t="shared" si="172"/>
         <v>0</v>
       </c>
       <c r="F106" s="1">
-        <f t="shared" si="133"/>
+        <f t="shared" si="173"/>
         <v>0</v>
       </c>
       <c r="G106" s="3">
-        <f t="shared" si="134"/>
+        <f t="shared" si="174"/>
         <v>0</v>
       </c>
       <c r="H106" s="5">
-        <f t="shared" si="135"/>
+        <f t="shared" si="175"/>
         <v>0</v>
       </c>
       <c r="J106" s="3">
-        <f t="shared" si="136"/>
+        <f t="shared" si="176"/>
         <v>0</v>
       </c>
       <c r="K106" s="5">
-        <f t="shared" si="137"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="M106" s="3">
-        <f t="shared" si="138"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="N106" s="5">
-        <f t="shared" si="139"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="5:14">
+        <f t="shared" si="179"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:14">
       <c r="E107" s="1">
-        <f t="shared" si="132"/>
+        <f t="shared" si="172"/>
         <v>0</v>
       </c>
       <c r="F107" s="1">
-        <f t="shared" si="133"/>
+        <f t="shared" si="173"/>
         <v>0</v>
       </c>
       <c r="G107" s="3">
-        <f t="shared" si="134"/>
+        <f t="shared" si="174"/>
         <v>0</v>
       </c>
       <c r="H107" s="5">
-        <f t="shared" si="135"/>
+        <f t="shared" si="175"/>
         <v>0</v>
       </c>
       <c r="J107" s="3">
-        <f t="shared" si="136"/>
+        <f t="shared" si="176"/>
         <v>0</v>
       </c>
       <c r="K107" s="5">
-        <f t="shared" si="137"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="M107" s="3">
-        <f t="shared" si="138"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="N107" s="5">
-        <f t="shared" si="139"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="5:14">
+        <f t="shared" si="179"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:14">
       <c r="E108" s="1">
-        <f t="shared" si="132"/>
+        <f t="shared" si="172"/>
         <v>0</v>
       </c>
       <c r="F108" s="1">
-        <f t="shared" si="133"/>
+        <f t="shared" si="173"/>
         <v>0</v>
       </c>
       <c r="G108" s="3">
-        <f t="shared" si="134"/>
+        <f t="shared" si="174"/>
         <v>0</v>
       </c>
       <c r="H108" s="5">
-        <f t="shared" si="135"/>
+        <f t="shared" si="175"/>
         <v>0</v>
       </c>
       <c r="J108" s="3">
-        <f t="shared" si="136"/>
+        <f t="shared" si="176"/>
         <v>0</v>
       </c>
       <c r="K108" s="5">
-        <f t="shared" si="137"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="M108" s="3">
-        <f t="shared" si="138"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="N108" s="5">
-        <f t="shared" si="139"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="5:14">
+        <f t="shared" si="179"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:14">
       <c r="E109" s="1">
-        <f t="shared" si="132"/>
+        <f t="shared" si="172"/>
         <v>0</v>
       </c>
       <c r="F109" s="1">
-        <f t="shared" si="133"/>
+        <f t="shared" si="173"/>
         <v>0</v>
       </c>
       <c r="G109" s="3">
-        <f t="shared" si="134"/>
+        <f t="shared" si="174"/>
         <v>0</v>
       </c>
       <c r="H109" s="5">
-        <f t="shared" si="135"/>
+        <f t="shared" si="175"/>
         <v>0</v>
       </c>
       <c r="J109" s="3">
-        <f t="shared" si="136"/>
+        <f t="shared" si="176"/>
         <v>0</v>
       </c>
       <c r="K109" s="5">
-        <f t="shared" si="137"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="M109" s="3">
-        <f t="shared" si="138"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="N109" s="5">
-        <f t="shared" si="139"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="5:14">
+        <f t="shared" si="179"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:14">
       <c r="E110" s="1">
-        <f t="shared" si="132"/>
+        <f t="shared" si="172"/>
         <v>0</v>
       </c>
       <c r="F110" s="1">
-        <f t="shared" si="133"/>
+        <f t="shared" si="173"/>
         <v>0</v>
       </c>
       <c r="G110" s="3">
-        <f t="shared" si="134"/>
+        <f t="shared" si="174"/>
         <v>0</v>
       </c>
       <c r="H110" s="5">
-        <f t="shared" si="135"/>
+        <f t="shared" si="175"/>
         <v>0</v>
       </c>
       <c r="J110" s="3">
-        <f t="shared" si="136"/>
+        <f t="shared" si="176"/>
         <v>0</v>
       </c>
       <c r="K110" s="5">
-        <f t="shared" si="137"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="M110" s="3">
-        <f t="shared" si="138"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="N110" s="5">
-        <f t="shared" si="139"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="5:14">
+        <f t="shared" si="179"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:14">
       <c r="E111" s="1">
-        <f t="shared" si="132"/>
+        <f t="shared" si="172"/>
         <v>0</v>
       </c>
       <c r="F111" s="1">
-        <f t="shared" si="133"/>
+        <f t="shared" si="173"/>
         <v>0</v>
       </c>
       <c r="G111" s="3">
-        <f t="shared" si="134"/>
+        <f t="shared" si="174"/>
         <v>0</v>
       </c>
       <c r="H111" s="5">
-        <f t="shared" si="135"/>
+        <f t="shared" si="175"/>
         <v>0</v>
       </c>
       <c r="J111" s="3">
-        <f t="shared" si="136"/>
+        <f t="shared" si="176"/>
         <v>0</v>
       </c>
       <c r="K111" s="5">
-        <f t="shared" si="137"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="M111" s="3">
-        <f t="shared" si="138"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="N111" s="5">
-        <f t="shared" si="139"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="5:14">
+        <f t="shared" si="179"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:14">
       <c r="E112" s="1">
-        <f t="shared" si="132"/>
+        <f t="shared" si="172"/>
         <v>0</v>
       </c>
       <c r="F112" s="1">
-        <f t="shared" si="133"/>
+        <f t="shared" si="173"/>
         <v>0</v>
       </c>
       <c r="G112" s="3">
-        <f t="shared" si="134"/>
+        <f t="shared" si="174"/>
         <v>0</v>
       </c>
       <c r="H112" s="5">
-        <f t="shared" si="135"/>
+        <f t="shared" si="175"/>
         <v>0</v>
       </c>
       <c r="J112" s="3">
-        <f t="shared" si="136"/>
+        <f t="shared" si="176"/>
         <v>0</v>
       </c>
       <c r="K112" s="5">
-        <f t="shared" si="137"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="M112" s="3">
-        <f t="shared" si="138"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="N112" s="5">
-        <f t="shared" si="139"/>
+        <f t="shared" si="179"/>
         <v>0</v>
       </c>
     </row>
     <row r="113" spans="5:14">
       <c r="E113" s="1">
-        <f t="shared" si="132"/>
+        <f t="shared" si="172"/>
         <v>0</v>
       </c>
       <c r="F113" s="1">
-        <f t="shared" si="133"/>
+        <f t="shared" si="173"/>
         <v>0</v>
       </c>
       <c r="G113" s="3">
-        <f t="shared" si="134"/>
+        <f t="shared" si="174"/>
         <v>0</v>
       </c>
       <c r="H113" s="5">
-        <f t="shared" si="135"/>
+        <f t="shared" si="175"/>
         <v>0</v>
       </c>
       <c r="J113" s="3">
-        <f t="shared" si="136"/>
+        <f t="shared" si="176"/>
         <v>0</v>
       </c>
       <c r="K113" s="5">
-        <f t="shared" si="137"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="M113" s="3">
-        <f t="shared" si="138"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="N113" s="5">
-        <f t="shared" si="139"/>
+        <f t="shared" si="179"/>
         <v>0</v>
       </c>
     </row>
     <row r="114" spans="5:14">
       <c r="E114" s="1">
-        <f t="shared" ref="E114:E124" si="140" xml:space="preserve"> C114/C$2</f>
+        <f t="shared" si="172"/>
         <v>0</v>
       </c>
       <c r="F114" s="1">
-        <f t="shared" ref="F114:F124" si="141" xml:space="preserve"> D114/D$2</f>
+        <f t="shared" si="173"/>
         <v>0</v>
       </c>
       <c r="G114" s="3">
-        <f t="shared" ref="G114:G124" si="142">IF(ISBLANK(C114),0,(C114*G$2/C$2))</f>
+        <f t="shared" si="174"/>
         <v>0</v>
       </c>
       <c r="H114" s="5">
-        <f t="shared" ref="H114:H124" si="143">IF(ISBLANK(D114),0,(D114*H$2/D$2))</f>
+        <f t="shared" si="175"/>
         <v>0</v>
       </c>
       <c r="J114" s="3">
-        <f t="shared" ref="J114:J124" si="144">IF(ISBLANK(C114),0,(C114*J$2/C$2))</f>
+        <f t="shared" si="176"/>
         <v>0</v>
       </c>
       <c r="K114" s="5">
-        <f t="shared" ref="K114:K124" si="145">IF(ISBLANK(D114),0,(D114*K$2/D$2))</f>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="M114" s="3">
-        <f t="shared" ref="M114:M124" si="146">IF(ISBLANK(C114),0,(C114*M$2/C$2))</f>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="N114" s="5">
-        <f t="shared" ref="N114:N124" si="147">IF(ISBLANK(D114),0,(D114*N$2/D$2))</f>
+        <f t="shared" si="179"/>
         <v>0</v>
       </c>
     </row>
     <row r="115" spans="5:14">
       <c r="E115" s="1">
-        <f t="shared" si="140"/>
+        <f t="shared" si="172"/>
         <v>0</v>
       </c>
       <c r="F115" s="1">
-        <f t="shared" si="141"/>
+        <f t="shared" si="173"/>
         <v>0</v>
       </c>
       <c r="G115" s="3">
-        <f t="shared" si="142"/>
+        <f t="shared" si="174"/>
         <v>0</v>
       </c>
       <c r="H115" s="5">
-        <f t="shared" si="143"/>
+        <f t="shared" si="175"/>
         <v>0</v>
       </c>
       <c r="J115" s="3">
-        <f t="shared" si="144"/>
+        <f t="shared" si="176"/>
         <v>0</v>
       </c>
       <c r="K115" s="5">
-        <f t="shared" si="145"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="M115" s="3">
-        <f t="shared" si="146"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="N115" s="5">
-        <f t="shared" si="147"/>
+        <f t="shared" si="179"/>
         <v>0</v>
       </c>
     </row>
     <row r="116" spans="5:14">
       <c r="E116" s="1">
-        <f t="shared" si="140"/>
+        <f t="shared" si="172"/>
         <v>0</v>
       </c>
       <c r="F116" s="1">
-        <f t="shared" si="141"/>
+        <f t="shared" si="173"/>
         <v>0</v>
       </c>
       <c r="G116" s="3">
-        <f t="shared" si="142"/>
+        <f t="shared" si="174"/>
         <v>0</v>
       </c>
       <c r="H116" s="5">
-        <f t="shared" si="143"/>
+        <f t="shared" si="175"/>
         <v>0</v>
       </c>
       <c r="J116" s="3">
-        <f t="shared" si="144"/>
+        <f t="shared" si="176"/>
         <v>0</v>
       </c>
       <c r="K116" s="5">
-        <f t="shared" si="145"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="M116" s="3">
-        <f t="shared" si="146"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="N116" s="5">
-        <f t="shared" si="147"/>
+        <f t="shared" si="179"/>
         <v>0</v>
       </c>
     </row>
     <row r="117" spans="5:14">
       <c r="E117" s="1">
-        <f t="shared" si="140"/>
+        <f t="shared" si="172"/>
         <v>0</v>
       </c>
       <c r="F117" s="1">
-        <f t="shared" si="141"/>
+        <f t="shared" si="173"/>
         <v>0</v>
       </c>
       <c r="G117" s="3">
-        <f t="shared" si="142"/>
+        <f t="shared" si="174"/>
         <v>0</v>
       </c>
       <c r="H117" s="5">
-        <f t="shared" si="143"/>
+        <f t="shared" si="175"/>
         <v>0</v>
       </c>
       <c r="J117" s="3">
-        <f t="shared" si="144"/>
+        <f t="shared" si="176"/>
         <v>0</v>
       </c>
       <c r="K117" s="5">
-        <f t="shared" si="145"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="M117" s="3">
-        <f t="shared" si="146"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="N117" s="5">
-        <f t="shared" si="147"/>
+        <f t="shared" si="179"/>
         <v>0</v>
       </c>
     </row>
     <row r="118" spans="5:14">
       <c r="E118" s="1">
-        <f t="shared" si="140"/>
+        <f t="shared" si="172"/>
         <v>0</v>
       </c>
       <c r="F118" s="1">
-        <f t="shared" si="141"/>
+        <f t="shared" si="173"/>
         <v>0</v>
       </c>
       <c r="G118" s="3">
-        <f t="shared" si="142"/>
+        <f t="shared" si="174"/>
         <v>0</v>
       </c>
       <c r="H118" s="5">
-        <f t="shared" si="143"/>
+        <f t="shared" si="175"/>
         <v>0</v>
       </c>
       <c r="J118" s="3">
-        <f t="shared" si="144"/>
+        <f t="shared" si="176"/>
         <v>0</v>
       </c>
       <c r="K118" s="5">
-        <f t="shared" si="145"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="M118" s="3">
-        <f t="shared" si="146"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="N118" s="5">
-        <f t="shared" si="147"/>
+        <f t="shared" si="179"/>
         <v>0</v>
       </c>
     </row>
     <row r="119" spans="5:14">
       <c r="E119" s="1">
-        <f t="shared" si="140"/>
+        <f t="shared" si="172"/>
         <v>0</v>
       </c>
       <c r="F119" s="1">
-        <f t="shared" si="141"/>
+        <f t="shared" si="173"/>
         <v>0</v>
       </c>
       <c r="G119" s="3">
-        <f t="shared" si="142"/>
+        <f t="shared" si="174"/>
         <v>0</v>
       </c>
       <c r="H119" s="5">
-        <f t="shared" si="143"/>
+        <f t="shared" si="175"/>
         <v>0</v>
       </c>
       <c r="J119" s="3">
-        <f t="shared" si="144"/>
+        <f t="shared" si="176"/>
         <v>0</v>
       </c>
       <c r="K119" s="5">
-        <f t="shared" si="145"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="M119" s="3">
-        <f t="shared" si="146"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="N119" s="5">
-        <f t="shared" si="147"/>
+        <f t="shared" si="179"/>
         <v>0</v>
       </c>
     </row>
     <row r="120" spans="5:14">
       <c r="E120" s="1">
-        <f t="shared" si="140"/>
+        <f t="shared" si="172"/>
         <v>0</v>
       </c>
       <c r="F120" s="1">
-        <f t="shared" si="141"/>
+        <f t="shared" si="173"/>
         <v>0</v>
       </c>
       <c r="G120" s="3">
-        <f t="shared" si="142"/>
+        <f t="shared" si="174"/>
         <v>0</v>
       </c>
       <c r="H120" s="5">
-        <f t="shared" si="143"/>
+        <f t="shared" si="175"/>
         <v>0</v>
       </c>
       <c r="J120" s="3">
-        <f t="shared" si="144"/>
+        <f t="shared" si="176"/>
         <v>0</v>
       </c>
       <c r="K120" s="5">
-        <f t="shared" si="145"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="M120" s="3">
-        <f t="shared" si="146"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="N120" s="5">
-        <f t="shared" si="147"/>
+        <f t="shared" si="179"/>
         <v>0</v>
       </c>
     </row>
     <row r="121" spans="5:14">
       <c r="E121" s="1">
-        <f t="shared" si="140"/>
+        <f t="shared" si="172"/>
         <v>0</v>
       </c>
       <c r="F121" s="1">
-        <f t="shared" si="141"/>
+        <f t="shared" si="173"/>
         <v>0</v>
       </c>
       <c r="G121" s="3">
-        <f t="shared" si="142"/>
+        <f t="shared" si="174"/>
         <v>0</v>
       </c>
       <c r="H121" s="5">
-        <f t="shared" si="143"/>
+        <f t="shared" si="175"/>
         <v>0</v>
       </c>
       <c r="J121" s="3">
-        <f t="shared" si="144"/>
+        <f t="shared" si="176"/>
         <v>0</v>
       </c>
       <c r="K121" s="5">
-        <f t="shared" si="145"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="M121" s="3">
-        <f t="shared" si="146"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="N121" s="5">
-        <f t="shared" si="147"/>
+        <f t="shared" si="179"/>
         <v>0</v>
       </c>
     </row>
     <row r="122" spans="5:14">
       <c r="E122" s="1">
-        <f t="shared" si="140"/>
+        <f t="shared" si="172"/>
         <v>0</v>
       </c>
       <c r="F122" s="1">
-        <f t="shared" si="141"/>
+        <f t="shared" si="173"/>
         <v>0</v>
       </c>
       <c r="G122" s="3">
-        <f t="shared" si="142"/>
+        <f t="shared" si="174"/>
         <v>0</v>
       </c>
       <c r="H122" s="5">
-        <f t="shared" si="143"/>
+        <f t="shared" si="175"/>
         <v>0</v>
       </c>
       <c r="J122" s="3">
-        <f t="shared" si="144"/>
+        <f t="shared" si="176"/>
         <v>0</v>
       </c>
       <c r="K122" s="5">
-        <f t="shared" si="145"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="M122" s="3">
-        <f t="shared" si="146"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="N122" s="5">
-        <f t="shared" si="147"/>
+        <f t="shared" si="179"/>
         <v>0</v>
       </c>
     </row>
     <row r="123" spans="5:14">
       <c r="E123" s="1">
-        <f t="shared" si="140"/>
+        <f t="shared" si="172"/>
         <v>0</v>
       </c>
       <c r="F123" s="1">
-        <f t="shared" si="141"/>
+        <f t="shared" si="173"/>
         <v>0</v>
       </c>
       <c r="G123" s="3">
-        <f t="shared" si="142"/>
+        <f t="shared" si="174"/>
         <v>0</v>
       </c>
       <c r="H123" s="5">
-        <f t="shared" si="143"/>
+        <f t="shared" si="175"/>
         <v>0</v>
       </c>
       <c r="J123" s="3">
-        <f t="shared" si="144"/>
+        <f t="shared" si="176"/>
         <v>0</v>
       </c>
       <c r="K123" s="5">
-        <f t="shared" si="145"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="M123" s="3">
-        <f t="shared" si="146"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="N123" s="5">
-        <f t="shared" si="147"/>
+        <f t="shared" si="179"/>
         <v>0</v>
       </c>
     </row>
     <row r="124" spans="5:14">
       <c r="E124" s="1">
-        <f t="shared" si="140"/>
+        <f t="shared" si="172"/>
         <v>0</v>
       </c>
       <c r="F124" s="1">
-        <f t="shared" si="141"/>
+        <f t="shared" si="173"/>
         <v>0</v>
       </c>
       <c r="G124" s="3">
-        <f t="shared" si="142"/>
+        <f t="shared" si="174"/>
         <v>0</v>
       </c>
       <c r="H124" s="5">
-        <f t="shared" si="143"/>
+        <f t="shared" si="175"/>
         <v>0</v>
       </c>
       <c r="J124" s="3">
-        <f t="shared" si="144"/>
+        <f t="shared" si="176"/>
         <v>0</v>
       </c>
       <c r="K124" s="5">
-        <f t="shared" si="145"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="M124" s="3">
-        <f t="shared" si="146"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="N124" s="5">
-        <f t="shared" si="147"/>
+        <f t="shared" si="179"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="5:14">
+      <c r="E125" s="1">
+        <f t="shared" ref="E125:E135" si="180" xml:space="preserve"> C125/C$2</f>
+        <v>0</v>
+      </c>
+      <c r="F125" s="1">
+        <f t="shared" ref="F125:F135" si="181" xml:space="preserve"> D125/D$2</f>
+        <v>0</v>
+      </c>
+      <c r="G125" s="3">
+        <f t="shared" ref="G125:G135" si="182">IF(ISBLANK(C125),0,(C125*G$2/C$2))</f>
+        <v>0</v>
+      </c>
+      <c r="H125" s="5">
+        <f t="shared" ref="H125:H135" si="183">IF(ISBLANK(D125),0,(D125*H$2/D$2))</f>
+        <v>0</v>
+      </c>
+      <c r="J125" s="3">
+        <f t="shared" ref="J125:J135" si="184">IF(ISBLANK(C125),0,(C125*J$2/C$2))</f>
+        <v>0</v>
+      </c>
+      <c r="K125" s="5">
+        <f t="shared" ref="K125:K135" si="185">IF(ISBLANK(D125),0,(D125*K$2/D$2))</f>
+        <v>0</v>
+      </c>
+      <c r="M125" s="3">
+        <f t="shared" ref="M125:M135" si="186">IF(ISBLANK(C125),0,(C125*M$2/C$2))</f>
+        <v>0</v>
+      </c>
+      <c r="N125" s="5">
+        <f t="shared" ref="N125:N135" si="187">IF(ISBLANK(D125),0,(D125*N$2/D$2))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="5:14">
+      <c r="E126" s="1">
+        <f t="shared" si="180"/>
+        <v>0</v>
+      </c>
+      <c r="F126" s="1">
+        <f t="shared" si="181"/>
+        <v>0</v>
+      </c>
+      <c r="G126" s="3">
+        <f t="shared" si="182"/>
+        <v>0</v>
+      </c>
+      <c r="H126" s="5">
+        <f t="shared" si="183"/>
+        <v>0</v>
+      </c>
+      <c r="J126" s="3">
+        <f t="shared" si="184"/>
+        <v>0</v>
+      </c>
+      <c r="K126" s="5">
+        <f t="shared" si="185"/>
+        <v>0</v>
+      </c>
+      <c r="M126" s="3">
+        <f t="shared" si="186"/>
+        <v>0</v>
+      </c>
+      <c r="N126" s="5">
+        <f t="shared" si="187"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="5:14">
+      <c r="E127" s="1">
+        <f t="shared" si="180"/>
+        <v>0</v>
+      </c>
+      <c r="F127" s="1">
+        <f t="shared" si="181"/>
+        <v>0</v>
+      </c>
+      <c r="G127" s="3">
+        <f t="shared" si="182"/>
+        <v>0</v>
+      </c>
+      <c r="H127" s="5">
+        <f t="shared" si="183"/>
+        <v>0</v>
+      </c>
+      <c r="J127" s="3">
+        <f t="shared" si="184"/>
+        <v>0</v>
+      </c>
+      <c r="K127" s="5">
+        <f t="shared" si="185"/>
+        <v>0</v>
+      </c>
+      <c r="M127" s="3">
+        <f t="shared" si="186"/>
+        <v>0</v>
+      </c>
+      <c r="N127" s="5">
+        <f t="shared" si="187"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="5:14">
+      <c r="E128" s="1">
+        <f t="shared" si="180"/>
+        <v>0</v>
+      </c>
+      <c r="F128" s="1">
+        <f t="shared" si="181"/>
+        <v>0</v>
+      </c>
+      <c r="G128" s="3">
+        <f t="shared" si="182"/>
+        <v>0</v>
+      </c>
+      <c r="H128" s="5">
+        <f t="shared" si="183"/>
+        <v>0</v>
+      </c>
+      <c r="J128" s="3">
+        <f t="shared" si="184"/>
+        <v>0</v>
+      </c>
+      <c r="K128" s="5">
+        <f t="shared" si="185"/>
+        <v>0</v>
+      </c>
+      <c r="M128" s="3">
+        <f t="shared" si="186"/>
+        <v>0</v>
+      </c>
+      <c r="N128" s="5">
+        <f t="shared" si="187"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="5:14">
+      <c r="E129" s="1">
+        <f t="shared" si="180"/>
+        <v>0</v>
+      </c>
+      <c r="F129" s="1">
+        <f t="shared" si="181"/>
+        <v>0</v>
+      </c>
+      <c r="G129" s="3">
+        <f t="shared" si="182"/>
+        <v>0</v>
+      </c>
+      <c r="H129" s="5">
+        <f t="shared" si="183"/>
+        <v>0</v>
+      </c>
+      <c r="J129" s="3">
+        <f t="shared" si="184"/>
+        <v>0</v>
+      </c>
+      <c r="K129" s="5">
+        <f t="shared" si="185"/>
+        <v>0</v>
+      </c>
+      <c r="M129" s="3">
+        <f t="shared" si="186"/>
+        <v>0</v>
+      </c>
+      <c r="N129" s="5">
+        <f t="shared" si="187"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="5:14">
+      <c r="E130" s="1">
+        <f t="shared" si="180"/>
+        <v>0</v>
+      </c>
+      <c r="F130" s="1">
+        <f t="shared" si="181"/>
+        <v>0</v>
+      </c>
+      <c r="G130" s="3">
+        <f t="shared" si="182"/>
+        <v>0</v>
+      </c>
+      <c r="H130" s="5">
+        <f t="shared" si="183"/>
+        <v>0</v>
+      </c>
+      <c r="J130" s="3">
+        <f t="shared" si="184"/>
+        <v>0</v>
+      </c>
+      <c r="K130" s="5">
+        <f t="shared" si="185"/>
+        <v>0</v>
+      </c>
+      <c r="M130" s="3">
+        <f t="shared" si="186"/>
+        <v>0</v>
+      </c>
+      <c r="N130" s="5">
+        <f t="shared" si="187"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="5:14">
+      <c r="E131" s="1">
+        <f t="shared" si="180"/>
+        <v>0</v>
+      </c>
+      <c r="F131" s="1">
+        <f t="shared" si="181"/>
+        <v>0</v>
+      </c>
+      <c r="G131" s="3">
+        <f t="shared" si="182"/>
+        <v>0</v>
+      </c>
+      <c r="H131" s="5">
+        <f t="shared" si="183"/>
+        <v>0</v>
+      </c>
+      <c r="J131" s="3">
+        <f t="shared" si="184"/>
+        <v>0</v>
+      </c>
+      <c r="K131" s="5">
+        <f t="shared" si="185"/>
+        <v>0</v>
+      </c>
+      <c r="M131" s="3">
+        <f t="shared" si="186"/>
+        <v>0</v>
+      </c>
+      <c r="N131" s="5">
+        <f t="shared" si="187"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="5:14">
+      <c r="E132" s="1">
+        <f t="shared" si="180"/>
+        <v>0</v>
+      </c>
+      <c r="F132" s="1">
+        <f t="shared" si="181"/>
+        <v>0</v>
+      </c>
+      <c r="G132" s="3">
+        <f t="shared" si="182"/>
+        <v>0</v>
+      </c>
+      <c r="H132" s="5">
+        <f t="shared" si="183"/>
+        <v>0</v>
+      </c>
+      <c r="J132" s="3">
+        <f t="shared" si="184"/>
+        <v>0</v>
+      </c>
+      <c r="K132" s="5">
+        <f t="shared" si="185"/>
+        <v>0</v>
+      </c>
+      <c r="M132" s="3">
+        <f t="shared" si="186"/>
+        <v>0</v>
+      </c>
+      <c r="N132" s="5">
+        <f t="shared" si="187"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="5:14">
+      <c r="E133" s="1">
+        <f t="shared" si="180"/>
+        <v>0</v>
+      </c>
+      <c r="F133" s="1">
+        <f t="shared" si="181"/>
+        <v>0</v>
+      </c>
+      <c r="G133" s="3">
+        <f t="shared" si="182"/>
+        <v>0</v>
+      </c>
+      <c r="H133" s="5">
+        <f t="shared" si="183"/>
+        <v>0</v>
+      </c>
+      <c r="J133" s="3">
+        <f t="shared" si="184"/>
+        <v>0</v>
+      </c>
+      <c r="K133" s="5">
+        <f t="shared" si="185"/>
+        <v>0</v>
+      </c>
+      <c r="M133" s="3">
+        <f t="shared" si="186"/>
+        <v>0</v>
+      </c>
+      <c r="N133" s="5">
+        <f t="shared" si="187"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="5:14">
+      <c r="E134" s="1">
+        <f t="shared" si="180"/>
+        <v>0</v>
+      </c>
+      <c r="F134" s="1">
+        <f t="shared" si="181"/>
+        <v>0</v>
+      </c>
+      <c r="G134" s="3">
+        <f t="shared" si="182"/>
+        <v>0</v>
+      </c>
+      <c r="H134" s="5">
+        <f t="shared" si="183"/>
+        <v>0</v>
+      </c>
+      <c r="J134" s="3">
+        <f t="shared" si="184"/>
+        <v>0</v>
+      </c>
+      <c r="K134" s="5">
+        <f t="shared" si="185"/>
+        <v>0</v>
+      </c>
+      <c r="M134" s="3">
+        <f t="shared" si="186"/>
+        <v>0</v>
+      </c>
+      <c r="N134" s="5">
+        <f t="shared" si="187"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="5:14">
+      <c r="E135" s="1">
+        <f t="shared" si="180"/>
+        <v>0</v>
+      </c>
+      <c r="F135" s="1">
+        <f t="shared" si="181"/>
+        <v>0</v>
+      </c>
+      <c r="G135" s="3">
+        <f t="shared" si="182"/>
+        <v>0</v>
+      </c>
+      <c r="H135" s="5">
+        <f t="shared" si="183"/>
+        <v>0</v>
+      </c>
+      <c r="J135" s="3">
+        <f t="shared" si="184"/>
+        <v>0</v>
+      </c>
+      <c r="K135" s="5">
+        <f t="shared" si="185"/>
+        <v>0</v>
+      </c>
+      <c r="M135" s="3">
+        <f t="shared" si="186"/>
+        <v>0</v>
+      </c>
+      <c r="N135" s="5">
+        <f t="shared" si="187"/>
         <v>0</v>
       </c>
     </row>
